--- a/sub-RQ1_result/analysis/result_analysis_excel.xlsx
+++ b/sub-RQ1_result/analysis/result_analysis_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Master_Winfo\MA_Supply_chain_security\MS_test_system\sub-RQ1_result\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BCECE8-29C0-483A-9C6A-A322BAECB354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BCDE57-8ED4-4F6D-BBB4-5E43C8C69CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{482212B2-0356-4914-B53B-8802B28615EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{482212B2-0356-4914-B53B-8802B28615EB}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="2" r:id="rId1"/>
@@ -2759,10 +2759,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2770,18 +2769,11 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="28">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2795,56 +2787,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2879,7 +2822,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2893,7 +2836,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2988,29 +2945,40 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7F29230C-F0E4-43EA-8341-3E01AF9D8D83}" name="results" displayName="results" ref="A1:S433" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:S433" xr:uid="{7F29230C-F0E4-43EA-8341-3E01AF9D8D83}"/>
+  <autoFilter ref="A1:S433" xr:uid="{7F29230C-F0E4-43EA-8341-3E01AF9D8D83}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="B1a"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <filter val="malicious_resolved"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{A65D53B3-AEE8-4BDA-A007-78AF105B23C7}" uniqueName="1" name="cell_id" queryTableFieldId="1" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{FAE1C5D0-B844-4E04-8570-5E7392EC0CD8}" uniqueName="2" name="timestamp" queryTableFieldId="2" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{BBF46145-6F90-4151-B5A4-CDBB35EFE548}" uniqueName="3" name="ecosystem" queryTableFieldId="3" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{BE192AD0-EA51-423D-8064-F03DFC2283D1}" uniqueName="4" name="A - private registry configuration" queryTableFieldId="4" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{0CC34752-F77F-4389-A551-0DF478F89775}" uniqueName="5" name="B1 - package manager configuration" queryTableFieldId="5" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{860742B4-072C-4C8E-A14D-384D82844D79}" uniqueName="6" name="B2 - version specifier" queryTableFieldId="6" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{55C1A906-487C-4BD6-9FE2-2C83CC981730}" uniqueName="7" name="C - pipeline operation type" queryTableFieldId="7" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{58E9AA63-32ED-49FD-8C66-24784E1318A0}" uniqueName="8" name="classification" queryTableFieldId="8" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{A44E4050-08CE-4488-B898-63D9257CCF92}" uniqueName="9" name="pk1_name" queryTableFieldId="9" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{A65D53B3-AEE8-4BDA-A007-78AF105B23C7}" uniqueName="1" name="cell_id" queryTableFieldId="1" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{FAE1C5D0-B844-4E04-8570-5E7392EC0CD8}" uniqueName="2" name="timestamp" queryTableFieldId="2" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{BBF46145-6F90-4151-B5A4-CDBB35EFE548}" uniqueName="3" name="ecosystem" queryTableFieldId="3" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{BE192AD0-EA51-423D-8064-F03DFC2283D1}" uniqueName="4" name="A - private registry configuration" queryTableFieldId="4" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{0CC34752-F77F-4389-A551-0DF478F89775}" uniqueName="5" name="B1 - package manager configuration" queryTableFieldId="5" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{860742B4-072C-4C8E-A14D-384D82844D79}" uniqueName="6" name="B2 - version specifier" queryTableFieldId="6" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{55C1A906-487C-4BD6-9FE2-2C83CC981730}" uniqueName="7" name="C - pipeline operation type" queryTableFieldId="7" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{58E9AA63-32ED-49FD-8C66-24784E1318A0}" uniqueName="8" name="classification" queryTableFieldId="8" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{A44E4050-08CE-4488-B898-63D9257CCF92}" uniqueName="9" name="pk1_name" queryTableFieldId="9" dataDxfId="19"/>
     <tableColumn id="10" xr3:uid="{71E0CA27-6CEE-4940-B266-B7513F22296A}" uniqueName="10" name="pk1_version" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{F6F3F30F-14D7-481E-A758-BCE99E99F129}" uniqueName="11" name="pk1_url" queryTableFieldId="11" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{921B2E99-895D-4E5E-9510-DEAAD18CD223}" uniqueName="12" name="pk2_name" queryTableFieldId="12" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{F6F3F30F-14D7-481E-A758-BCE99E99F129}" uniqueName="11" name="pk1_url" queryTableFieldId="11" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{921B2E99-895D-4E5E-9510-DEAAD18CD223}" uniqueName="12" name="pk2_name" queryTableFieldId="12" dataDxfId="17"/>
     <tableColumn id="13" xr3:uid="{9084FB30-82DC-4AE6-8FB6-1C31A0551FB8}" uniqueName="13" name="pk2_version" queryTableFieldId="13"/>
-    <tableColumn id="14" xr3:uid="{D5B22B60-C596-4281-B574-FA3B124D4F4F}" uniqueName="14" name="pk2_url" queryTableFieldId="14" dataDxfId="22"/>
-    <tableColumn id="15" xr3:uid="{D94E0725-5A59-42CC-BE75-97D4507A7741}" uniqueName="15" name="artifact_path" queryTableFieldId="15" dataDxfId="21"/>
-    <tableColumn id="16" xr3:uid="{71208F8D-867D-4980-A5B2-3594876264F4}" uniqueName="16" name="git_commit" queryTableFieldId="16" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{D5B22B60-C596-4281-B574-FA3B124D4F4F}" uniqueName="14" name="pk2_url" queryTableFieldId="14" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{D94E0725-5A59-42CC-BE75-97D4507A7741}" uniqueName="15" name="artifact_path" queryTableFieldId="15" dataDxfId="15"/>
+    <tableColumn id="16" xr3:uid="{71208F8D-867D-4980-A5B2-3594876264F4}" uniqueName="16" name="git_commit" queryTableFieldId="16" dataDxfId="14"/>
     <tableColumn id="17" xr3:uid="{27213F26-9F4A-4C3E-AE70-27C7397D8686}" uniqueName="17" name="github_run_id" queryTableFieldId="17"/>
-    <tableColumn id="18" xr3:uid="{91A6E711-13C5-4562-A6EC-0ECEC846B0F3}" uniqueName="18" name="key" queryTableFieldId="18" dataDxfId="19">
+    <tableColumn id="18" xr3:uid="{91A6E711-13C5-4562-A6EC-0ECEC846B0F3}" uniqueName="18" name="key" queryTableFieldId="18" dataDxfId="13">
       <calculatedColumnFormula>C2&amp;"|"&amp;D2&amp;"|"&amp;E2&amp;"|"&amp;F2&amp;"|"&amp;G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{CD516DC1-753B-4C59-ABD3-C987D8E0FB42}" uniqueName="19" name="code" queryTableFieldId="19" dataDxfId="18">
+    <tableColumn id="19" xr3:uid="{CD516DC1-753B-4C59-ABD3-C987D8E0FB42}" uniqueName="19" name="code" queryTableFieldId="19" dataDxfId="12">
       <calculatedColumnFormula>IF(H2="malicious_resolved","M",IF(H2="private_resolved","P",IF(H2="resolution_error","E","-")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3416,7 +3384,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -3468,16 +3436,16 @@
       <c r="Q2">
         <v>34113888907</v>
       </c>
-      <c r="R2" s="3" t="str">
+      <c r="R2" s="2" t="str">
         <f t="shared" ref="R2" si="0">C2&amp;"|"&amp;D2&amp;"|"&amp;E2&amp;"|"&amp;F2&amp;"|"&amp;G2</f>
         <v>nodejs|A1a|B1a|B2a|C1a</v>
       </c>
-      <c r="S2" s="2" t="str">
+      <c r="S2" t="str">
         <f>IF(H2="malicious_resolved","M",IF(H2="private_resolved","P",IF(H2="resolution_error","E","-")))</f>
         <v>P</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -3529,11 +3497,11 @@
       <c r="Q3">
         <v>34114003220</v>
       </c>
-      <c r="R3" s="3" t="str">
+      <c r="R3" s="2" t="str">
         <f t="shared" ref="R3:R66" si="1">C3&amp;"|"&amp;D3&amp;"|"&amp;E3&amp;"|"&amp;F3&amp;"|"&amp;G3</f>
         <v>nodejs|A1a|B1a|B2a|C1c</v>
       </c>
-      <c r="S3" s="2" t="str">
+      <c r="S3" t="str">
         <f t="shared" ref="S3:S66" si="2">IF(H3="malicious_resolved","M",IF(H3="private_resolved","P",IF(H3="resolution_error","E","-")))</f>
         <v>P</v>
       </c>
@@ -3590,11 +3558,11 @@
       <c r="Q4">
         <v>34114057763</v>
       </c>
-      <c r="R4" s="3" t="str">
+      <c r="R4" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1a|B2b|C1a</v>
       </c>
-      <c r="S4" s="2" t="str">
+      <c r="S4" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
@@ -3651,11 +3619,11 @@
       <c r="Q5">
         <v>34114159819</v>
       </c>
-      <c r="R5" s="3" t="str">
+      <c r="R5" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1a|B2b|C1c</v>
       </c>
-      <c r="S5" s="2" t="str">
+      <c r="S5" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
@@ -3712,11 +3680,11 @@
       <c r="Q6">
         <v>34114208812</v>
       </c>
-      <c r="R6" s="3" t="str">
+      <c r="R6" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1a|B2c|C1a</v>
       </c>
-      <c r="S6" s="2" t="str">
+      <c r="S6" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
@@ -3773,16 +3741,16 @@
       <c r="Q7">
         <v>34114305648</v>
       </c>
-      <c r="R7" s="3" t="str">
+      <c r="R7" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1a|B2c|C1c</v>
       </c>
-      <c r="S7" s="2" t="str">
+      <c r="S7" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -3828,16 +3796,16 @@
       <c r="Q8">
         <v>34114369482</v>
       </c>
-      <c r="R8" s="3" t="str">
+      <c r="R8" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1b|B2a|C1a</v>
       </c>
-      <c r="S8" s="2" t="str">
+      <c r="S8" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -3883,16 +3851,16 @@
       <c r="Q9">
         <v>34114483207</v>
       </c>
-      <c r="R9" s="3" t="str">
+      <c r="R9" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1b|B2a|C1c</v>
       </c>
-      <c r="S9" s="2" t="str">
+      <c r="S9" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -3944,16 +3912,16 @@
       <c r="Q10">
         <v>34114535707</v>
       </c>
-      <c r="R10" s="3" t="str">
+      <c r="R10" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1b|B2b|C1a</v>
       </c>
-      <c r="S10" s="2" t="str">
+      <c r="S10" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -4005,16 +3973,16 @@
       <c r="Q11">
         <v>34114637322</v>
       </c>
-      <c r="R11" s="3" t="str">
+      <c r="R11" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1b|B2b|C1c</v>
       </c>
-      <c r="S11" s="2" t="str">
+      <c r="S11" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -4066,16 +4034,16 @@
       <c r="Q12">
         <v>34114690711</v>
       </c>
-      <c r="R12" s="3" t="str">
+      <c r="R12" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1b|B2c|C1a</v>
       </c>
-      <c r="S12" s="2" t="str">
+      <c r="S12" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -4127,16 +4095,16 @@
       <c r="Q13">
         <v>34114787510</v>
       </c>
-      <c r="R13" s="3" t="str">
+      <c r="R13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1b|B2c|C1c</v>
       </c>
-      <c r="S13" s="2" t="str">
+      <c r="S13" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -4182,16 +4150,16 @@
       <c r="Q14">
         <v>34114844504</v>
       </c>
-      <c r="R14" s="3" t="str">
+      <c r="R14" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1c|B2a|C1a</v>
       </c>
-      <c r="S14" s="2" t="str">
+      <c r="S14" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -4237,16 +4205,16 @@
       <c r="Q15">
         <v>34114952360</v>
       </c>
-      <c r="R15" s="3" t="str">
+      <c r="R15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1c|B2a|C1c</v>
       </c>
-      <c r="S15" s="2" t="str">
+      <c r="S15" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -4298,16 +4266,16 @@
       <c r="Q16">
         <v>34115004820</v>
       </c>
-      <c r="R16" s="3" t="str">
+      <c r="R16" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1c|B2b|C1a</v>
       </c>
-      <c r="S16" s="2" t="str">
+      <c r="S16" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>72</v>
       </c>
@@ -4359,16 +4327,16 @@
       <c r="Q17">
         <v>34115104720</v>
       </c>
-      <c r="R17" s="3" t="str">
+      <c r="R17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1c|B2b|C1c</v>
       </c>
-      <c r="S17" s="2" t="str">
+      <c r="S17" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -4420,16 +4388,16 @@
       <c r="Q18">
         <v>34115162489</v>
       </c>
-      <c r="R18" s="3" t="str">
+      <c r="R18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1c|B2c|C1a</v>
       </c>
-      <c r="S18" s="2" t="str">
+      <c r="S18" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -4481,16 +4449,16 @@
       <c r="Q19">
         <v>34115272384</v>
       </c>
-      <c r="R19" s="3" t="str">
+      <c r="R19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1c|B2c|C1c</v>
       </c>
-      <c r="S19" s="2" t="str">
+      <c r="S19" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>78</v>
       </c>
@@ -4536,16 +4504,16 @@
       <c r="Q20">
         <v>34115330065</v>
       </c>
-      <c r="R20" s="3" t="str">
+      <c r="R20" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1d|B2a|C1a</v>
       </c>
-      <c r="S20" s="2" t="str">
+      <c r="S20" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -4591,16 +4559,16 @@
       <c r="Q21">
         <v>34115441545</v>
       </c>
-      <c r="R21" s="3" t="str">
+      <c r="R21" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1d|B2a|C1c</v>
       </c>
-      <c r="S21" s="2" t="str">
+      <c r="S21" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -4652,16 +4620,16 @@
       <c r="Q22">
         <v>34115499907</v>
       </c>
-      <c r="R22" s="3" t="str">
+      <c r="R22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1d|B2b|C1a</v>
       </c>
-      <c r="S22" s="2" t="str">
+      <c r="S22" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -4713,16 +4681,16 @@
       <c r="Q23">
         <v>34115617847</v>
       </c>
-      <c r="R23" s="3" t="str">
+      <c r="R23" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1d|B2b|C1c</v>
       </c>
-      <c r="S23" s="2" t="str">
+      <c r="S23" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>87</v>
       </c>
@@ -4774,16 +4742,16 @@
       <c r="Q24">
         <v>34115678801</v>
       </c>
-      <c r="R24" s="3" t="str">
+      <c r="R24" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1d|B2c|C1a</v>
       </c>
-      <c r="S24" s="2" t="str">
+      <c r="S24" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>89</v>
       </c>
@@ -4835,16 +4803,16 @@
       <c r="Q25">
         <v>34115784848</v>
       </c>
-      <c r="R25" s="3" t="str">
+      <c r="R25" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1a|B1d|B2c|C1c</v>
       </c>
-      <c r="S25" s="2" t="str">
+      <c r="S25" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>91</v>
       </c>
@@ -4896,16 +4864,16 @@
       <c r="Q26">
         <v>34115837590</v>
       </c>
-      <c r="R26" s="3" t="str">
+      <c r="R26" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1a|B2a|C1a</v>
       </c>
-      <c r="S26" s="2" t="str">
+      <c r="S26" t="str">
         <f t="shared" si="2"/>
         <v>P</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>96</v>
       </c>
@@ -4957,11 +4925,11 @@
       <c r="Q27">
         <v>34115935529</v>
       </c>
-      <c r="R27" s="3" t="str">
+      <c r="R27" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1a|B2a|C1c</v>
       </c>
-      <c r="S27" s="2" t="str">
+      <c r="S27" t="str">
         <f t="shared" si="2"/>
         <v>P</v>
       </c>
@@ -5018,11 +4986,11 @@
       <c r="Q28">
         <v>34115994072</v>
       </c>
-      <c r="R28" s="3" t="str">
+      <c r="R28" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1a|B2b|C1a</v>
       </c>
-      <c r="S28" s="2" t="str">
+      <c r="S28" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
@@ -5079,11 +5047,11 @@
       <c r="Q29">
         <v>34116096214</v>
       </c>
-      <c r="R29" s="3" t="str">
+      <c r="R29" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1a|B2b|C1c</v>
       </c>
-      <c r="S29" s="2" t="str">
+      <c r="S29" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
@@ -5140,11 +5108,11 @@
       <c r="Q30">
         <v>34116151303</v>
       </c>
-      <c r="R30" s="3" t="str">
+      <c r="R30" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1a|B2c|C1a</v>
       </c>
-      <c r="S30" s="2" t="str">
+      <c r="S30" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
@@ -5201,16 +5169,16 @@
       <c r="Q31">
         <v>34116253591</v>
       </c>
-      <c r="R31" s="3" t="str">
+      <c r="R31" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1a|B2c|C1c</v>
       </c>
-      <c r="S31" s="2" t="str">
+      <c r="S31" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>108</v>
       </c>
@@ -5256,16 +5224,16 @@
       <c r="Q32">
         <v>34116308952</v>
       </c>
-      <c r="R32" s="3" t="str">
+      <c r="R32" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1b|B2a|C1a</v>
       </c>
-      <c r="S32" s="2" t="str">
+      <c r="S32" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -5311,16 +5279,16 @@
       <c r="Q33">
         <v>34116407149</v>
       </c>
-      <c r="R33" s="3" t="str">
+      <c r="R33" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1b|B2a|C1c</v>
       </c>
-      <c r="S33" s="2" t="str">
+      <c r="S33" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>112</v>
       </c>
@@ -5372,16 +5340,16 @@
       <c r="Q34">
         <v>34116456879</v>
       </c>
-      <c r="R34" s="3" t="str">
+      <c r="R34" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1b|B2b|C1a</v>
       </c>
-      <c r="S34" s="2" t="str">
+      <c r="S34" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>114</v>
       </c>
@@ -5433,16 +5401,16 @@
       <c r="Q35">
         <v>34116567249</v>
       </c>
-      <c r="R35" s="3" t="str">
+      <c r="R35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1b|B2b|C1c</v>
       </c>
-      <c r="S35" s="2" t="str">
+      <c r="S35" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>116</v>
       </c>
@@ -5494,16 +5462,16 @@
       <c r="Q36">
         <v>34116621847</v>
       </c>
-      <c r="R36" s="3" t="str">
+      <c r="R36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1b|B2c|C1a</v>
       </c>
-      <c r="S36" s="2" t="str">
+      <c r="S36" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -5555,16 +5523,16 @@
       <c r="Q37">
         <v>34116718007</v>
       </c>
-      <c r="R37" s="3" t="str">
+      <c r="R37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1b|B2c|C1c</v>
       </c>
-      <c r="S37" s="2" t="str">
+      <c r="S37" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>120</v>
       </c>
@@ -5610,16 +5578,16 @@
       <c r="Q38">
         <v>34116770132</v>
       </c>
-      <c r="R38" s="3" t="str">
+      <c r="R38" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1c|B2a|C1a</v>
       </c>
-      <c r="S38" s="2" t="str">
+      <c r="S38" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -5665,16 +5633,16 @@
       <c r="Q39">
         <v>34116863329</v>
       </c>
-      <c r="R39" s="3" t="str">
+      <c r="R39" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1c|B2a|C1c</v>
       </c>
-      <c r="S39" s="2" t="str">
+      <c r="S39" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>124</v>
       </c>
@@ -5726,16 +5694,16 @@
       <c r="Q40">
         <v>34116911633</v>
       </c>
-      <c r="R40" s="3" t="str">
+      <c r="R40" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1c|B2b|C1a</v>
       </c>
-      <c r="S40" s="2" t="str">
+      <c r="S40" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -5787,16 +5755,16 @@
       <c r="Q41">
         <v>34117020007</v>
       </c>
-      <c r="R41" s="3" t="str">
+      <c r="R41" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1c|B2b|C1c</v>
       </c>
-      <c r="S41" s="2" t="str">
+      <c r="S41" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>128</v>
       </c>
@@ -5848,16 +5816,16 @@
       <c r="Q42">
         <v>34117073958</v>
       </c>
-      <c r="R42" s="3" t="str">
+      <c r="R42" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1c|B2c|C1a</v>
       </c>
-      <c r="S42" s="2" t="str">
+      <c r="S42" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>130</v>
       </c>
@@ -5909,16 +5877,16 @@
       <c r="Q43">
         <v>34117177741</v>
       </c>
-      <c r="R43" s="3" t="str">
+      <c r="R43" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1c|B2c|C1c</v>
       </c>
-      <c r="S43" s="2" t="str">
+      <c r="S43" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>132</v>
       </c>
@@ -5964,16 +5932,16 @@
       <c r="Q44">
         <v>34117230118</v>
       </c>
-      <c r="R44" s="3" t="str">
+      <c r="R44" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1d|B2a|C1a</v>
       </c>
-      <c r="S44" s="2" t="str">
+      <c r="S44" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>134</v>
       </c>
@@ -6019,16 +5987,16 @@
       <c r="Q45">
         <v>34117326219</v>
       </c>
-      <c r="R45" s="3" t="str">
+      <c r="R45" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1d|B2a|C1c</v>
       </c>
-      <c r="S45" s="2" t="str">
+      <c r="S45" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>136</v>
       </c>
@@ -6080,16 +6048,16 @@
       <c r="Q46">
         <v>34117375663</v>
       </c>
-      <c r="R46" s="3" t="str">
+      <c r="R46" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1d|B2b|C1a</v>
       </c>
-      <c r="S46" s="2" t="str">
+      <c r="S46" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>138</v>
       </c>
@@ -6141,16 +6109,16 @@
       <c r="Q47">
         <v>34117475534</v>
       </c>
-      <c r="R47" s="3" t="str">
+      <c r="R47" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1d|B2b|C1c</v>
       </c>
-      <c r="S47" s="2" t="str">
+      <c r="S47" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -6202,16 +6170,16 @@
       <c r="Q48">
         <v>34117532741</v>
       </c>
-      <c r="R48" s="3" t="str">
+      <c r="R48" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1d|B2c|C1a</v>
       </c>
-      <c r="S48" s="2" t="str">
+      <c r="S48" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>142</v>
       </c>
@@ -6263,16 +6231,16 @@
       <c r="Q49">
         <v>34117627729</v>
       </c>
-      <c r="R49" s="3" t="str">
+      <c r="R49" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A1b|B1d|B2c|C1c</v>
       </c>
-      <c r="S49" s="2" t="str">
+      <c r="S49" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>144</v>
       </c>
@@ -6318,16 +6286,16 @@
       <c r="Q50">
         <v>34117679431</v>
       </c>
-      <c r="R50" s="3" t="str">
+      <c r="R50" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1a|B2a|C1a</v>
       </c>
-      <c r="S50" s="2" t="str">
+      <c r="S50" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>147</v>
       </c>
@@ -6373,16 +6341,16 @@
       <c r="Q51">
         <v>34117770868</v>
       </c>
-      <c r="R51" s="3" t="str">
+      <c r="R51" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1a|B2a|C1c</v>
       </c>
-      <c r="S51" s="2" t="str">
+      <c r="S51" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>149</v>
       </c>
@@ -6428,16 +6396,16 @@
       <c r="Q52">
         <v>34117821027</v>
       </c>
-      <c r="R52" s="3" t="str">
+      <c r="R52" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1a|B2b|C1a</v>
       </c>
-      <c r="S52" s="2" t="str">
+      <c r="S52" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>151</v>
       </c>
@@ -6483,16 +6451,16 @@
       <c r="Q53">
         <v>34117918305</v>
       </c>
-      <c r="R53" s="3" t="str">
+      <c r="R53" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1a|B2b|C1c</v>
       </c>
-      <c r="S53" s="2" t="str">
+      <c r="S53" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>153</v>
       </c>
@@ -6538,16 +6506,16 @@
       <c r="Q54">
         <v>34117966213</v>
       </c>
-      <c r="R54" s="3" t="str">
+      <c r="R54" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1a|B2c|C1a</v>
       </c>
-      <c r="S54" s="2" t="str">
+      <c r="S54" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>155</v>
       </c>
@@ -6593,16 +6561,16 @@
       <c r="Q55">
         <v>34118059587</v>
       </c>
-      <c r="R55" s="3" t="str">
+      <c r="R55" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1a|B2c|C1c</v>
       </c>
-      <c r="S55" s="2" t="str">
+      <c r="S55" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>157</v>
       </c>
@@ -6648,16 +6616,16 @@
       <c r="Q56">
         <v>34118106463</v>
       </c>
-      <c r="R56" s="3" t="str">
+      <c r="R56" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1b|B2a|C1a</v>
       </c>
-      <c r="S56" s="2" t="str">
+      <c r="S56" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>159</v>
       </c>
@@ -6703,16 +6671,16 @@
       <c r="Q57">
         <v>34118201797</v>
       </c>
-      <c r="R57" s="3" t="str">
+      <c r="R57" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1b|B2a|C1c</v>
       </c>
-      <c r="S57" s="2" t="str">
+      <c r="S57" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>161</v>
       </c>
@@ -6764,16 +6732,16 @@
       <c r="Q58">
         <v>34118257735</v>
       </c>
-      <c r="R58" s="3" t="str">
+      <c r="R58" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1b|B2b|C1a</v>
       </c>
-      <c r="S58" s="2" t="str">
+      <c r="S58" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>163</v>
       </c>
@@ -6825,16 +6793,16 @@
       <c r="Q59">
         <v>34118356779</v>
       </c>
-      <c r="R59" s="3" t="str">
+      <c r="R59" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1b|B2b|C1c</v>
       </c>
-      <c r="S59" s="2" t="str">
+      <c r="S59" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>165</v>
       </c>
@@ -6886,16 +6854,16 @@
       <c r="Q60">
         <v>34118404806</v>
       </c>
-      <c r="R60" s="3" t="str">
+      <c r="R60" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1b|B2c|C1a</v>
       </c>
-      <c r="S60" s="2" t="str">
+      <c r="S60" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>167</v>
       </c>
@@ -6947,16 +6915,16 @@
       <c r="Q61">
         <v>34118508506</v>
       </c>
-      <c r="R61" s="3" t="str">
+      <c r="R61" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1b|B2c|C1c</v>
       </c>
-      <c r="S61" s="2" t="str">
+      <c r="S61" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>169</v>
       </c>
@@ -7002,16 +6970,16 @@
       <c r="Q62">
         <v>34118562775</v>
       </c>
-      <c r="R62" s="3" t="str">
+      <c r="R62" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1c|B2a|C1a</v>
       </c>
-      <c r="S62" s="2" t="str">
+      <c r="S62" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>171</v>
       </c>
@@ -7057,16 +7025,16 @@
       <c r="Q63">
         <v>34118662913</v>
       </c>
-      <c r="R63" s="3" t="str">
+      <c r="R63" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1c|B2a|C1c</v>
       </c>
-      <c r="S63" s="2" t="str">
+      <c r="S63" t="str">
         <f t="shared" si="2"/>
         <v>E</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>173</v>
       </c>
@@ -7118,16 +7086,16 @@
       <c r="Q64">
         <v>34118718562</v>
       </c>
-      <c r="R64" s="3" t="str">
+      <c r="R64" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1c|B2b|C1a</v>
       </c>
-      <c r="S64" s="2" t="str">
+      <c r="S64" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>175</v>
       </c>
@@ -7179,16 +7147,16 @@
       <c r="Q65">
         <v>34118818239</v>
       </c>
-      <c r="R65" s="3" t="str">
+      <c r="R65" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1c|B2b|C1c</v>
       </c>
-      <c r="S65" s="2" t="str">
+      <c r="S65" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>177</v>
       </c>
@@ -7240,16 +7208,16 @@
       <c r="Q66">
         <v>34118867960</v>
       </c>
-      <c r="R66" s="3" t="str">
+      <c r="R66" s="2" t="str">
         <f t="shared" si="1"/>
         <v>nodejs|A2|B1c|B2c|C1a</v>
       </c>
-      <c r="S66" s="2" t="str">
+      <c r="S66" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>179</v>
       </c>
@@ -7301,16 +7269,16 @@
       <c r="Q67">
         <v>34118960446</v>
       </c>
-      <c r="R67" s="3" t="str">
+      <c r="R67" s="2" t="str">
         <f t="shared" ref="R67:R130" si="3">C67&amp;"|"&amp;D67&amp;"|"&amp;E67&amp;"|"&amp;F67&amp;"|"&amp;G67</f>
         <v>nodejs|A2|B1c|B2c|C1c</v>
       </c>
-      <c r="S67" s="2" t="str">
+      <c r="S67" t="str">
         <f t="shared" ref="S67:S130" si="4">IF(H67="malicious_resolved","M",IF(H67="private_resolved","P",IF(H67="resolution_error","E","-")))</f>
         <v>M</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>181</v>
       </c>
@@ -7356,16 +7324,16 @@
       <c r="Q68">
         <v>34119014127</v>
       </c>
-      <c r="R68" s="3" t="str">
+      <c r="R68" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A2|B1d|B2a|C1a</v>
       </c>
-      <c r="S68" s="2" t="str">
+      <c r="S68" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>183</v>
       </c>
@@ -7411,16 +7379,16 @@
       <c r="Q69">
         <v>34119113739</v>
       </c>
-      <c r="R69" s="3" t="str">
+      <c r="R69" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A2|B1d|B2a|C1c</v>
       </c>
-      <c r="S69" s="2" t="str">
+      <c r="S69" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>185</v>
       </c>
@@ -7472,16 +7440,16 @@
       <c r="Q70">
         <v>34119161569</v>
       </c>
-      <c r="R70" s="3" t="str">
+      <c r="R70" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A2|B1d|B2b|C1a</v>
       </c>
-      <c r="S70" s="2" t="str">
+      <c r="S70" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>187</v>
       </c>
@@ -7533,16 +7501,16 @@
       <c r="Q71">
         <v>34119259971</v>
       </c>
-      <c r="R71" s="3" t="str">
+      <c r="R71" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A2|B1d|B2b|C1c</v>
       </c>
-      <c r="S71" s="2" t="str">
+      <c r="S71" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>189</v>
       </c>
@@ -7594,16 +7562,16 @@
       <c r="Q72">
         <v>34119312950</v>
       </c>
-      <c r="R72" s="3" t="str">
+      <c r="R72" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A2|B1d|B2c|C1a</v>
       </c>
-      <c r="S72" s="2" t="str">
+      <c r="S72" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>191</v>
       </c>
@@ -7655,16 +7623,16 @@
       <c r="Q73">
         <v>34119411234</v>
       </c>
-      <c r="R73" s="3" t="str">
+      <c r="R73" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A2|B1d|B2c|C1c</v>
       </c>
-      <c r="S73" s="2" t="str">
+      <c r="S73" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>193</v>
       </c>
@@ -7710,16 +7678,16 @@
       <c r="Q74">
         <v>34119463864</v>
       </c>
-      <c r="R74" s="3" t="str">
+      <c r="R74" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1a|B2a|C1a</v>
       </c>
-      <c r="S74" s="2" t="str">
+      <c r="S74" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>196</v>
       </c>
@@ -7765,16 +7733,16 @@
       <c r="Q75">
         <v>34119568144</v>
       </c>
-      <c r="R75" s="3" t="str">
+      <c r="R75" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1a|B2a|C1c</v>
       </c>
-      <c r="S75" s="2" t="str">
+      <c r="S75" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>198</v>
       </c>
@@ -7820,16 +7788,16 @@
       <c r="Q76">
         <v>34119622186</v>
       </c>
-      <c r="R76" s="3" t="str">
+      <c r="R76" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1a|B2b|C1a</v>
       </c>
-      <c r="S76" s="2" t="str">
+      <c r="S76" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>200</v>
       </c>
@@ -7875,16 +7843,16 @@
       <c r="Q77">
         <v>34119725097</v>
       </c>
-      <c r="R77" s="3" t="str">
+      <c r="R77" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1a|B2b|C1c</v>
       </c>
-      <c r="S77" s="2" t="str">
+      <c r="S77" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>202</v>
       </c>
@@ -7930,16 +7898,16 @@
       <c r="Q78">
         <v>34119775392</v>
       </c>
-      <c r="R78" s="3" t="str">
+      <c r="R78" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1a|B2c|C1a</v>
       </c>
-      <c r="S78" s="2" t="str">
+      <c r="S78" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>204</v>
       </c>
@@ -7985,16 +7953,16 @@
       <c r="Q79">
         <v>34119873134</v>
       </c>
-      <c r="R79" s="3" t="str">
+      <c r="R79" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1a|B2c|C1c</v>
       </c>
-      <c r="S79" s="2" t="str">
+      <c r="S79" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>206</v>
       </c>
@@ -8040,16 +8008,16 @@
       <c r="Q80">
         <v>34119927201</v>
       </c>
-      <c r="R80" s="3" t="str">
+      <c r="R80" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1b|B2a|C1a</v>
       </c>
-      <c r="S80" s="2" t="str">
+      <c r="S80" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>208</v>
       </c>
@@ -8095,16 +8063,16 @@
       <c r="Q81">
         <v>34120032574</v>
       </c>
-      <c r="R81" s="3" t="str">
+      <c r="R81" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1b|B2a|C1c</v>
       </c>
-      <c r="S81" s="2" t="str">
+      <c r="S81" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>210</v>
       </c>
@@ -8156,16 +8124,16 @@
       <c r="Q82">
         <v>34120080544</v>
       </c>
-      <c r="R82" s="3" t="str">
+      <c r="R82" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1b|B2b|C1a</v>
       </c>
-      <c r="S82" s="2" t="str">
+      <c r="S82" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>212</v>
       </c>
@@ -8217,16 +8185,16 @@
       <c r="Q83">
         <v>34120180209</v>
       </c>
-      <c r="R83" s="3" t="str">
+      <c r="R83" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1b|B2b|C1c</v>
       </c>
-      <c r="S83" s="2" t="str">
+      <c r="S83" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>214</v>
       </c>
@@ -8278,16 +8246,16 @@
       <c r="Q84">
         <v>34120239746</v>
       </c>
-      <c r="R84" s="3" t="str">
+      <c r="R84" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1b|B2c|C1a</v>
       </c>
-      <c r="S84" s="2" t="str">
+      <c r="S84" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>216</v>
       </c>
@@ -8339,16 +8307,16 @@
       <c r="Q85">
         <v>34120345302</v>
       </c>
-      <c r="R85" s="3" t="str">
+      <c r="R85" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1b|B2c|C1c</v>
       </c>
-      <c r="S85" s="2" t="str">
+      <c r="S85" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>218</v>
       </c>
@@ -8394,16 +8362,16 @@
       <c r="Q86">
         <v>34120402886</v>
       </c>
-      <c r="R86" s="3" t="str">
+      <c r="R86" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1d|B2a|C1a</v>
       </c>
-      <c r="S86" s="2" t="str">
+      <c r="S86" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>220</v>
       </c>
@@ -8449,16 +8417,16 @@
       <c r="Q87">
         <v>34120518073</v>
       </c>
-      <c r="R87" s="3" t="str">
+      <c r="R87" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1d|B2a|C1c</v>
       </c>
-      <c r="S87" s="2" t="str">
+      <c r="S87" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>222</v>
       </c>
@@ -8510,16 +8478,16 @@
       <c r="Q88">
         <v>34120592828</v>
       </c>
-      <c r="R88" s="3" t="str">
+      <c r="R88" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1d|B2b|C1a</v>
       </c>
-      <c r="S88" s="2" t="str">
+      <c r="S88" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>224</v>
       </c>
@@ -8571,16 +8539,16 @@
       <c r="Q89">
         <v>34120699518</v>
       </c>
-      <c r="R89" s="3" t="str">
+      <c r="R89" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1d|B2b|C1c</v>
       </c>
-      <c r="S89" s="2" t="str">
+      <c r="S89" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>226</v>
       </c>
@@ -8632,16 +8600,16 @@
       <c r="Q90">
         <v>34120757851</v>
       </c>
-      <c r="R90" s="3" t="str">
+      <c r="R90" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1d|B2c|C1a</v>
       </c>
-      <c r="S90" s="2" t="str">
+      <c r="S90" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>228</v>
       </c>
@@ -8693,16 +8661,16 @@
       <c r="Q91">
         <v>34120871263</v>
       </c>
-      <c r="R91" s="3" t="str">
+      <c r="R91" s="2" t="str">
         <f t="shared" si="3"/>
         <v>nodejs|A3|B1d|B2c|C1c</v>
       </c>
-      <c r="S91" s="2" t="str">
+      <c r="S91" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>230</v>
       </c>
@@ -8754,16 +8722,16 @@
       <c r="Q92">
         <v>34120931612</v>
       </c>
-      <c r="R92" s="3" t="str">
+      <c r="R92" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1a|B2a|C1a</v>
       </c>
-      <c r="S92" s="2" t="str">
+      <c r="S92" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>237</v>
       </c>
@@ -8815,16 +8783,16 @@
       <c r="Q93">
         <v>34121001559</v>
       </c>
-      <c r="R93" s="3" t="str">
+      <c r="R93" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1a|B2a|C1b</v>
       </c>
-      <c r="S93" s="2" t="str">
+      <c r="S93" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>240</v>
       </c>
@@ -8876,11 +8844,11 @@
       <c r="Q94">
         <v>34121077911</v>
       </c>
-      <c r="R94" s="3" t="str">
+      <c r="R94" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1a|B2a|C1c</v>
       </c>
-      <c r="S94" s="2" t="str">
+      <c r="S94" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
@@ -8937,11 +8905,11 @@
       <c r="Q95">
         <v>34121142276</v>
       </c>
-      <c r="R95" s="3" t="str">
+      <c r="R95" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1a|B2b|C1a</v>
       </c>
-      <c r="S95" s="2" t="str">
+      <c r="S95" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
@@ -8998,11 +8966,11 @@
       <c r="Q96">
         <v>34121196965</v>
       </c>
-      <c r="R96" s="3" t="str">
+      <c r="R96" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1a|B2b|C1b</v>
       </c>
-      <c r="S96" s="2" t="str">
+      <c r="S96" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
@@ -9059,11 +9027,11 @@
       <c r="Q97">
         <v>34121268501</v>
       </c>
-      <c r="R97" s="3" t="str">
+      <c r="R97" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1a|B2b|C1c</v>
       </c>
-      <c r="S97" s="2" t="str">
+      <c r="S97" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
@@ -9120,11 +9088,11 @@
       <c r="Q98">
         <v>34121335898</v>
       </c>
-      <c r="R98" s="3" t="str">
+      <c r="R98" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1a|B2c|C1a</v>
       </c>
-      <c r="S98" s="2" t="str">
+      <c r="S98" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
@@ -9181,11 +9149,11 @@
       <c r="Q99">
         <v>34121388780</v>
       </c>
-      <c r="R99" s="3" t="str">
+      <c r="R99" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1a|B2c|C1b</v>
       </c>
-      <c r="S99" s="2" t="str">
+      <c r="S99" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
@@ -9242,16 +9210,16 @@
       <c r="Q100">
         <v>34121456574</v>
       </c>
-      <c r="R100" s="3" t="str">
+      <c r="R100" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1a|B2c|C1c</v>
       </c>
-      <c r="S100" s="2" t="str">
+      <c r="S100" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>256</v>
       </c>
@@ -9303,16 +9271,16 @@
       <c r="Q101">
         <v>34121510343</v>
       </c>
-      <c r="R101" s="3" t="str">
+      <c r="R101" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1b|B2a|C1a</v>
       </c>
-      <c r="S101" s="2" t="str">
+      <c r="S101" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>258</v>
       </c>
@@ -9364,16 +9332,16 @@
       <c r="Q102">
         <v>34121572057</v>
       </c>
-      <c r="R102" s="3" t="str">
+      <c r="R102" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1b|B2a|C1b</v>
       </c>
-      <c r="S102" s="2" t="str">
+      <c r="S102" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>260</v>
       </c>
@@ -9425,16 +9393,16 @@
       <c r="Q103">
         <v>34121647872</v>
       </c>
-      <c r="R103" s="3" t="str">
+      <c r="R103" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1b|B2a|C1c</v>
       </c>
-      <c r="S103" s="2" t="str">
+      <c r="S103" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>262</v>
       </c>
@@ -9486,16 +9454,16 @@
       <c r="Q104">
         <v>34121717338</v>
       </c>
-      <c r="R104" s="3" t="str">
+      <c r="R104" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1b|B2b|C1a</v>
       </c>
-      <c r="S104" s="2" t="str">
+      <c r="S104" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>266</v>
       </c>
@@ -9547,16 +9515,16 @@
       <c r="Q105">
         <v>34121792257</v>
       </c>
-      <c r="R105" s="3" t="str">
+      <c r="R105" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1b|B2b|C1b</v>
       </c>
-      <c r="S105" s="2" t="str">
+      <c r="S105" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>268</v>
       </c>
@@ -9608,16 +9576,16 @@
       <c r="Q106">
         <v>34121876011</v>
       </c>
-      <c r="R106" s="3" t="str">
+      <c r="R106" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1b|B2b|C1c</v>
       </c>
-      <c r="S106" s="2" t="str">
+      <c r="S106" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>270</v>
       </c>
@@ -9669,16 +9637,16 @@
       <c r="Q107">
         <v>34121938098</v>
       </c>
-      <c r="R107" s="3" t="str">
+      <c r="R107" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1b|B2c|C1a</v>
       </c>
-      <c r="S107" s="2" t="str">
+      <c r="S107" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>272</v>
       </c>
@@ -9730,16 +9698,16 @@
       <c r="Q108">
         <v>34121998883</v>
       </c>
-      <c r="R108" s="3" t="str">
+      <c r="R108" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1b|B2c|C1b</v>
       </c>
-      <c r="S108" s="2" t="str">
+      <c r="S108" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>274</v>
       </c>
@@ -9791,16 +9759,16 @@
       <c r="Q109">
         <v>34122094413</v>
       </c>
-      <c r="R109" s="3" t="str">
+      <c r="R109" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1b|B2c|C1c</v>
       </c>
-      <c r="S109" s="2" t="str">
+      <c r="S109" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>276</v>
       </c>
@@ -9852,16 +9820,16 @@
       <c r="Q110">
         <v>34122167211</v>
       </c>
-      <c r="R110" s="3" t="str">
+      <c r="R110" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1c|B2a|C1a</v>
       </c>
-      <c r="S110" s="2" t="str">
+      <c r="S110" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>278</v>
       </c>
@@ -9913,16 +9881,16 @@
       <c r="Q111">
         <v>34122254187</v>
       </c>
-      <c r="R111" s="3" t="str">
+      <c r="R111" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1c|B2a|C1b</v>
       </c>
-      <c r="S111" s="2" t="str">
+      <c r="S111" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>280</v>
       </c>
@@ -9974,16 +9942,16 @@
       <c r="Q112">
         <v>34122391849</v>
       </c>
-      <c r="R112" s="3" t="str">
+      <c r="R112" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1c|B2a|C1c</v>
       </c>
-      <c r="S112" s="2" t="str">
+      <c r="S112" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>282</v>
       </c>
@@ -10035,16 +10003,16 @@
       <c r="Q113">
         <v>34122490493</v>
       </c>
-      <c r="R113" s="3" t="str">
+      <c r="R113" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1c|B2b|C1a</v>
       </c>
-      <c r="S113" s="2" t="str">
+      <c r="S113" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>286</v>
       </c>
@@ -10096,16 +10064,16 @@
       <c r="Q114">
         <v>34122579428</v>
       </c>
-      <c r="R114" s="3" t="str">
+      <c r="R114" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1c|B2b|C1b</v>
       </c>
-      <c r="S114" s="2" t="str">
+      <c r="S114" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>288</v>
       </c>
@@ -10157,16 +10125,16 @@
       <c r="Q115">
         <v>34122680606</v>
       </c>
-      <c r="R115" s="3" t="str">
+      <c r="R115" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1c|B2b|C1c</v>
       </c>
-      <c r="S115" s="2" t="str">
+      <c r="S115" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>290</v>
       </c>
@@ -10218,16 +10186,16 @@
       <c r="Q116">
         <v>34122745968</v>
       </c>
-      <c r="R116" s="3" t="str">
+      <c r="R116" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1c|B2c|C1a</v>
       </c>
-      <c r="S116" s="2" t="str">
+      <c r="S116" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>292</v>
       </c>
@@ -10279,16 +10247,16 @@
       <c r="Q117">
         <v>34122807814</v>
       </c>
-      <c r="R117" s="3" t="str">
+      <c r="R117" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1c|B2c|C1b</v>
       </c>
-      <c r="S117" s="2" t="str">
+      <c r="S117" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>294</v>
       </c>
@@ -10340,16 +10308,16 @@
       <c r="Q118">
         <v>34122897223</v>
       </c>
-      <c r="R118" s="3" t="str">
+      <c r="R118" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1c|B2c|C1c</v>
       </c>
-      <c r="S118" s="2" t="str">
+      <c r="S118" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>296</v>
       </c>
@@ -10395,16 +10363,16 @@
       <c r="Q119">
         <v>34122969054</v>
       </c>
-      <c r="R119" s="3" t="str">
+      <c r="R119" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1d|B2a|C1a</v>
       </c>
-      <c r="S119" s="2" t="str">
+      <c r="S119" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>298</v>
       </c>
@@ -10450,16 +10418,16 @@
       <c r="Q120">
         <v>34123031113</v>
       </c>
-      <c r="R120" s="3" t="str">
+      <c r="R120" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1d|B2a|C1b</v>
       </c>
-      <c r="S120" s="2" t="str">
+      <c r="S120" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>300</v>
       </c>
@@ -10505,16 +10473,16 @@
       <c r="Q121">
         <v>34123096827</v>
       </c>
-      <c r="R121" s="3" t="str">
+      <c r="R121" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1d|B2a|C1c</v>
       </c>
-      <c r="S121" s="2" t="str">
+      <c r="S121" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>302</v>
       </c>
@@ -10566,16 +10534,16 @@
       <c r="Q122">
         <v>34123168930</v>
       </c>
-      <c r="R122" s="3" t="str">
+      <c r="R122" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1d|B2b|C1a</v>
       </c>
-      <c r="S122" s="2" t="str">
+      <c r="S122" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>304</v>
       </c>
@@ -10621,16 +10589,16 @@
       <c r="Q123">
         <v>34123233592</v>
       </c>
-      <c r="R123" s="3" t="str">
+      <c r="R123" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1d|B2b|C1b</v>
       </c>
-      <c r="S123" s="2" t="str">
+      <c r="S123" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>306</v>
       </c>
@@ -10682,16 +10650,16 @@
       <c r="Q124">
         <v>34123303823</v>
       </c>
-      <c r="R124" s="3" t="str">
+      <c r="R124" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1d|B2b|C1c</v>
       </c>
-      <c r="S124" s="2" t="str">
+      <c r="S124" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>308</v>
       </c>
@@ -10743,16 +10711,16 @@
       <c r="Q125">
         <v>34123376416</v>
       </c>
-      <c r="R125" s="3" t="str">
+      <c r="R125" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1d|B2c|C1a</v>
       </c>
-      <c r="S125" s="2" t="str">
+      <c r="S125" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>310</v>
       </c>
@@ -10798,16 +10766,16 @@
       <c r="Q126">
         <v>34123442059</v>
       </c>
-      <c r="R126" s="3" t="str">
+      <c r="R126" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1d|B2c|C1b</v>
       </c>
-      <c r="S126" s="2" t="str">
+      <c r="S126" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>312</v>
       </c>
@@ -10859,16 +10827,16 @@
       <c r="Q127">
         <v>34123512194</v>
       </c>
-      <c r="R127" s="3" t="str">
+      <c r="R127" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1a|B1d|B2c|C1c</v>
       </c>
-      <c r="S127" s="2" t="str">
+      <c r="S127" t="str">
         <f t="shared" si="4"/>
         <v>M</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>314</v>
       </c>
@@ -10920,16 +10888,16 @@
       <c r="Q128">
         <v>34123590536</v>
       </c>
-      <c r="R128" s="3" t="str">
+      <c r="R128" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1b|B1a|B2a|C1a</v>
       </c>
-      <c r="S128" s="2" t="str">
+      <c r="S128" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>318</v>
       </c>
@@ -10981,16 +10949,16 @@
       <c r="Q129">
         <v>34123674516</v>
       </c>
-      <c r="R129" s="3" t="str">
+      <c r="R129" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1b|B1a|B2a|C1b</v>
       </c>
-      <c r="S129" s="2" t="str">
+      <c r="S129" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>320</v>
       </c>
@@ -11042,11 +11010,11 @@
       <c r="Q130">
         <v>34123782223</v>
       </c>
-      <c r="R130" s="3" t="str">
+      <c r="R130" s="2" t="str">
         <f t="shared" si="3"/>
         <v>python|A1b|B1a|B2a|C1c</v>
       </c>
-      <c r="S130" s="2" t="str">
+      <c r="S130" t="str">
         <f t="shared" si="4"/>
         <v>P</v>
       </c>
@@ -11103,11 +11071,11 @@
       <c r="Q131">
         <v>34123862136</v>
       </c>
-      <c r="R131" s="3" t="str">
+      <c r="R131" s="2" t="str">
         <f t="shared" ref="R131:R194" si="5">C131&amp;"|"&amp;D131&amp;"|"&amp;E131&amp;"|"&amp;F131&amp;"|"&amp;G131</f>
         <v>python|A1b|B1a|B2b|C1a</v>
       </c>
-      <c r="S131" s="2" t="str">
+      <c r="S131" t="str">
         <f t="shared" ref="S131:S194" si="6">IF(H131="malicious_resolved","M",IF(H131="private_resolved","P",IF(H131="resolution_error","E","-")))</f>
         <v>M</v>
       </c>
@@ -11164,11 +11132,11 @@
       <c r="Q132">
         <v>34123935304</v>
       </c>
-      <c r="R132" s="3" t="str">
+      <c r="R132" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1a|B2b|C1b</v>
       </c>
-      <c r="S132" s="2" t="str">
+      <c r="S132" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
@@ -11225,11 +11193,11 @@
       <c r="Q133">
         <v>34124046702</v>
       </c>
-      <c r="R133" s="3" t="str">
+      <c r="R133" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1a|B2b|C1c</v>
       </c>
-      <c r="S133" s="2" t="str">
+      <c r="S133" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
@@ -11286,11 +11254,11 @@
       <c r="Q134">
         <v>34124130739</v>
       </c>
-      <c r="R134" s="3" t="str">
+      <c r="R134" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1a|B2c|C1a</v>
       </c>
-      <c r="S134" s="2" t="str">
+      <c r="S134" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
@@ -11347,11 +11315,11 @@
       <c r="Q135">
         <v>34124201761</v>
       </c>
-      <c r="R135" s="3" t="str">
+      <c r="R135" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1a|B2c|C1b</v>
       </c>
-      <c r="S135" s="2" t="str">
+      <c r="S135" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
@@ -11408,16 +11376,16 @@
       <c r="Q136">
         <v>34124291942</v>
       </c>
-      <c r="R136" s="3" t="str">
+      <c r="R136" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1a|B2c|C1c</v>
       </c>
-      <c r="S136" s="2" t="str">
+      <c r="S136" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>336</v>
       </c>
@@ -11469,16 +11437,16 @@
       <c r="Q137">
         <v>34124373551</v>
       </c>
-      <c r="R137" s="3" t="str">
+      <c r="R137" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1b|B2a|C1a</v>
       </c>
-      <c r="S137" s="2" t="str">
+      <c r="S137" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>338</v>
       </c>
@@ -11530,16 +11498,16 @@
       <c r="Q138">
         <v>34124453375</v>
       </c>
-      <c r="R138" s="3" t="str">
+      <c r="R138" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1b|B2a|C1b</v>
       </c>
-      <c r="S138" s="2" t="str">
+      <c r="S138" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>340</v>
       </c>
@@ -11591,16 +11559,16 @@
       <c r="Q139">
         <v>34124548942</v>
       </c>
-      <c r="R139" s="3" t="str">
+      <c r="R139" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1b|B2a|C1c</v>
       </c>
-      <c r="S139" s="2" t="str">
+      <c r="S139" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>342</v>
       </c>
@@ -11652,16 +11620,16 @@
       <c r="Q140">
         <v>34124635518</v>
       </c>
-      <c r="R140" s="3" t="str">
+      <c r="R140" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1b|B2b|C1a</v>
       </c>
-      <c r="S140" s="2" t="str">
+      <c r="S140" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>344</v>
       </c>
@@ -11713,16 +11681,16 @@
       <c r="Q141">
         <v>34124713082</v>
       </c>
-      <c r="R141" s="3" t="str">
+      <c r="R141" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1b|B2b|C1b</v>
       </c>
-      <c r="S141" s="2" t="str">
+      <c r="S141" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>346</v>
       </c>
@@ -11774,16 +11742,16 @@
       <c r="Q142">
         <v>34124800637</v>
       </c>
-      <c r="R142" s="3" t="str">
+      <c r="R142" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1b|B2b|C1c</v>
       </c>
-      <c r="S142" s="2" t="str">
+      <c r="S142" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>348</v>
       </c>
@@ -11835,16 +11803,16 @@
       <c r="Q143">
         <v>34124874711</v>
       </c>
-      <c r="R143" s="3" t="str">
+      <c r="R143" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1b|B2c|C1a</v>
       </c>
-      <c r="S143" s="2" t="str">
+      <c r="S143" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>350</v>
       </c>
@@ -11896,16 +11864,16 @@
       <c r="Q144">
         <v>34124932757</v>
       </c>
-      <c r="R144" s="3" t="str">
+      <c r="R144" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1b|B2c|C1b</v>
       </c>
-      <c r="S144" s="2" t="str">
+      <c r="S144" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>352</v>
       </c>
@@ -11957,16 +11925,16 @@
       <c r="Q145">
         <v>34125041258</v>
       </c>
-      <c r="R145" s="3" t="str">
+      <c r="R145" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1b|B2c|C1c</v>
       </c>
-      <c r="S145" s="2" t="str">
+      <c r="S145" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>354</v>
       </c>
@@ -12018,16 +11986,16 @@
       <c r="Q146">
         <v>34125116065</v>
       </c>
-      <c r="R146" s="3" t="str">
+      <c r="R146" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1c|B2a|C1a</v>
       </c>
-      <c r="S146" s="2" t="str">
+      <c r="S146" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>356</v>
       </c>
@@ -12079,16 +12047,16 @@
       <c r="Q147">
         <v>34125208162</v>
       </c>
-      <c r="R147" s="3" t="str">
+      <c r="R147" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1c|B2a|C1b</v>
       </c>
-      <c r="S147" s="2" t="str">
+      <c r="S147" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>358</v>
       </c>
@@ -12140,16 +12108,16 @@
       <c r="Q148">
         <v>34125322385</v>
       </c>
-      <c r="R148" s="3" t="str">
+      <c r="R148" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1c|B2a|C1c</v>
       </c>
-      <c r="S148" s="2" t="str">
+      <c r="S148" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>360</v>
       </c>
@@ -12201,16 +12169,16 @@
       <c r="Q149">
         <v>34125415641</v>
       </c>
-      <c r="R149" s="3" t="str">
+      <c r="R149" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1c|B2b|C1a</v>
       </c>
-      <c r="S149" s="2" t="str">
+      <c r="S149" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>362</v>
       </c>
@@ -12262,16 +12230,16 @@
       <c r="Q150">
         <v>34125490302</v>
       </c>
-      <c r="R150" s="3" t="str">
+      <c r="R150" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1c|B2b|C1b</v>
       </c>
-      <c r="S150" s="2" t="str">
+      <c r="S150" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>364</v>
       </c>
@@ -12323,16 +12291,16 @@
       <c r="Q151">
         <v>34125587769</v>
       </c>
-      <c r="R151" s="3" t="str">
+      <c r="R151" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1c|B2b|C1c</v>
       </c>
-      <c r="S151" s="2" t="str">
+      <c r="S151" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>366</v>
       </c>
@@ -12384,16 +12352,16 @@
       <c r="Q152">
         <v>34125665545</v>
       </c>
-      <c r="R152" s="3" t="str">
+      <c r="R152" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1c|B2c|C1a</v>
       </c>
-      <c r="S152" s="2" t="str">
+      <c r="S152" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>368</v>
       </c>
@@ -12445,16 +12413,16 @@
       <c r="Q153">
         <v>34125735585</v>
       </c>
-      <c r="R153" s="3" t="str">
+      <c r="R153" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1c|B2c|C1b</v>
       </c>
-      <c r="S153" s="2" t="str">
+      <c r="S153" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>370</v>
       </c>
@@ -12506,16 +12474,16 @@
       <c r="Q154">
         <v>34125834947</v>
       </c>
-      <c r="R154" s="3" t="str">
+      <c r="R154" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1c|B2c|C1c</v>
       </c>
-      <c r="S154" s="2" t="str">
+      <c r="S154" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>372</v>
       </c>
@@ -12561,16 +12529,16 @@
       <c r="Q155">
         <v>34125912614</v>
       </c>
-      <c r="R155" s="3" t="str">
+      <c r="R155" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1d|B2a|C1a</v>
       </c>
-      <c r="S155" s="2" t="str">
+      <c r="S155" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>374</v>
       </c>
@@ -12616,16 +12584,16 @@
       <c r="Q156">
         <v>34125982506</v>
       </c>
-      <c r="R156" s="3" t="str">
+      <c r="R156" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1d|B2a|C1b</v>
       </c>
-      <c r="S156" s="2" t="str">
+      <c r="S156" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>376</v>
       </c>
@@ -12671,16 +12639,16 @@
       <c r="Q157">
         <v>34126048925</v>
       </c>
-      <c r="R157" s="3" t="str">
+      <c r="R157" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1d|B2a|C1c</v>
       </c>
-      <c r="S157" s="2" t="str">
+      <c r="S157" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>378</v>
       </c>
@@ -12732,16 +12700,16 @@
       <c r="Q158">
         <v>34126116473</v>
       </c>
-      <c r="R158" s="3" t="str">
+      <c r="R158" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1d|B2b|C1a</v>
       </c>
-      <c r="S158" s="2" t="str">
+      <c r="S158" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>380</v>
       </c>
@@ -12787,16 +12755,16 @@
       <c r="Q159">
         <v>34126186710</v>
       </c>
-      <c r="R159" s="3" t="str">
+      <c r="R159" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1d|B2b|C1b</v>
       </c>
-      <c r="S159" s="2" t="str">
+      <c r="S159" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>382</v>
       </c>
@@ -12848,16 +12816,16 @@
       <c r="Q160">
         <v>34126254780</v>
       </c>
-      <c r="R160" s="3" t="str">
+      <c r="R160" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1d|B2b|C1c</v>
       </c>
-      <c r="S160" s="2" t="str">
+      <c r="S160" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>384</v>
       </c>
@@ -12909,16 +12877,16 @@
       <c r="Q161">
         <v>34126323126</v>
       </c>
-      <c r="R161" s="3" t="str">
+      <c r="R161" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1d|B2c|C1a</v>
       </c>
-      <c r="S161" s="2" t="str">
+      <c r="S161" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>386</v>
       </c>
@@ -12964,16 +12932,16 @@
       <c r="Q162">
         <v>34126389093</v>
       </c>
-      <c r="R162" s="3" t="str">
+      <c r="R162" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1d|B2c|C1b</v>
       </c>
-      <c r="S162" s="2" t="str">
+      <c r="S162" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>388</v>
       </c>
@@ -13025,16 +12993,16 @@
       <c r="Q163">
         <v>34126452474</v>
       </c>
-      <c r="R163" s="3" t="str">
+      <c r="R163" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A1b|B1d|B2c|C1c</v>
       </c>
-      <c r="S163" s="2" t="str">
+      <c r="S163" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>390</v>
       </c>
@@ -13080,16 +13048,16 @@
       <c r="Q164">
         <v>34126518002</v>
       </c>
-      <c r="R164" s="3" t="str">
+      <c r="R164" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1a|B2a|C1a</v>
       </c>
-      <c r="S164" s="2" t="str">
+      <c r="S164" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>392</v>
       </c>
@@ -13135,16 +13103,16 @@
       <c r="Q165">
         <v>34126583112</v>
       </c>
-      <c r="R165" s="3" t="str">
+      <c r="R165" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1a|B2a|C1b</v>
       </c>
-      <c r="S165" s="2" t="str">
+      <c r="S165" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>394</v>
       </c>
@@ -13190,16 +13158,16 @@
       <c r="Q166">
         <v>34126649079</v>
       </c>
-      <c r="R166" s="3" t="str">
+      <c r="R166" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1a|B2a|C1c</v>
       </c>
-      <c r="S166" s="2" t="str">
+      <c r="S166" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>396</v>
       </c>
@@ -13245,16 +13213,16 @@
       <c r="Q167">
         <v>34126713869</v>
       </c>
-      <c r="R167" s="3" t="str">
+      <c r="R167" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1a|B2b|C1a</v>
       </c>
-      <c r="S167" s="2" t="str">
+      <c r="S167" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>398</v>
       </c>
@@ -13300,16 +13268,16 @@
       <c r="Q168">
         <v>34126780015</v>
       </c>
-      <c r="R168" s="3" t="str">
+      <c r="R168" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1a|B2b|C1b</v>
       </c>
-      <c r="S168" s="2" t="str">
+      <c r="S168" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>400</v>
       </c>
@@ -13355,16 +13323,16 @@
       <c r="Q169">
         <v>34126848447</v>
       </c>
-      <c r="R169" s="3" t="str">
+      <c r="R169" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1a|B2b|C1c</v>
       </c>
-      <c r="S169" s="2" t="str">
+      <c r="S169" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>402</v>
       </c>
@@ -13410,16 +13378,16 @@
       <c r="Q170">
         <v>34126914018</v>
       </c>
-      <c r="R170" s="3" t="str">
+      <c r="R170" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1a|B2c|C1a</v>
       </c>
-      <c r="S170" s="2" t="str">
+      <c r="S170" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>404</v>
       </c>
@@ -13465,16 +13433,16 @@
       <c r="Q171">
         <v>34126978469</v>
       </c>
-      <c r="R171" s="3" t="str">
+      <c r="R171" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1a|B2c|C1b</v>
       </c>
-      <c r="S171" s="2" t="str">
+      <c r="S171" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>406</v>
       </c>
@@ -13520,16 +13488,16 @@
       <c r="Q172">
         <v>34127041123</v>
       </c>
-      <c r="R172" s="3" t="str">
+      <c r="R172" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1a|B2c|C1c</v>
       </c>
-      <c r="S172" s="2" t="str">
+      <c r="S172" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>408</v>
       </c>
@@ -13581,16 +13549,16 @@
       <c r="Q173">
         <v>34127106311</v>
       </c>
-      <c r="R173" s="3" t="str">
+      <c r="R173" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1b|B2a|C1a</v>
       </c>
-      <c r="S173" s="2" t="str">
+      <c r="S173" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>412</v>
       </c>
@@ -13642,16 +13610,16 @@
       <c r="Q174">
         <v>34127173091</v>
       </c>
-      <c r="R174" s="3" t="str">
+      <c r="R174" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1b|B2a|C1b</v>
       </c>
-      <c r="S174" s="2" t="str">
+      <c r="S174" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>414</v>
       </c>
@@ -13703,16 +13671,16 @@
       <c r="Q175">
         <v>34127251988</v>
       </c>
-      <c r="R175" s="3" t="str">
+      <c r="R175" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1b|B2a|C1c</v>
       </c>
-      <c r="S175" s="2" t="str">
+      <c r="S175" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>416</v>
       </c>
@@ -13764,16 +13732,16 @@
       <c r="Q176">
         <v>34127327573</v>
       </c>
-      <c r="R176" s="3" t="str">
+      <c r="R176" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1b|B2b|C1a</v>
       </c>
-      <c r="S176" s="2" t="str">
+      <c r="S176" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>418</v>
       </c>
@@ -13825,16 +13793,16 @@
       <c r="Q177">
         <v>34127394499</v>
       </c>
-      <c r="R177" s="3" t="str">
+      <c r="R177" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1b|B2b|C1b</v>
       </c>
-      <c r="S177" s="2" t="str">
+      <c r="S177" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>420</v>
       </c>
@@ -13886,16 +13854,16 @@
       <c r="Q178">
         <v>34127472578</v>
       </c>
-      <c r="R178" s="3" t="str">
+      <c r="R178" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1b|B2b|C1c</v>
       </c>
-      <c r="S178" s="2" t="str">
+      <c r="S178" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>422</v>
       </c>
@@ -13947,16 +13915,16 @@
       <c r="Q179">
         <v>34127545774</v>
       </c>
-      <c r="R179" s="3" t="str">
+      <c r="R179" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1b|B2c|C1a</v>
       </c>
-      <c r="S179" s="2" t="str">
+      <c r="S179" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>424</v>
       </c>
@@ -14008,16 +13976,16 @@
       <c r="Q180">
         <v>34127611317</v>
       </c>
-      <c r="R180" s="3" t="str">
+      <c r="R180" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1b|B2c|C1b</v>
       </c>
-      <c r="S180" s="2" t="str">
+      <c r="S180" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>426</v>
       </c>
@@ -14069,16 +14037,16 @@
       <c r="Q181">
         <v>34127696363</v>
       </c>
-      <c r="R181" s="3" t="str">
+      <c r="R181" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1b|B2c|C1c</v>
       </c>
-      <c r="S181" s="2" t="str">
+      <c r="S181" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>428</v>
       </c>
@@ -14130,16 +14098,16 @@
       <c r="Q182">
         <v>34127777719</v>
       </c>
-      <c r="R182" s="3" t="str">
+      <c r="R182" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1c|B2a|C1a</v>
       </c>
-      <c r="S182" s="2" t="str">
+      <c r="S182" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>430</v>
       </c>
@@ -14191,16 +14159,16 @@
       <c r="Q183">
         <v>34127862738</v>
       </c>
-      <c r="R183" s="3" t="str">
+      <c r="R183" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1c|B2a|C1b</v>
       </c>
-      <c r="S183" s="2" t="str">
+      <c r="S183" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>432</v>
       </c>
@@ -14252,16 +14220,16 @@
       <c r="Q184">
         <v>34127957834</v>
       </c>
-      <c r="R184" s="3" t="str">
+      <c r="R184" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1c|B2a|C1c</v>
       </c>
-      <c r="S184" s="2" t="str">
+      <c r="S184" t="str">
         <f t="shared" si="6"/>
         <v>P</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>434</v>
       </c>
@@ -14313,16 +14281,16 @@
       <c r="Q185">
         <v>34128043255</v>
       </c>
-      <c r="R185" s="3" t="str">
+      <c r="R185" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1c|B2b|C1a</v>
       </c>
-      <c r="S185" s="2" t="str">
+      <c r="S185" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>436</v>
       </c>
@@ -14374,16 +14342,16 @@
       <c r="Q186">
         <v>34128125622</v>
       </c>
-      <c r="R186" s="3" t="str">
+      <c r="R186" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1c|B2b|C1b</v>
       </c>
-      <c r="S186" s="2" t="str">
+      <c r="S186" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>438</v>
       </c>
@@ -14435,16 +14403,16 @@
       <c r="Q187">
         <v>34128252040</v>
       </c>
-      <c r="R187" s="3" t="str">
+      <c r="R187" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1c|B2b|C1c</v>
       </c>
-      <c r="S187" s="2" t="str">
+      <c r="S187" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>440</v>
       </c>
@@ -14496,16 +14464,16 @@
       <c r="Q188">
         <v>34128336811</v>
       </c>
-      <c r="R188" s="3" t="str">
+      <c r="R188" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1c|B2c|C1a</v>
       </c>
-      <c r="S188" s="2" t="str">
+      <c r="S188" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>442</v>
       </c>
@@ -14557,16 +14525,16 @@
       <c r="Q189">
         <v>34128408528</v>
       </c>
-      <c r="R189" s="3" t="str">
+      <c r="R189" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1c|B2c|C1b</v>
       </c>
-      <c r="S189" s="2" t="str">
+      <c r="S189" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>444</v>
       </c>
@@ -14618,16 +14586,16 @@
       <c r="Q190">
         <v>34128496081</v>
       </c>
-      <c r="R190" s="3" t="str">
+      <c r="R190" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1c|B2c|C1c</v>
       </c>
-      <c r="S190" s="2" t="str">
+      <c r="S190" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>446</v>
       </c>
@@ -14673,16 +14641,16 @@
       <c r="Q191">
         <v>34128569731</v>
       </c>
-      <c r="R191" s="3" t="str">
+      <c r="R191" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1d|B2a|C1a</v>
       </c>
-      <c r="S191" s="2" t="str">
+      <c r="S191" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>448</v>
       </c>
@@ -14728,16 +14696,16 @@
       <c r="Q192">
         <v>34128637602</v>
       </c>
-      <c r="R192" s="3" t="str">
+      <c r="R192" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1d|B2a|C1b</v>
       </c>
-      <c r="S192" s="2" t="str">
+      <c r="S192" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>450</v>
       </c>
@@ -14783,16 +14751,16 @@
       <c r="Q193">
         <v>34128710753</v>
       </c>
-      <c r="R193" s="3" t="str">
+      <c r="R193" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1d|B2a|C1c</v>
       </c>
-      <c r="S193" s="2" t="str">
+      <c r="S193" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>452</v>
       </c>
@@ -14844,16 +14812,16 @@
       <c r="Q194">
         <v>34128788107</v>
       </c>
-      <c r="R194" s="3" t="str">
+      <c r="R194" s="2" t="str">
         <f t="shared" si="5"/>
         <v>python|A2|B1d|B2b|C1a</v>
       </c>
-      <c r="S194" s="2" t="str">
+      <c r="S194" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>454</v>
       </c>
@@ -14899,16 +14867,16 @@
       <c r="Q195">
         <v>34128867008</v>
       </c>
-      <c r="R195" s="3" t="str">
+      <c r="R195" s="2" t="str">
         <f t="shared" ref="R195:R258" si="7">C195&amp;"|"&amp;D195&amp;"|"&amp;E195&amp;"|"&amp;F195&amp;"|"&amp;G195</f>
         <v>python|A2|B1d|B2b|C1b</v>
       </c>
-      <c r="S195" s="2" t="str">
+      <c r="S195" t="str">
         <f t="shared" ref="S195:S258" si="8">IF(H195="malicious_resolved","M",IF(H195="private_resolved","P",IF(H195="resolution_error","E","-")))</f>
         <v>E</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>456</v>
       </c>
@@ -14960,16 +14928,16 @@
       <c r="Q196">
         <v>34128938438</v>
       </c>
-      <c r="R196" s="3" t="str">
+      <c r="R196" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A2|B1d|B2b|C1c</v>
       </c>
-      <c r="S196" s="2" t="str">
+      <c r="S196" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>458</v>
       </c>
@@ -15021,16 +14989,16 @@
       <c r="Q197">
         <v>34129016026</v>
       </c>
-      <c r="R197" s="3" t="str">
+      <c r="R197" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A2|B1d|B2c|C1a</v>
       </c>
-      <c r="S197" s="2" t="str">
+      <c r="S197" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>460</v>
       </c>
@@ -15076,16 +15044,16 @@
       <c r="Q198">
         <v>34129090181</v>
       </c>
-      <c r="R198" s="3" t="str">
+      <c r="R198" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A2|B1d|B2c|C1b</v>
       </c>
-      <c r="S198" s="2" t="str">
+      <c r="S198" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>462</v>
       </c>
@@ -15137,16 +15105,16 @@
       <c r="Q199">
         <v>34129162109</v>
       </c>
-      <c r="R199" s="3" t="str">
+      <c r="R199" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A2|B1d|B2c|C1c</v>
       </c>
-      <c r="S199" s="2" t="str">
+      <c r="S199" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>464</v>
       </c>
@@ -15192,16 +15160,16 @@
       <c r="Q200">
         <v>34129240078</v>
       </c>
-      <c r="R200" s="3" t="str">
+      <c r="R200" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1a|B2a|C1a</v>
       </c>
-      <c r="S200" s="2" t="str">
+      <c r="S200" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>466</v>
       </c>
@@ -15247,16 +15215,16 @@
       <c r="Q201">
         <v>34129306949</v>
       </c>
-      <c r="R201" s="3" t="str">
+      <c r="R201" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1a|B2a|C1b</v>
       </c>
-      <c r="S201" s="2" t="str">
+      <c r="S201" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>468</v>
       </c>
@@ -15302,16 +15270,16 @@
       <c r="Q202">
         <v>34129369585</v>
       </c>
-      <c r="R202" s="3" t="str">
+      <c r="R202" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1a|B2a|C1c</v>
       </c>
-      <c r="S202" s="2" t="str">
+      <c r="S202" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>470</v>
       </c>
@@ -15357,16 +15325,16 @@
       <c r="Q203">
         <v>34129435551</v>
       </c>
-      <c r="R203" s="3" t="str">
+      <c r="R203" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1a|B2b|C1a</v>
       </c>
-      <c r="S203" s="2" t="str">
+      <c r="S203" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>472</v>
       </c>
@@ -15412,16 +15380,16 @@
       <c r="Q204">
         <v>34129498739</v>
       </c>
-      <c r="R204" s="3" t="str">
+      <c r="R204" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1a|B2b|C1b</v>
       </c>
-      <c r="S204" s="2" t="str">
+      <c r="S204" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>474</v>
       </c>
@@ -15467,16 +15435,16 @@
       <c r="Q205">
         <v>34129557934</v>
       </c>
-      <c r="R205" s="3" t="str">
+      <c r="R205" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1a|B2b|C1c</v>
       </c>
-      <c r="S205" s="2" t="str">
+      <c r="S205" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>476</v>
       </c>
@@ -15522,16 +15490,16 @@
       <c r="Q206">
         <v>34129621360</v>
       </c>
-      <c r="R206" s="3" t="str">
+      <c r="R206" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1a|B2c|C1a</v>
       </c>
-      <c r="S206" s="2" t="str">
+      <c r="S206" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>478</v>
       </c>
@@ -15577,16 +15545,16 @@
       <c r="Q207">
         <v>34129676402</v>
       </c>
-      <c r="R207" s="3" t="str">
+      <c r="R207" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1a|B2c|C1b</v>
       </c>
-      <c r="S207" s="2" t="str">
+      <c r="S207" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>480</v>
       </c>
@@ -15632,16 +15600,16 @@
       <c r="Q208">
         <v>34129727046</v>
       </c>
-      <c r="R208" s="3" t="str">
+      <c r="R208" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1a|B2c|C1c</v>
       </c>
-      <c r="S208" s="2" t="str">
+      <c r="S208" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>482</v>
       </c>
@@ -15693,16 +15661,16 @@
       <c r="Q209">
         <v>34129787012</v>
       </c>
-      <c r="R209" s="3" t="str">
+      <c r="R209" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1b|B2a|C1a</v>
       </c>
-      <c r="S209" s="2" t="str">
+      <c r="S209" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>484</v>
       </c>
@@ -15754,16 +15722,16 @@
       <c r="Q210">
         <v>34129863419</v>
       </c>
-      <c r="R210" s="3" t="str">
+      <c r="R210" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1b|B2a|C1b</v>
       </c>
-      <c r="S210" s="2" t="str">
+      <c r="S210" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>486</v>
       </c>
@@ -15815,16 +15783,16 @@
       <c r="Q211">
         <v>34129942736</v>
       </c>
-      <c r="R211" s="3" t="str">
+      <c r="R211" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1b|B2a|C1c</v>
       </c>
-      <c r="S211" s="2" t="str">
+      <c r="S211" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>488</v>
       </c>
@@ -15876,16 +15844,16 @@
       <c r="Q212">
         <v>34130021084</v>
       </c>
-      <c r="R212" s="3" t="str">
+      <c r="R212" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1b|B2b|C1a</v>
       </c>
-      <c r="S212" s="2" t="str">
+      <c r="S212" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>490</v>
       </c>
@@ -15937,16 +15905,16 @@
       <c r="Q213">
         <v>34130088849</v>
       </c>
-      <c r="R213" s="3" t="str">
+      <c r="R213" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1b|B2b|C1b</v>
       </c>
-      <c r="S213" s="2" t="str">
+      <c r="S213" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>492</v>
       </c>
@@ -15998,16 +15966,16 @@
       <c r="Q214">
         <v>34130167179</v>
       </c>
-      <c r="R214" s="3" t="str">
+      <c r="R214" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1b|B2b|C1c</v>
       </c>
-      <c r="S214" s="2" t="str">
+      <c r="S214" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>494</v>
       </c>
@@ -16059,16 +16027,16 @@
       <c r="Q215">
         <v>34130233324</v>
       </c>
-      <c r="R215" s="3" t="str">
+      <c r="R215" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1b|B2c|C1a</v>
       </c>
-      <c r="S215" s="2" t="str">
+      <c r="S215" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>496</v>
       </c>
@@ -16120,16 +16088,16 @@
       <c r="Q216">
         <v>34130296847</v>
       </c>
-      <c r="R216" s="3" t="str">
+      <c r="R216" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1b|B2c|C1b</v>
       </c>
-      <c r="S216" s="2" t="str">
+      <c r="S216" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>498</v>
       </c>
@@ -16181,16 +16149,16 @@
       <c r="Q217">
         <v>34130371308</v>
       </c>
-      <c r="R217" s="3" t="str">
+      <c r="R217" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1b|B2c|C1c</v>
       </c>
-      <c r="S217" s="2" t="str">
+      <c r="S217" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>500</v>
       </c>
@@ -16236,16 +16204,16 @@
       <c r="Q218">
         <v>34130434748</v>
       </c>
-      <c r="R218" s="3" t="str">
+      <c r="R218" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1d|B2a|C1a</v>
       </c>
-      <c r="S218" s="2" t="str">
+      <c r="S218" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>502</v>
       </c>
@@ -16291,16 +16259,16 @@
       <c r="Q219">
         <v>34130489947</v>
       </c>
-      <c r="R219" s="3" t="str">
+      <c r="R219" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1d|B2a|C1b</v>
       </c>
-      <c r="S219" s="2" t="str">
+      <c r="S219" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>504</v>
       </c>
@@ -16346,16 +16314,16 @@
       <c r="Q220">
         <v>34130556830</v>
       </c>
-      <c r="R220" s="3" t="str">
+      <c r="R220" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1d|B2a|C1c</v>
       </c>
-      <c r="S220" s="2" t="str">
+      <c r="S220" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>506</v>
       </c>
@@ -16407,16 +16375,16 @@
       <c r="Q221">
         <v>34130620184</v>
       </c>
-      <c r="R221" s="3" t="str">
+      <c r="R221" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1d|B2b|C1a</v>
       </c>
-      <c r="S221" s="2" t="str">
+      <c r="S221" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>508</v>
       </c>
@@ -16462,16 +16430,16 @@
       <c r="Q222">
         <v>34130688734</v>
       </c>
-      <c r="R222" s="3" t="str">
+      <c r="R222" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1d|B2b|C1b</v>
       </c>
-      <c r="S222" s="2" t="str">
+      <c r="S222" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>510</v>
       </c>
@@ -16523,16 +16491,16 @@
       <c r="Q223">
         <v>34130758540</v>
       </c>
-      <c r="R223" s="3" t="str">
+      <c r="R223" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1d|B2b|C1c</v>
       </c>
-      <c r="S223" s="2" t="str">
+      <c r="S223" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>512</v>
       </c>
@@ -16584,16 +16552,16 @@
       <c r="Q224">
         <v>34130835387</v>
       </c>
-      <c r="R224" s="3" t="str">
+      <c r="R224" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1d|B2c|C1a</v>
       </c>
-      <c r="S224" s="2" t="str">
+      <c r="S224" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>514</v>
       </c>
@@ -16639,16 +16607,16 @@
       <c r="Q225">
         <v>34130904085</v>
       </c>
-      <c r="R225" s="3" t="str">
+      <c r="R225" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1d|B2c|C1b</v>
       </c>
-      <c r="S225" s="2" t="str">
+      <c r="S225" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>516</v>
       </c>
@@ -16700,16 +16668,16 @@
       <c r="Q226">
         <v>34130972245</v>
       </c>
-      <c r="R226" s="3" t="str">
+      <c r="R226" s="2" t="str">
         <f t="shared" si="7"/>
         <v>python|A3|B1d|B2c|C1c</v>
       </c>
-      <c r="S226" s="2" t="str">
+      <c r="S226" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>518</v>
       </c>
@@ -16761,16 +16729,16 @@
       <c r="Q227">
         <v>34131050358</v>
       </c>
-      <c r="R227" s="3" t="str">
+      <c r="R227" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1a|B2a|C1a</v>
       </c>
-      <c r="S227" s="2" t="str">
+      <c r="S227" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>525</v>
       </c>
@@ -16822,16 +16790,16 @@
       <c r="Q228">
         <v>34131325556</v>
       </c>
-      <c r="R228" s="3" t="str">
+      <c r="R228" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1a|B2a|C1b</v>
       </c>
-      <c r="S228" s="2" t="str">
+      <c r="S228" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>527</v>
       </c>
@@ -16883,11 +16851,11 @@
       <c r="Q229">
         <v>34131718099</v>
       </c>
-      <c r="R229" s="3" t="str">
+      <c r="R229" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1a|B2a|C1c</v>
       </c>
-      <c r="S229" s="2" t="str">
+      <c r="S229" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
@@ -16944,11 +16912,11 @@
       <c r="Q230">
         <v>34132033077</v>
       </c>
-      <c r="R230" s="3" t="str">
+      <c r="R230" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1a|B2b|C1a</v>
       </c>
-      <c r="S230" s="2" t="str">
+      <c r="S230" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
@@ -17005,11 +16973,11 @@
       <c r="Q231">
         <v>34132275385</v>
       </c>
-      <c r="R231" s="3" t="str">
+      <c r="R231" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1a|B2b|C1b</v>
       </c>
-      <c r="S231" s="2" t="str">
+      <c r="S231" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
@@ -17066,16 +17034,16 @@
       <c r="Q232">
         <v>34132694817</v>
       </c>
-      <c r="R232" s="3" t="str">
+      <c r="R232" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1a|B2b|C1c</v>
       </c>
-      <c r="S232" s="2" t="str">
+      <c r="S232" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>537</v>
       </c>
@@ -17127,16 +17095,16 @@
       <c r="Q233">
         <v>34133073188</v>
       </c>
-      <c r="R233" s="3" t="str">
+      <c r="R233" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1b|B2a|C1a</v>
       </c>
-      <c r="S233" s="2" t="str">
+      <c r="S233" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>539</v>
       </c>
@@ -17188,16 +17156,16 @@
       <c r="Q234">
         <v>34133320788</v>
       </c>
-      <c r="R234" s="3" t="str">
+      <c r="R234" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1b|B2a|C1b</v>
       </c>
-      <c r="S234" s="2" t="str">
+      <c r="S234" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>541</v>
       </c>
@@ -17249,16 +17217,16 @@
       <c r="Q235">
         <v>34133664190</v>
       </c>
-      <c r="R235" s="3" t="str">
+      <c r="R235" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1b|B2a|C1c</v>
       </c>
-      <c r="S235" s="2" t="str">
+      <c r="S235" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>543</v>
       </c>
@@ -17310,16 +17278,16 @@
       <c r="Q236">
         <v>34134043751</v>
       </c>
-      <c r="R236" s="3" t="str">
+      <c r="R236" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1b|B2b|C1a</v>
       </c>
-      <c r="S236" s="2" t="str">
+      <c r="S236" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>547</v>
       </c>
@@ -17371,16 +17339,16 @@
       <c r="Q237">
         <v>34134187456</v>
       </c>
-      <c r="R237" s="3" t="str">
+      <c r="R237" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1b|B2b|C1b</v>
       </c>
-      <c r="S237" s="2" t="str">
+      <c r="S237" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>549</v>
       </c>
@@ -17432,16 +17400,16 @@
       <c r="Q238">
         <v>34134372303</v>
       </c>
-      <c r="R238" s="3" t="str">
+      <c r="R238" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1b|B2b|C1c</v>
       </c>
-      <c r="S238" s="2" t="str">
+      <c r="S238" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>551</v>
       </c>
@@ -17493,16 +17461,16 @@
       <c r="Q239">
         <v>34134566471</v>
       </c>
-      <c r="R239" s="3" t="str">
+      <c r="R239" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1c|B2a|C1a</v>
       </c>
-      <c r="S239" s="2" t="str">
+      <c r="S239" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>553</v>
       </c>
@@ -17554,16 +17522,16 @@
       <c r="Q240">
         <v>34134726829</v>
       </c>
-      <c r="R240" s="3" t="str">
+      <c r="R240" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1c|B2a|C1b</v>
       </c>
-      <c r="S240" s="2" t="str">
+      <c r="S240" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>555</v>
       </c>
@@ -17615,16 +17583,16 @@
       <c r="Q241">
         <v>34134931903</v>
       </c>
-      <c r="R241" s="3" t="str">
+      <c r="R241" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1c|B2a|C1c</v>
       </c>
-      <c r="S241" s="2" t="str">
+      <c r="S241" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>557</v>
       </c>
@@ -17676,16 +17644,16 @@
       <c r="Q242">
         <v>34135110660</v>
       </c>
-      <c r="R242" s="3" t="str">
+      <c r="R242" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1c|B2b|C1a</v>
       </c>
-      <c r="S242" s="2" t="str">
+      <c r="S242" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>561</v>
       </c>
@@ -17737,16 +17705,16 @@
       <c r="Q243">
         <v>34135266760</v>
       </c>
-      <c r="R243" s="3" t="str">
+      <c r="R243" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1c|B2b|C1b</v>
       </c>
-      <c r="S243" s="2" t="str">
+      <c r="S243" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>563</v>
       </c>
@@ -17798,16 +17766,16 @@
       <c r="Q244">
         <v>34135418412</v>
       </c>
-      <c r="R244" s="3" t="str">
+      <c r="R244" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1c|B2b|C1c</v>
       </c>
-      <c r="S244" s="2" t="str">
+      <c r="S244" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>565</v>
       </c>
@@ -17853,16 +17821,16 @@
       <c r="Q245">
         <v>34135580883</v>
       </c>
-      <c r="R245" s="3" t="str">
+      <c r="R245" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1d|B2a|C1a</v>
       </c>
-      <c r="S245" s="2" t="str">
+      <c r="S245" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>567</v>
       </c>
@@ -17914,16 +17882,16 @@
       <c r="Q246">
         <v>34135640130</v>
       </c>
-      <c r="R246" s="3" t="str">
+      <c r="R246" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1d|B2a|C1b</v>
       </c>
-      <c r="S246" s="2" t="str">
+      <c r="S246" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>569</v>
       </c>
@@ -17969,16 +17937,16 @@
       <c r="Q247">
         <v>34135799227</v>
       </c>
-      <c r="R247" s="3" t="str">
+      <c r="R247" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1d|B2a|C1c</v>
       </c>
-      <c r="S247" s="2" t="str">
+      <c r="S247" t="str">
         <f t="shared" si="8"/>
         <v>E</v>
       </c>
     </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>571</v>
       </c>
@@ -18030,16 +17998,16 @@
       <c r="Q248">
         <v>34135865443</v>
       </c>
-      <c r="R248" s="3" t="str">
+      <c r="R248" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1d|B2b|C1a</v>
       </c>
-      <c r="S248" s="2" t="str">
+      <c r="S248" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>573</v>
       </c>
@@ -18091,16 +18059,16 @@
       <c r="Q249">
         <v>34136015042</v>
       </c>
-      <c r="R249" s="3" t="str">
+      <c r="R249" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1d|B2b|C1b</v>
       </c>
-      <c r="S249" s="2" t="str">
+      <c r="S249" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>575</v>
       </c>
@@ -18152,16 +18120,16 @@
       <c r="Q250">
         <v>34136168264</v>
       </c>
-      <c r="R250" s="3" t="str">
+      <c r="R250" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1a|B1d|B2b|C1c</v>
       </c>
-      <c r="S250" s="2" t="str">
+      <c r="S250" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>577</v>
       </c>
@@ -18213,16 +18181,16 @@
       <c r="Q251">
         <v>34136339070</v>
       </c>
-      <c r="R251" s="3" t="str">
+      <c r="R251" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1b|B1a|B2a|C1a</v>
       </c>
-      <c r="S251" s="2" t="str">
+      <c r="S251" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>581</v>
       </c>
@@ -18274,16 +18242,16 @@
       <c r="Q252">
         <v>34136502603</v>
       </c>
-      <c r="R252" s="3" t="str">
+      <c r="R252" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1b|B1a|B2a|C1b</v>
       </c>
-      <c r="S252" s="2" t="str">
+      <c r="S252" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>583</v>
       </c>
@@ -18335,11 +18303,11 @@
       <c r="Q253">
         <v>34136666649</v>
       </c>
-      <c r="R253" s="3" t="str">
+      <c r="R253" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1b|B1a|B2a|C1c</v>
       </c>
-      <c r="S253" s="2" t="str">
+      <c r="S253" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
@@ -18396,11 +18364,11 @@
       <c r="Q254">
         <v>34136893636</v>
       </c>
-      <c r="R254" s="3" t="str">
+      <c r="R254" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1b|B1a|B2b|C1a</v>
       </c>
-      <c r="S254" s="2" t="str">
+      <c r="S254" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
@@ -18457,11 +18425,11 @@
       <c r="Q255">
         <v>34137164810</v>
       </c>
-      <c r="R255" s="3" t="str">
+      <c r="R255" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1b|B1a|B2b|C1b</v>
       </c>
-      <c r="S255" s="2" t="str">
+      <c r="S255" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
@@ -18518,16 +18486,16 @@
       <c r="Q256">
         <v>34137462716</v>
       </c>
-      <c r="R256" s="3" t="str">
+      <c r="R256" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1b|B1a|B2b|C1c</v>
       </c>
-      <c r="S256" s="2" t="str">
+      <c r="S256" t="str">
         <f t="shared" si="8"/>
         <v>M</v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>593</v>
       </c>
@@ -18579,16 +18547,16 @@
       <c r="Q257">
         <v>34137813273</v>
       </c>
-      <c r="R257" s="3" t="str">
+      <c r="R257" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1b|B1b|B2a|C1a</v>
       </c>
-      <c r="S257" s="2" t="str">
+      <c r="S257" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>595</v>
       </c>
@@ -18640,16 +18608,16 @@
       <c r="Q258">
         <v>34138121078</v>
       </c>
-      <c r="R258" s="3" t="str">
+      <c r="R258" s="2" t="str">
         <f t="shared" si="7"/>
         <v>java|A1b|B1b|B2a|C1b</v>
       </c>
-      <c r="S258" s="2" t="str">
+      <c r="S258" t="str">
         <f t="shared" si="8"/>
         <v>P</v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>597</v>
       </c>
@@ -18701,16 +18669,16 @@
       <c r="Q259">
         <v>34138446277</v>
       </c>
-      <c r="R259" s="3" t="str">
+      <c r="R259" s="2" t="str">
         <f t="shared" ref="R259:R322" si="9">C259&amp;"|"&amp;D259&amp;"|"&amp;E259&amp;"|"&amp;F259&amp;"|"&amp;G259</f>
         <v>java|A1b|B1b|B2a|C1c</v>
       </c>
-      <c r="S259" s="2" t="str">
+      <c r="S259" t="str">
         <f t="shared" ref="S259:S322" si="10">IF(H259="malicious_resolved","M",IF(H259="private_resolved","P",IF(H259="resolution_error","E","-")))</f>
         <v>P</v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>599</v>
       </c>
@@ -18762,16 +18730,16 @@
       <c r="Q260">
         <v>34138749414</v>
       </c>
-      <c r="R260" s="3" t="str">
+      <c r="R260" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1b|B2b|C1a</v>
       </c>
-      <c r="S260" s="2" t="str">
+      <c r="S260" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>601</v>
       </c>
@@ -18823,16 +18791,16 @@
       <c r="Q261">
         <v>34138973408</v>
       </c>
-      <c r="R261" s="3" t="str">
+      <c r="R261" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1b|B2b|C1b</v>
       </c>
-      <c r="S261" s="2" t="str">
+      <c r="S261" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>603</v>
       </c>
@@ -18884,16 +18852,16 @@
       <c r="Q262">
         <v>34139220418</v>
       </c>
-      <c r="R262" s="3" t="str">
+      <c r="R262" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1b|B2b|C1c</v>
       </c>
-      <c r="S262" s="2" t="str">
+      <c r="S262" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>605</v>
       </c>
@@ -18945,16 +18913,16 @@
       <c r="Q263">
         <v>34139490870</v>
       </c>
-      <c r="R263" s="3" t="str">
+      <c r="R263" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1c|B2a|C1a</v>
       </c>
-      <c r="S263" s="2" t="str">
+      <c r="S263" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>607</v>
       </c>
@@ -19006,16 +18974,16 @@
       <c r="Q264">
         <v>34139841001</v>
       </c>
-      <c r="R264" s="3" t="str">
+      <c r="R264" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1c|B2a|C1b</v>
       </c>
-      <c r="S264" s="2" t="str">
+      <c r="S264" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>609</v>
       </c>
@@ -19067,16 +19035,16 @@
       <c r="Q265">
         <v>34140117606</v>
       </c>
-      <c r="R265" s="3" t="str">
+      <c r="R265" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1c|B2a|C1c</v>
       </c>
-      <c r="S265" s="2" t="str">
+      <c r="S265" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>611</v>
       </c>
@@ -19128,16 +19096,16 @@
       <c r="Q266">
         <v>34140391303</v>
       </c>
-      <c r="R266" s="3" t="str">
+      <c r="R266" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1c|B2b|C1a</v>
       </c>
-      <c r="S266" s="2" t="str">
+      <c r="S266" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>613</v>
       </c>
@@ -19189,16 +19157,16 @@
       <c r="Q267">
         <v>34140607444</v>
       </c>
-      <c r="R267" s="3" t="str">
+      <c r="R267" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1c|B2b|C1b</v>
       </c>
-      <c r="S267" s="2" t="str">
+      <c r="S267" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>615</v>
       </c>
@@ -19250,16 +19218,16 @@
       <c r="Q268">
         <v>34140750490</v>
       </c>
-      <c r="R268" s="3" t="str">
+      <c r="R268" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1c|B2b|C1c</v>
       </c>
-      <c r="S268" s="2" t="str">
+      <c r="S268" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>617</v>
       </c>
@@ -19305,16 +19273,16 @@
       <c r="Q269">
         <v>34140971217</v>
       </c>
-      <c r="R269" s="3" t="str">
+      <c r="R269" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1d|B2a|C1a</v>
       </c>
-      <c r="S269" s="2" t="str">
+      <c r="S269" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>619</v>
       </c>
@@ -19366,16 +19334,16 @@
       <c r="Q270">
         <v>34141026105</v>
       </c>
-      <c r="R270" s="3" t="str">
+      <c r="R270" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1d|B2a|C1b</v>
       </c>
-      <c r="S270" s="2" t="str">
+      <c r="S270" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>621</v>
       </c>
@@ -19421,16 +19389,16 @@
       <c r="Q271">
         <v>34141175264</v>
       </c>
-      <c r="R271" s="3" t="str">
+      <c r="R271" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1d|B2a|C1c</v>
       </c>
-      <c r="S271" s="2" t="str">
+      <c r="S271" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>623</v>
       </c>
@@ -19482,16 +19450,16 @@
       <c r="Q272">
         <v>34141235179</v>
       </c>
-      <c r="R272" s="3" t="str">
+      <c r="R272" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1d|B2b|C1a</v>
       </c>
-      <c r="S272" s="2" t="str">
+      <c r="S272" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>625</v>
       </c>
@@ -19543,16 +19511,16 @@
       <c r="Q273">
         <v>34141372199</v>
       </c>
-      <c r="R273" s="3" t="str">
+      <c r="R273" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1d|B2b|C1b</v>
       </c>
-      <c r="S273" s="2" t="str">
+      <c r="S273" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>627</v>
       </c>
@@ -19604,16 +19572,16 @@
       <c r="Q274">
         <v>34141550249</v>
       </c>
-      <c r="R274" s="3" t="str">
+      <c r="R274" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A1b|B1d|B2b|C1c</v>
       </c>
-      <c r="S274" s="2" t="str">
+      <c r="S274" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>629</v>
       </c>
@@ -19659,16 +19627,16 @@
       <c r="Q275">
         <v>34141699881</v>
       </c>
-      <c r="R275" s="3" t="str">
+      <c r="R275" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1a|B2a|C1a</v>
       </c>
-      <c r="S275" s="2" t="str">
+      <c r="S275" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>631</v>
       </c>
@@ -19720,16 +19688,16 @@
       <c r="Q276">
         <v>34141751890</v>
       </c>
-      <c r="R276" s="3" t="str">
+      <c r="R276" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1a|B2a|C1b</v>
       </c>
-      <c r="S276" s="2" t="str">
+      <c r="S276" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>635</v>
       </c>
@@ -19775,16 +19743,16 @@
       <c r="Q277">
         <v>34141886111</v>
       </c>
-      <c r="R277" s="3" t="str">
+      <c r="R277" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1a|B2a|C1c</v>
       </c>
-      <c r="S277" s="2" t="str">
+      <c r="S277" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>637</v>
       </c>
@@ -19830,16 +19798,16 @@
       <c r="Q278">
         <v>34141942796</v>
       </c>
-      <c r="R278" s="3" t="str">
+      <c r="R278" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1a|B2b|C1a</v>
       </c>
-      <c r="S278" s="2" t="str">
+      <c r="S278" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>639</v>
       </c>
@@ -19891,16 +19859,16 @@
       <c r="Q279">
         <v>34142002899</v>
       </c>
-      <c r="R279" s="3" t="str">
+      <c r="R279" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1a|B2b|C1b</v>
       </c>
-      <c r="S279" s="2" t="str">
+      <c r="S279" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>643</v>
       </c>
@@ -19946,16 +19914,16 @@
       <c r="Q280">
         <v>34142190664</v>
       </c>
-      <c r="R280" s="3" t="str">
+      <c r="R280" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1a|B2b|C1c</v>
       </c>
-      <c r="S280" s="2" t="str">
+      <c r="S280" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>645</v>
       </c>
@@ -20007,16 +19975,16 @@
       <c r="Q281">
         <v>34142242845</v>
       </c>
-      <c r="R281" s="3" t="str">
+      <c r="R281" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1b|B2a|C1a</v>
       </c>
-      <c r="S281" s="2" t="str">
+      <c r="S281" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>647</v>
       </c>
@@ -20068,16 +20036,16 @@
       <c r="Q282">
         <v>34142468113</v>
       </c>
-      <c r="R282" s="3" t="str">
+      <c r="R282" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1b|B2a|C1b</v>
       </c>
-      <c r="S282" s="2" t="str">
+      <c r="S282" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>649</v>
       </c>
@@ -20129,16 +20097,16 @@
       <c r="Q283">
         <v>34142603471</v>
       </c>
-      <c r="R283" s="3" t="str">
+      <c r="R283" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1b|B2a|C1c</v>
       </c>
-      <c r="S283" s="2" t="str">
+      <c r="S283" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>651</v>
       </c>
@@ -20190,16 +20158,16 @@
       <c r="Q284">
         <v>34142771452</v>
       </c>
-      <c r="R284" s="3" t="str">
+      <c r="R284" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1b|B2b|C1a</v>
       </c>
-      <c r="S284" s="2" t="str">
+      <c r="S284" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>653</v>
       </c>
@@ -20251,16 +20219,16 @@
       <c r="Q285">
         <v>34142903313</v>
       </c>
-      <c r="R285" s="3" t="str">
+      <c r="R285" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1b|B2b|C1b</v>
       </c>
-      <c r="S285" s="2" t="str">
+      <c r="S285" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>655</v>
       </c>
@@ -20312,16 +20280,16 @@
       <c r="Q286">
         <v>34143036895</v>
       </c>
-      <c r="R286" s="3" t="str">
+      <c r="R286" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1b|B2b|C1c</v>
       </c>
-      <c r="S286" s="2" t="str">
+      <c r="S286" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>657</v>
       </c>
@@ -20373,16 +20341,16 @@
       <c r="Q287">
         <v>34143178109</v>
       </c>
-      <c r="R287" s="3" t="str">
+      <c r="R287" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1c|B2a|C1a</v>
       </c>
-      <c r="S287" s="2" t="str">
+      <c r="S287" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>659</v>
       </c>
@@ -20434,16 +20402,16 @@
       <c r="Q288">
         <v>34143292418</v>
       </c>
-      <c r="R288" s="3" t="str">
+      <c r="R288" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1c|B2a|C1b</v>
       </c>
-      <c r="S288" s="2" t="str">
+      <c r="S288" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>661</v>
       </c>
@@ -20495,16 +20463,16 @@
       <c r="Q289">
         <v>34143409425</v>
       </c>
-      <c r="R289" s="3" t="str">
+      <c r="R289" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1c|B2a|C1c</v>
       </c>
-      <c r="S289" s="2" t="str">
+      <c r="S289" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>663</v>
       </c>
@@ -20556,16 +20524,16 @@
       <c r="Q290">
         <v>34143548885</v>
       </c>
-      <c r="R290" s="3" t="str">
+      <c r="R290" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1c|B2b|C1a</v>
       </c>
-      <c r="S290" s="2" t="str">
+      <c r="S290" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>665</v>
       </c>
@@ -20617,16 +20585,16 @@
       <c r="Q291">
         <v>34143663393</v>
       </c>
-      <c r="R291" s="3" t="str">
+      <c r="R291" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1c|B2b|C1b</v>
       </c>
-      <c r="S291" s="2" t="str">
+      <c r="S291" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>667</v>
       </c>
@@ -20678,16 +20646,16 @@
       <c r="Q292">
         <v>34143787807</v>
       </c>
-      <c r="R292" s="3" t="str">
+      <c r="R292" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1c|B2b|C1c</v>
       </c>
-      <c r="S292" s="2" t="str">
+      <c r="S292" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>669</v>
       </c>
@@ -20733,16 +20701,16 @@
       <c r="Q293">
         <v>34143915183</v>
       </c>
-      <c r="R293" s="3" t="str">
+      <c r="R293" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1d|B2a|C1a</v>
       </c>
-      <c r="S293" s="2" t="str">
+      <c r="S293" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>671</v>
       </c>
@@ -20794,16 +20762,16 @@
       <c r="Q294">
         <v>34143975606</v>
       </c>
-      <c r="R294" s="3" t="str">
+      <c r="R294" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1d|B2a|C1b</v>
       </c>
-      <c r="S294" s="2" t="str">
+      <c r="S294" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>673</v>
       </c>
@@ -20849,16 +20817,16 @@
       <c r="Q295">
         <v>34144103221</v>
       </c>
-      <c r="R295" s="3" t="str">
+      <c r="R295" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1d|B2a|C1c</v>
       </c>
-      <c r="S295" s="2" t="str">
+      <c r="S295" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>675</v>
       </c>
@@ -20910,16 +20878,16 @@
       <c r="Q296">
         <v>34144159753</v>
       </c>
-      <c r="R296" s="3" t="str">
+      <c r="R296" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1d|B2b|C1a</v>
       </c>
-      <c r="S296" s="2" t="str">
+      <c r="S296" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>677</v>
       </c>
@@ -20971,16 +20939,16 @@
       <c r="Q297">
         <v>34144277791</v>
       </c>
-      <c r="R297" s="3" t="str">
+      <c r="R297" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1d|B2b|C1b</v>
       </c>
-      <c r="S297" s="2" t="str">
+      <c r="S297" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>679</v>
       </c>
@@ -21032,16 +21000,16 @@
       <c r="Q298">
         <v>34144386256</v>
       </c>
-      <c r="R298" s="3" t="str">
+      <c r="R298" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A2|B1d|B2b|C1c</v>
       </c>
-      <c r="S298" s="2" t="str">
+      <c r="S298" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>681</v>
       </c>
@@ -21093,16 +21061,16 @@
       <c r="Q299">
         <v>34144499278</v>
       </c>
-      <c r="R299" s="3" t="str">
+      <c r="R299" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1a|B2a|C1a</v>
       </c>
-      <c r="S299" s="2" t="str">
+      <c r="S299" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>683</v>
       </c>
@@ -21154,16 +21122,16 @@
       <c r="Q300">
         <v>34144614446</v>
       </c>
-      <c r="R300" s="3" t="str">
+      <c r="R300" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1a|B2a|C1b</v>
       </c>
-      <c r="S300" s="2" t="str">
+      <c r="S300" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>685</v>
       </c>
@@ -21215,11 +21183,11 @@
       <c r="Q301">
         <v>34144718810</v>
       </c>
-      <c r="R301" s="3" t="str">
+      <c r="R301" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1a|B2a|C1c</v>
       </c>
-      <c r="S301" s="2" t="str">
+      <c r="S301" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
@@ -21276,11 +21244,11 @@
       <c r="Q302">
         <v>34144831462</v>
       </c>
-      <c r="R302" s="3" t="str">
+      <c r="R302" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1a|B2b|C1a</v>
       </c>
-      <c r="S302" s="2" t="str">
+      <c r="S302" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
@@ -21337,11 +21305,11 @@
       <c r="Q303">
         <v>34144922871</v>
       </c>
-      <c r="R303" s="3" t="str">
+      <c r="R303" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1a|B2b|C1b</v>
       </c>
-      <c r="S303" s="2" t="str">
+      <c r="S303" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
@@ -21398,16 +21366,16 @@
       <c r="Q304">
         <v>34145024709</v>
       </c>
-      <c r="R304" s="3" t="str">
+      <c r="R304" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1a|B2b|C1c</v>
       </c>
-      <c r="S304" s="2" t="str">
+      <c r="S304" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>693</v>
       </c>
@@ -21459,16 +21427,16 @@
       <c r="Q305">
         <v>34145128222</v>
       </c>
-      <c r="R305" s="3" t="str">
+      <c r="R305" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1b|B2a|C1a</v>
       </c>
-      <c r="S305" s="2" t="str">
+      <c r="S305" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>695</v>
       </c>
@@ -21520,16 +21488,16 @@
       <c r="Q306">
         <v>34145226429</v>
       </c>
-      <c r="R306" s="3" t="str">
+      <c r="R306" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1b|B2a|C1b</v>
       </c>
-      <c r="S306" s="2" t="str">
+      <c r="S306" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>697</v>
       </c>
@@ -21581,16 +21549,16 @@
       <c r="Q307">
         <v>34145386104</v>
       </c>
-      <c r="R307" s="3" t="str">
+      <c r="R307" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1b|B2a|C1c</v>
       </c>
-      <c r="S307" s="2" t="str">
+      <c r="S307" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
     </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>699</v>
       </c>
@@ -21642,16 +21610,16 @@
       <c r="Q308">
         <v>34145490315</v>
       </c>
-      <c r="R308" s="3" t="str">
+      <c r="R308" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1b|B2b|C1a</v>
       </c>
-      <c r="S308" s="2" t="str">
+      <c r="S308" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>701</v>
       </c>
@@ -21703,16 +21671,16 @@
       <c r="Q309">
         <v>34145605625</v>
       </c>
-      <c r="R309" s="3" t="str">
+      <c r="R309" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1b|B2b|C1b</v>
       </c>
-      <c r="S309" s="2" t="str">
+      <c r="S309" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>703</v>
       </c>
@@ -21764,16 +21732,16 @@
       <c r="Q310">
         <v>34145718972</v>
       </c>
-      <c r="R310" s="3" t="str">
+      <c r="R310" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1b|B2b|C1c</v>
       </c>
-      <c r="S310" s="2" t="str">
+      <c r="S310" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>705</v>
       </c>
@@ -21819,16 +21787,16 @@
       <c r="Q311">
         <v>34145853694</v>
       </c>
-      <c r="R311" s="3" t="str">
+      <c r="R311" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1d|B2a|C1a</v>
       </c>
-      <c r="S311" s="2" t="str">
+      <c r="S311" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>707</v>
       </c>
@@ -21880,16 +21848,16 @@
       <c r="Q312">
         <v>34145906393</v>
       </c>
-      <c r="R312" s="3" t="str">
+      <c r="R312" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1d|B2a|C1b</v>
       </c>
-      <c r="S312" s="2" t="str">
+      <c r="S312" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>709</v>
       </c>
@@ -21935,16 +21903,16 @@
       <c r="Q313">
         <v>34146024038</v>
       </c>
-      <c r="R313" s="3" t="str">
+      <c r="R313" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1d|B2a|C1c</v>
       </c>
-      <c r="S313" s="2" t="str">
+      <c r="S313" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>711</v>
       </c>
@@ -21996,16 +21964,16 @@
       <c r="Q314">
         <v>34146075871</v>
       </c>
-      <c r="R314" s="3" t="str">
+      <c r="R314" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1d|B2b|C1a</v>
       </c>
-      <c r="S314" s="2" t="str">
+      <c r="S314" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="315" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>713</v>
       </c>
@@ -22057,16 +22025,16 @@
       <c r="Q315">
         <v>34146172798</v>
       </c>
-      <c r="R315" s="3" t="str">
+      <c r="R315" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1d|B2b|C1b</v>
       </c>
-      <c r="S315" s="2" t="str">
+      <c r="S315" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="316" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>715</v>
       </c>
@@ -22118,16 +22086,16 @@
       <c r="Q316">
         <v>34146276254</v>
       </c>
-      <c r="R316" s="3" t="str">
+      <c r="R316" s="2" t="str">
         <f t="shared" si="9"/>
         <v>java|A3|B1d|B2b|C1c</v>
       </c>
-      <c r="S316" s="2" t="str">
+      <c r="S316" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="317" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>717</v>
       </c>
@@ -22179,11 +22147,11 @@
       <c r="Q317">
         <v>34197397528</v>
       </c>
-      <c r="R317" s="3" t="str">
+      <c r="R317" s="2" t="str">
         <f t="shared" si="9"/>
         <v>nodejs|A1a|B1a|B2a|C1b</v>
       </c>
-      <c r="S317" s="2" t="str">
+      <c r="S317" t="str">
         <f t="shared" si="10"/>
         <v>P</v>
       </c>
@@ -22240,11 +22208,11 @@
       <c r="Q318">
         <v>34197451848</v>
       </c>
-      <c r="R318" s="3" t="str">
+      <c r="R318" s="2" t="str">
         <f t="shared" si="9"/>
         <v>nodejs|A1a|B1a|B2b|C1b</v>
       </c>
-      <c r="S318" s="2" t="str">
+      <c r="S318" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
@@ -22301,16 +22269,16 @@
       <c r="Q319">
         <v>34197497889</v>
       </c>
-      <c r="R319" s="3" t="str">
+      <c r="R319" s="2" t="str">
         <f t="shared" si="9"/>
         <v>nodejs|A1a|B1a|B2c|C1b</v>
       </c>
-      <c r="S319" s="2" t="str">
+      <c r="S319" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="320" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>726</v>
       </c>
@@ -22356,16 +22324,16 @@
       <c r="Q320">
         <v>34197543317</v>
       </c>
-      <c r="R320" s="3" t="str">
+      <c r="R320" s="2" t="str">
         <f t="shared" si="9"/>
         <v>nodejs|A1a|B1b|B2a|C1b</v>
       </c>
-      <c r="S320" s="2" t="str">
+      <c r="S320" t="str">
         <f t="shared" si="10"/>
         <v>E</v>
       </c>
     </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>728</v>
       </c>
@@ -22417,16 +22385,16 @@
       <c r="Q321">
         <v>34197589207</v>
       </c>
-      <c r="R321" s="3" t="str">
+      <c r="R321" s="2" t="str">
         <f t="shared" si="9"/>
         <v>nodejs|A1a|B1b|B2b|C1b</v>
       </c>
-      <c r="S321" s="2" t="str">
+      <c r="S321" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="322" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>730</v>
       </c>
@@ -22478,16 +22446,16 @@
       <c r="Q322">
         <v>34197638344</v>
       </c>
-      <c r="R322" s="3" t="str">
+      <c r="R322" s="2" t="str">
         <f t="shared" si="9"/>
         <v>nodejs|A1a|B1b|B2c|C1b</v>
       </c>
-      <c r="S322" s="2" t="str">
+      <c r="S322" t="str">
         <f t="shared" si="10"/>
         <v>M</v>
       </c>
     </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>732</v>
       </c>
@@ -22533,16 +22501,16 @@
       <c r="Q323">
         <v>34197686598</v>
       </c>
-      <c r="R323" s="3" t="str">
+      <c r="R323" s="2" t="str">
         <f t="shared" ref="R323:R386" si="11">C323&amp;"|"&amp;D323&amp;"|"&amp;E323&amp;"|"&amp;F323&amp;"|"&amp;G323</f>
         <v>nodejs|A1a|B1c|B2a|C1b</v>
       </c>
-      <c r="S323" s="2" t="str">
+      <c r="S323" t="str">
         <f t="shared" ref="S323:S386" si="12">IF(H323="malicious_resolved","M",IF(H323="private_resolved","P",IF(H323="resolution_error","E","-")))</f>
         <v>E</v>
       </c>
     </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>734</v>
       </c>
@@ -22594,16 +22562,16 @@
       <c r="Q324">
         <v>34197733067</v>
       </c>
-      <c r="R324" s="3" t="str">
+      <c r="R324" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1a|B1c|B2b|C1b</v>
       </c>
-      <c r="S324" s="2" t="str">
+      <c r="S324" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>736</v>
       </c>
@@ -22655,16 +22623,16 @@
       <c r="Q325">
         <v>34197778937</v>
       </c>
-      <c r="R325" s="3" t="str">
+      <c r="R325" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1a|B1c|B2c|C1b</v>
       </c>
-      <c r="S325" s="2" t="str">
+      <c r="S325" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>738</v>
       </c>
@@ -22710,16 +22678,16 @@
       <c r="Q326">
         <v>34197822949</v>
       </c>
-      <c r="R326" s="3" t="str">
+      <c r="R326" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1a|B1d|B2a|C1b</v>
       </c>
-      <c r="S326" s="2" t="str">
+      <c r="S326" t="str">
         <f t="shared" si="12"/>
         <v>E</v>
       </c>
     </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>740</v>
       </c>
@@ -22771,16 +22739,16 @@
       <c r="Q327">
         <v>34197868372</v>
       </c>
-      <c r="R327" s="3" t="str">
+      <c r="R327" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1a|B1d|B2b|C1b</v>
       </c>
-      <c r="S327" s="2" t="str">
+      <c r="S327" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>742</v>
       </c>
@@ -22832,16 +22800,16 @@
       <c r="Q328">
         <v>34197911213</v>
       </c>
-      <c r="R328" s="3" t="str">
+      <c r="R328" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1a|B1d|B2c|C1b</v>
       </c>
-      <c r="S328" s="2" t="str">
+      <c r="S328" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>744</v>
       </c>
@@ -22893,11 +22861,11 @@
       <c r="Q329">
         <v>34197955068</v>
       </c>
-      <c r="R329" s="3" t="str">
+      <c r="R329" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1a|B2a|C1b</v>
       </c>
-      <c r="S329" s="2" t="str">
+      <c r="S329" t="str">
         <f t="shared" si="12"/>
         <v>P</v>
       </c>
@@ -22954,11 +22922,11 @@
       <c r="Q330">
         <v>34197998779</v>
       </c>
-      <c r="R330" s="3" t="str">
+      <c r="R330" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1a|B2b|C1b</v>
       </c>
-      <c r="S330" s="2" t="str">
+      <c r="S330" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
@@ -23015,16 +22983,16 @@
       <c r="Q331">
         <v>34198045664</v>
       </c>
-      <c r="R331" s="3" t="str">
+      <c r="R331" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1a|B2c|C1b</v>
       </c>
-      <c r="S331" s="2" t="str">
+      <c r="S331" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>750</v>
       </c>
@@ -23070,16 +23038,16 @@
       <c r="Q332">
         <v>34198090249</v>
       </c>
-      <c r="R332" s="3" t="str">
+      <c r="R332" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1b|B2a|C1b</v>
       </c>
-      <c r="S332" s="2" t="str">
+      <c r="S332" t="str">
         <f t="shared" si="12"/>
         <v>E</v>
       </c>
     </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>752</v>
       </c>
@@ -23131,16 +23099,16 @@
       <c r="Q333">
         <v>34198132471</v>
       </c>
-      <c r="R333" s="3" t="str">
+      <c r="R333" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1b|B2b|C1b</v>
       </c>
-      <c r="S333" s="2" t="str">
+      <c r="S333" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="334" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>754</v>
       </c>
@@ -23192,16 +23160,16 @@
       <c r="Q334">
         <v>34198176277</v>
       </c>
-      <c r="R334" s="3" t="str">
+      <c r="R334" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1b|B2c|C1b</v>
       </c>
-      <c r="S334" s="2" t="str">
+      <c r="S334" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>756</v>
       </c>
@@ -23247,16 +23215,16 @@
       <c r="Q335">
         <v>34198222764</v>
       </c>
-      <c r="R335" s="3" t="str">
+      <c r="R335" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1c|B2a|C1b</v>
       </c>
-      <c r="S335" s="2" t="str">
+      <c r="S335" t="str">
         <f t="shared" si="12"/>
         <v>E</v>
       </c>
     </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>758</v>
       </c>
@@ -23308,16 +23276,16 @@
       <c r="Q336">
         <v>34198267914</v>
       </c>
-      <c r="R336" s="3" t="str">
+      <c r="R336" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1c|B2b|C1b</v>
       </c>
-      <c r="S336" s="2" t="str">
+      <c r="S336" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>760</v>
       </c>
@@ -23369,16 +23337,16 @@
       <c r="Q337">
         <v>34198313884</v>
       </c>
-      <c r="R337" s="3" t="str">
+      <c r="R337" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1c|B2c|C1b</v>
       </c>
-      <c r="S337" s="2" t="str">
+      <c r="S337" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>762</v>
       </c>
@@ -23424,16 +23392,16 @@
       <c r="Q338">
         <v>34198359318</v>
       </c>
-      <c r="R338" s="3" t="str">
+      <c r="R338" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1d|B2a|C1b</v>
       </c>
-      <c r="S338" s="2" t="str">
+      <c r="S338" t="str">
         <f t="shared" si="12"/>
         <v>E</v>
       </c>
     </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>764</v>
       </c>
@@ -23485,16 +23453,16 @@
       <c r="Q339">
         <v>34198405657</v>
       </c>
-      <c r="R339" s="3" t="str">
+      <c r="R339" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1d|B2b|C1b</v>
       </c>
-      <c r="S339" s="2" t="str">
+      <c r="S339" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>766</v>
       </c>
@@ -23546,16 +23514,16 @@
       <c r="Q340">
         <v>34198454543</v>
       </c>
-      <c r="R340" s="3" t="str">
+      <c r="R340" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A1b|B1d|B2c|C1b</v>
       </c>
-      <c r="S340" s="2" t="str">
+      <c r="S340" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>768</v>
       </c>
@@ -23607,16 +23575,16 @@
       <c r="Q341">
         <v>34198499472</v>
       </c>
-      <c r="R341" s="3" t="str">
+      <c r="R341" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1a|B2a|C1b</v>
       </c>
-      <c r="S341" s="2" t="str">
+      <c r="S341" t="str">
         <f t="shared" si="12"/>
         <v>P</v>
       </c>
     </row>
-    <row r="342" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>770</v>
       </c>
@@ -23668,16 +23636,16 @@
       <c r="Q342">
         <v>34198544276</v>
       </c>
-      <c r="R342" s="3" t="str">
+      <c r="R342" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1a|B2b|C1b</v>
       </c>
-      <c r="S342" s="2" t="str">
+      <c r="S342" t="str">
         <f t="shared" si="12"/>
         <v>P</v>
       </c>
     </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>774</v>
       </c>
@@ -23729,16 +23697,16 @@
       <c r="Q343">
         <v>34198589670</v>
       </c>
-      <c r="R343" s="3" t="str">
+      <c r="R343" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1a|B2c|C1b</v>
       </c>
-      <c r="S343" s="2" t="str">
+      <c r="S343" t="str">
         <f t="shared" si="12"/>
         <v>P</v>
       </c>
     </row>
-    <row r="344" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>776</v>
       </c>
@@ -23784,16 +23752,16 @@
       <c r="Q344">
         <v>34198633501</v>
       </c>
-      <c r="R344" s="3" t="str">
+      <c r="R344" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1b|B2a|C1b</v>
       </c>
-      <c r="S344" s="2" t="str">
+      <c r="S344" t="str">
         <f t="shared" si="12"/>
         <v>E</v>
       </c>
     </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>778</v>
       </c>
@@ -23845,16 +23813,16 @@
       <c r="Q345">
         <v>34198678953</v>
       </c>
-      <c r="R345" s="3" t="str">
+      <c r="R345" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1b|B2b|C1b</v>
       </c>
-      <c r="S345" s="2" t="str">
+      <c r="S345" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>780</v>
       </c>
@@ -23906,16 +23874,16 @@
       <c r="Q346">
         <v>34198724793</v>
       </c>
-      <c r="R346" s="3" t="str">
+      <c r="R346" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1b|B2c|C1b</v>
       </c>
-      <c r="S346" s="2" t="str">
+      <c r="S346" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>782</v>
       </c>
@@ -23961,16 +23929,16 @@
       <c r="Q347">
         <v>34198769113</v>
       </c>
-      <c r="R347" s="3" t="str">
+      <c r="R347" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1c|B2a|C1b</v>
       </c>
-      <c r="S347" s="2" t="str">
+      <c r="S347" t="str">
         <f t="shared" si="12"/>
         <v>E</v>
       </c>
     </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>784</v>
       </c>
@@ -24022,16 +23990,16 @@
       <c r="Q348">
         <v>34198815898</v>
       </c>
-      <c r="R348" s="3" t="str">
+      <c r="R348" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1c|B2b|C1b</v>
       </c>
-      <c r="S348" s="2" t="str">
+      <c r="S348" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>786</v>
       </c>
@@ -24083,16 +24051,16 @@
       <c r="Q349">
         <v>34198861804</v>
       </c>
-      <c r="R349" s="3" t="str">
+      <c r="R349" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1c|B2c|C1b</v>
       </c>
-      <c r="S349" s="2" t="str">
+      <c r="S349" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>788</v>
       </c>
@@ -24138,16 +24106,16 @@
       <c r="Q350">
         <v>34198909493</v>
       </c>
-      <c r="R350" s="3" t="str">
+      <c r="R350" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1d|B2a|C1b</v>
       </c>
-      <c r="S350" s="2" t="str">
+      <c r="S350" t="str">
         <f t="shared" si="12"/>
         <v>E</v>
       </c>
     </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>790</v>
       </c>
@@ -24199,16 +24167,16 @@
       <c r="Q351">
         <v>34198953281</v>
       </c>
-      <c r="R351" s="3" t="str">
+      <c r="R351" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1d|B2b|C1b</v>
       </c>
-      <c r="S351" s="2" t="str">
+      <c r="S351" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>792</v>
       </c>
@@ -24260,16 +24228,16 @@
       <c r="Q352">
         <v>34198999916</v>
       </c>
-      <c r="R352" s="3" t="str">
+      <c r="R352" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A2|B1d|B2c|C1b</v>
       </c>
-      <c r="S352" s="2" t="str">
+      <c r="S352" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>794</v>
       </c>
@@ -24321,16 +24289,16 @@
       <c r="Q353">
         <v>34199046919</v>
       </c>
-      <c r="R353" s="3" t="str">
+      <c r="R353" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1a|B2a|C1b</v>
       </c>
-      <c r="S353" s="2" t="str">
+      <c r="S353" t="str">
         <f t="shared" si="12"/>
         <v>P</v>
       </c>
     </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>796</v>
       </c>
@@ -24382,16 +24350,16 @@
       <c r="Q354">
         <v>34199096741</v>
       </c>
-      <c r="R354" s="3" t="str">
+      <c r="R354" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1a|B2b|C1b</v>
       </c>
-      <c r="S354" s="2" t="str">
+      <c r="S354" t="str">
         <f t="shared" si="12"/>
         <v>P</v>
       </c>
     </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>798</v>
       </c>
@@ -24443,16 +24411,16 @@
       <c r="Q355">
         <v>34199145000</v>
       </c>
-      <c r="R355" s="3" t="str">
+      <c r="R355" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1a|B2c|C1b</v>
       </c>
-      <c r="S355" s="2" t="str">
+      <c r="S355" t="str">
         <f t="shared" si="12"/>
         <v>P</v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>800</v>
       </c>
@@ -24498,16 +24466,16 @@
       <c r="Q356">
         <v>34199194494</v>
       </c>
-      <c r="R356" s="3" t="str">
+      <c r="R356" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1b|B2a|C1b</v>
       </c>
-      <c r="S356" s="2" t="str">
+      <c r="S356" t="str">
         <f t="shared" si="12"/>
         <v>E</v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>802</v>
       </c>
@@ -24559,16 +24527,16 @@
       <c r="Q357">
         <v>34199241018</v>
       </c>
-      <c r="R357" s="3" t="str">
+      <c r="R357" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1b|B2b|C1b</v>
       </c>
-      <c r="S357" s="2" t="str">
+      <c r="S357" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>804</v>
       </c>
@@ -24620,16 +24588,16 @@
       <c r="Q358">
         <v>34199287252</v>
       </c>
-      <c r="R358" s="3" t="str">
+      <c r="R358" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1b|B2c|C1b</v>
       </c>
-      <c r="S358" s="2" t="str">
+      <c r="S358" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>806</v>
       </c>
@@ -24675,16 +24643,16 @@
       <c r="Q359">
         <v>34199333188</v>
       </c>
-      <c r="R359" s="3" t="str">
+      <c r="R359" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1d|B2a|C1b</v>
       </c>
-      <c r="S359" s="2" t="str">
+      <c r="S359" t="str">
         <f t="shared" si="12"/>
         <v>E</v>
       </c>
     </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>808</v>
       </c>
@@ -24736,16 +24704,16 @@
       <c r="Q360">
         <v>34199379573</v>
       </c>
-      <c r="R360" s="3" t="str">
+      <c r="R360" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1d|B2b|C1b</v>
       </c>
-      <c r="S360" s="2" t="str">
+      <c r="S360" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>810</v>
       </c>
@@ -24797,16 +24765,16 @@
       <c r="Q361">
         <v>34199425736</v>
       </c>
-      <c r="R361" s="3" t="str">
+      <c r="R361" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1d|B2c|C1b</v>
       </c>
-      <c r="S361" s="2" t="str">
+      <c r="S361" t="str">
         <f t="shared" si="12"/>
         <v>M</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>812</v>
       </c>
@@ -24849,16 +24817,16 @@
       <c r="P362" t="s">
         <v>721</v>
       </c>
-      <c r="R362" s="3" t="str">
+      <c r="R362" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1c|B2a|C1a</v>
       </c>
-      <c r="S362" s="2" t="str">
+      <c r="S362" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>814</v>
       </c>
@@ -24901,16 +24869,16 @@
       <c r="P363" t="s">
         <v>721</v>
       </c>
-      <c r="R363" s="3" t="str">
+      <c r="R363" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1c|B2a|C1b</v>
       </c>
-      <c r="S363" s="2" t="str">
+      <c r="S363" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>815</v>
       </c>
@@ -24953,16 +24921,16 @@
       <c r="P364" t="s">
         <v>721</v>
       </c>
-      <c r="R364" s="3" t="str">
+      <c r="R364" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1c|B2a|C1c</v>
       </c>
-      <c r="S364" s="2" t="str">
+      <c r="S364" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>816</v>
       </c>
@@ -25005,16 +24973,16 @@
       <c r="P365" t="s">
         <v>721</v>
       </c>
-      <c r="R365" s="3" t="str">
+      <c r="R365" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1c|B2b|C1a</v>
       </c>
-      <c r="S365" s="2" t="str">
+      <c r="S365" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>817</v>
       </c>
@@ -25057,16 +25025,16 @@
       <c r="P366" t="s">
         <v>721</v>
       </c>
-      <c r="R366" s="3" t="str">
+      <c r="R366" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1c|B2b|C1b</v>
       </c>
-      <c r="S366" s="2" t="str">
+      <c r="S366" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>818</v>
       </c>
@@ -25109,16 +25077,16 @@
       <c r="P367" t="s">
         <v>721</v>
       </c>
-      <c r="R367" s="3" t="str">
+      <c r="R367" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1c|B2b|C1c</v>
       </c>
-      <c r="S367" s="2" t="str">
+      <c r="S367" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>819</v>
       </c>
@@ -25161,16 +25129,16 @@
       <c r="P368" t="s">
         <v>721</v>
       </c>
-      <c r="R368" s="3" t="str">
+      <c r="R368" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1c|B2c|C1a</v>
       </c>
-      <c r="S368" s="2" t="str">
+      <c r="S368" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>820</v>
       </c>
@@ -25213,16 +25181,16 @@
       <c r="P369" t="s">
         <v>721</v>
       </c>
-      <c r="R369" s="3" t="str">
+      <c r="R369" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1c|B2c|C1b</v>
       </c>
-      <c r="S369" s="2" t="str">
+      <c r="S369" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>821</v>
       </c>
@@ -25265,16 +25233,16 @@
       <c r="P370" t="s">
         <v>721</v>
       </c>
-      <c r="R370" s="3" t="str">
+      <c r="R370" s="2" t="str">
         <f t="shared" si="11"/>
         <v>nodejs|A3|B1c|B2c|C1c</v>
       </c>
-      <c r="S370" s="2" t="str">
+      <c r="S370" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>822</v>
       </c>
@@ -25317,16 +25285,16 @@
       <c r="P371" t="s">
         <v>721</v>
       </c>
-      <c r="R371" s="3" t="str">
+      <c r="R371" s="2" t="str">
         <f t="shared" si="11"/>
         <v>python|A3|B1c|B2a|C1a</v>
       </c>
-      <c r="S371" s="2" t="str">
+      <c r="S371" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>823</v>
       </c>
@@ -25369,16 +25337,16 @@
       <c r="P372" t="s">
         <v>721</v>
       </c>
-      <c r="R372" s="3" t="str">
+      <c r="R372" s="2" t="str">
         <f t="shared" si="11"/>
         <v>python|A3|B1c|B2a|C1b</v>
       </c>
-      <c r="S372" s="2" t="str">
+      <c r="S372" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>824</v>
       </c>
@@ -25421,16 +25389,16 @@
       <c r="P373" t="s">
         <v>721</v>
       </c>
-      <c r="R373" s="3" t="str">
+      <c r="R373" s="2" t="str">
         <f t="shared" si="11"/>
         <v>python|A3|B1c|B2a|C1c</v>
       </c>
-      <c r="S373" s="2" t="str">
+      <c r="S373" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>825</v>
       </c>
@@ -25473,16 +25441,16 @@
       <c r="P374" t="s">
         <v>721</v>
       </c>
-      <c r="R374" s="3" t="str">
+      <c r="R374" s="2" t="str">
         <f t="shared" si="11"/>
         <v>python|A3|B1c|B2b|C1a</v>
       </c>
-      <c r="S374" s="2" t="str">
+      <c r="S374" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>826</v>
       </c>
@@ -25525,16 +25493,16 @@
       <c r="P375" t="s">
         <v>721</v>
       </c>
-      <c r="R375" s="3" t="str">
+      <c r="R375" s="2" t="str">
         <f t="shared" si="11"/>
         <v>python|A3|B1c|B2b|C1b</v>
       </c>
-      <c r="S375" s="2" t="str">
+      <c r="S375" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>827</v>
       </c>
@@ -25577,16 +25545,16 @@
       <c r="P376" t="s">
         <v>721</v>
       </c>
-      <c r="R376" s="3" t="str">
+      <c r="R376" s="2" t="str">
         <f t="shared" si="11"/>
         <v>python|A3|B1c|B2b|C1c</v>
       </c>
-      <c r="S376" s="2" t="str">
+      <c r="S376" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>828</v>
       </c>
@@ -25629,16 +25597,16 @@
       <c r="P377" t="s">
         <v>721</v>
       </c>
-      <c r="R377" s="3" t="str">
+      <c r="R377" s="2" t="str">
         <f t="shared" si="11"/>
         <v>python|A3|B1c|B2c|C1a</v>
       </c>
-      <c r="S377" s="2" t="str">
+      <c r="S377" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>829</v>
       </c>
@@ -25681,16 +25649,16 @@
       <c r="P378" t="s">
         <v>721</v>
       </c>
-      <c r="R378" s="3" t="str">
+      <c r="R378" s="2" t="str">
         <f t="shared" si="11"/>
         <v>python|A3|B1c|B2c|C1b</v>
       </c>
-      <c r="S378" s="2" t="str">
+      <c r="S378" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>830</v>
       </c>
@@ -25733,16 +25701,16 @@
       <c r="P379" t="s">
         <v>721</v>
       </c>
-      <c r="R379" s="3" t="str">
+      <c r="R379" s="2" t="str">
         <f t="shared" si="11"/>
         <v>python|A3|B1c|B2c|C1c</v>
       </c>
-      <c r="S379" s="2" t="str">
+      <c r="S379" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>831</v>
       </c>
@@ -25785,16 +25753,16 @@
       <c r="P380" t="s">
         <v>721</v>
       </c>
-      <c r="R380" s="3" t="str">
+      <c r="R380" s="2" t="str">
         <f t="shared" si="11"/>
         <v>java|A1a|B1a|B2c|C1a</v>
       </c>
-      <c r="S380" s="2" t="str">
+      <c r="S380" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>832</v>
       </c>
@@ -25837,16 +25805,16 @@
       <c r="P381" t="s">
         <v>721</v>
       </c>
-      <c r="R381" s="3" t="str">
+      <c r="R381" s="2" t="str">
         <f t="shared" si="11"/>
         <v>java|A1a|B1a|B2c|C1b</v>
       </c>
-      <c r="S381" s="2" t="str">
+      <c r="S381" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>833</v>
       </c>
@@ -25889,16 +25857,16 @@
       <c r="P382" t="s">
         <v>721</v>
       </c>
-      <c r="R382" s="3" t="str">
+      <c r="R382" s="2" t="str">
         <f t="shared" si="11"/>
         <v>java|A1a|B1a|B2c|C1c</v>
       </c>
-      <c r="S382" s="2" t="str">
+      <c r="S382" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>834</v>
       </c>
@@ -25941,16 +25909,16 @@
       <c r="P383" t="s">
         <v>721</v>
       </c>
-      <c r="R383" s="3" t="str">
+      <c r="R383" s="2" t="str">
         <f t="shared" si="11"/>
         <v>java|A1a|B1b|B2c|C1a</v>
       </c>
-      <c r="S383" s="2" t="str">
+      <c r="S383" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>835</v>
       </c>
@@ -25993,16 +25961,16 @@
       <c r="P384" t="s">
         <v>721</v>
       </c>
-      <c r="R384" s="3" t="str">
+      <c r="R384" s="2" t="str">
         <f t="shared" si="11"/>
         <v>java|A1a|B1b|B2c|C1b</v>
       </c>
-      <c r="S384" s="2" t="str">
+      <c r="S384" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>836</v>
       </c>
@@ -26045,16 +26013,16 @@
       <c r="P385" t="s">
         <v>721</v>
       </c>
-      <c r="R385" s="3" t="str">
+      <c r="R385" s="2" t="str">
         <f t="shared" si="11"/>
         <v>java|A1a|B1b|B2c|C1c</v>
       </c>
-      <c r="S385" s="2" t="str">
+      <c r="S385" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>837</v>
       </c>
@@ -26097,16 +26065,16 @@
       <c r="P386" t="s">
         <v>721</v>
       </c>
-      <c r="R386" s="3" t="str">
+      <c r="R386" s="2" t="str">
         <f t="shared" si="11"/>
         <v>java|A1a|B1c|B2c|C1a</v>
       </c>
-      <c r="S386" s="2" t="str">
+      <c r="S386" t="str">
         <f t="shared" si="12"/>
         <v>-</v>
       </c>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>838</v>
       </c>
@@ -26149,16 +26117,16 @@
       <c r="P387" t="s">
         <v>721</v>
       </c>
-      <c r="R387" s="3" t="str">
+      <c r="R387" s="2" t="str">
         <f t="shared" ref="R387:R433" si="13">C387&amp;"|"&amp;D387&amp;"|"&amp;E387&amp;"|"&amp;F387&amp;"|"&amp;G387</f>
         <v>java|A1a|B1c|B2c|C1b</v>
       </c>
-      <c r="S387" s="2" t="str">
+      <c r="S387" t="str">
         <f t="shared" ref="S387:S433" si="14">IF(H387="malicious_resolved","M",IF(H387="private_resolved","P",IF(H387="resolution_error","E","-")))</f>
         <v>-</v>
       </c>
     </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>839</v>
       </c>
@@ -26201,16 +26169,16 @@
       <c r="P388" t="s">
         <v>721</v>
       </c>
-      <c r="R388" s="3" t="str">
+      <c r="R388" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1a|B1c|B2c|C1c</v>
       </c>
-      <c r="S388" s="2" t="str">
+      <c r="S388" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>840</v>
       </c>
@@ -26253,16 +26221,16 @@
       <c r="P389" t="s">
         <v>721</v>
       </c>
-      <c r="R389" s="3" t="str">
+      <c r="R389" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1a|B1d|B2c|C1a</v>
       </c>
-      <c r="S389" s="2" t="str">
+      <c r="S389" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>841</v>
       </c>
@@ -26305,16 +26273,16 @@
       <c r="P390" t="s">
         <v>721</v>
       </c>
-      <c r="R390" s="3" t="str">
+      <c r="R390" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1a|B1d|B2c|C1b</v>
       </c>
-      <c r="S390" s="2" t="str">
+      <c r="S390" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>842</v>
       </c>
@@ -26357,16 +26325,16 @@
       <c r="P391" t="s">
         <v>721</v>
       </c>
-      <c r="R391" s="3" t="str">
+      <c r="R391" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1a|B1d|B2c|C1c</v>
       </c>
-      <c r="S391" s="2" t="str">
+      <c r="S391" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>843</v>
       </c>
@@ -26409,16 +26377,16 @@
       <c r="P392" t="s">
         <v>721</v>
       </c>
-      <c r="R392" s="3" t="str">
+      <c r="R392" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1a|B2c|C1a</v>
       </c>
-      <c r="S392" s="2" t="str">
+      <c r="S392" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>844</v>
       </c>
@@ -26461,16 +26429,16 @@
       <c r="P393" t="s">
         <v>721</v>
       </c>
-      <c r="R393" s="3" t="str">
+      <c r="R393" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1a|B2c|C1b</v>
       </c>
-      <c r="S393" s="2" t="str">
+      <c r="S393" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>845</v>
       </c>
@@ -26513,16 +26481,16 @@
       <c r="P394" t="s">
         <v>721</v>
       </c>
-      <c r="R394" s="3" t="str">
+      <c r="R394" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1a|B2c|C1c</v>
       </c>
-      <c r="S394" s="2" t="str">
+      <c r="S394" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>846</v>
       </c>
@@ -26565,16 +26533,16 @@
       <c r="P395" t="s">
         <v>721</v>
       </c>
-      <c r="R395" s="3" t="str">
+      <c r="R395" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1b|B2c|C1a</v>
       </c>
-      <c r="S395" s="2" t="str">
+      <c r="S395" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>847</v>
       </c>
@@ -26617,16 +26585,16 @@
       <c r="P396" t="s">
         <v>721</v>
       </c>
-      <c r="R396" s="3" t="str">
+      <c r="R396" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1b|B2c|C1b</v>
       </c>
-      <c r="S396" s="2" t="str">
+      <c r="S396" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>848</v>
       </c>
@@ -26669,16 +26637,16 @@
       <c r="P397" t="s">
         <v>721</v>
       </c>
-      <c r="R397" s="3" t="str">
+      <c r="R397" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1b|B2c|C1c</v>
       </c>
-      <c r="S397" s="2" t="str">
+      <c r="S397" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>849</v>
       </c>
@@ -26721,16 +26689,16 @@
       <c r="P398" t="s">
         <v>721</v>
       </c>
-      <c r="R398" s="3" t="str">
+      <c r="R398" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1c|B2c|C1a</v>
       </c>
-      <c r="S398" s="2" t="str">
+      <c r="S398" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>850</v>
       </c>
@@ -26773,16 +26741,16 @@
       <c r="P399" t="s">
         <v>721</v>
       </c>
-      <c r="R399" s="3" t="str">
+      <c r="R399" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1c|B2c|C1b</v>
       </c>
-      <c r="S399" s="2" t="str">
+      <c r="S399" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>851</v>
       </c>
@@ -26825,16 +26793,16 @@
       <c r="P400" t="s">
         <v>721</v>
       </c>
-      <c r="R400" s="3" t="str">
+      <c r="R400" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1c|B2c|C1c</v>
       </c>
-      <c r="S400" s="2" t="str">
+      <c r="S400" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="401" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>852</v>
       </c>
@@ -26877,16 +26845,16 @@
       <c r="P401" t="s">
         <v>721</v>
       </c>
-      <c r="R401" s="3" t="str">
+      <c r="R401" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1d|B2c|C1a</v>
       </c>
-      <c r="S401" s="2" t="str">
+      <c r="S401" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="402" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>853</v>
       </c>
@@ -26929,16 +26897,16 @@
       <c r="P402" t="s">
         <v>721</v>
       </c>
-      <c r="R402" s="3" t="str">
+      <c r="R402" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1d|B2c|C1b</v>
       </c>
-      <c r="S402" s="2" t="str">
+      <c r="S402" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="403" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>854</v>
       </c>
@@ -26981,16 +26949,16 @@
       <c r="P403" t="s">
         <v>721</v>
       </c>
-      <c r="R403" s="3" t="str">
+      <c r="R403" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A1b|B1d|B2c|C1c</v>
       </c>
-      <c r="S403" s="2" t="str">
+      <c r="S403" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="404" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>855</v>
       </c>
@@ -27033,16 +27001,16 @@
       <c r="P404" t="s">
         <v>721</v>
       </c>
-      <c r="R404" s="3" t="str">
+      <c r="R404" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1a|B2c|C1a</v>
       </c>
-      <c r="S404" s="2" t="str">
+      <c r="S404" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="405" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>856</v>
       </c>
@@ -27085,16 +27053,16 @@
       <c r="P405" t="s">
         <v>721</v>
       </c>
-      <c r="R405" s="3" t="str">
+      <c r="R405" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1a|B2c|C1b</v>
       </c>
-      <c r="S405" s="2" t="str">
+      <c r="S405" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="406" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>857</v>
       </c>
@@ -27137,16 +27105,16 @@
       <c r="P406" t="s">
         <v>721</v>
       </c>
-      <c r="R406" s="3" t="str">
+      <c r="R406" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1a|B2c|C1c</v>
       </c>
-      <c r="S406" s="2" t="str">
+      <c r="S406" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="407" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>858</v>
       </c>
@@ -27189,16 +27157,16 @@
       <c r="P407" t="s">
         <v>721</v>
       </c>
-      <c r="R407" s="3" t="str">
+      <c r="R407" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1b|B2c|C1a</v>
       </c>
-      <c r="S407" s="2" t="str">
+      <c r="S407" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="408" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>859</v>
       </c>
@@ -27241,16 +27209,16 @@
       <c r="P408" t="s">
         <v>721</v>
       </c>
-      <c r="R408" s="3" t="str">
+      <c r="R408" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1b|B2c|C1b</v>
       </c>
-      <c r="S408" s="2" t="str">
+      <c r="S408" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="409" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>860</v>
       </c>
@@ -27293,16 +27261,16 @@
       <c r="P409" t="s">
         <v>721</v>
       </c>
-      <c r="R409" s="3" t="str">
+      <c r="R409" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1b|B2c|C1c</v>
       </c>
-      <c r="S409" s="2" t="str">
+      <c r="S409" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="410" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>861</v>
       </c>
@@ -27345,16 +27313,16 @@
       <c r="P410" t="s">
         <v>721</v>
       </c>
-      <c r="R410" s="3" t="str">
+      <c r="R410" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1c|B2c|C1a</v>
       </c>
-      <c r="S410" s="2" t="str">
+      <c r="S410" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="411" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>862</v>
       </c>
@@ -27397,16 +27365,16 @@
       <c r="P411" t="s">
         <v>721</v>
       </c>
-      <c r="R411" s="3" t="str">
+      <c r="R411" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1c|B2c|C1b</v>
       </c>
-      <c r="S411" s="2" t="str">
+      <c r="S411" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="412" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>863</v>
       </c>
@@ -27449,16 +27417,16 @@
       <c r="P412" t="s">
         <v>721</v>
       </c>
-      <c r="R412" s="3" t="str">
+      <c r="R412" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1c|B2c|C1c</v>
       </c>
-      <c r="S412" s="2" t="str">
+      <c r="S412" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="413" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>864</v>
       </c>
@@ -27501,16 +27469,16 @@
       <c r="P413" t="s">
         <v>721</v>
       </c>
-      <c r="R413" s="3" t="str">
+      <c r="R413" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1d|B2c|C1a</v>
       </c>
-      <c r="S413" s="2" t="str">
+      <c r="S413" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="414" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>865</v>
       </c>
@@ -27553,16 +27521,16 @@
       <c r="P414" t="s">
         <v>721</v>
       </c>
-      <c r="R414" s="3" t="str">
+      <c r="R414" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1d|B2c|C1b</v>
       </c>
-      <c r="S414" s="2" t="str">
+      <c r="S414" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="415" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>866</v>
       </c>
@@ -27605,16 +27573,16 @@
       <c r="P415" t="s">
         <v>721</v>
       </c>
-      <c r="R415" s="3" t="str">
+      <c r="R415" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A2|B1d|B2c|C1c</v>
       </c>
-      <c r="S415" s="2" t="str">
+      <c r="S415" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="416" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>867</v>
       </c>
@@ -27657,16 +27625,16 @@
       <c r="P416" t="s">
         <v>721</v>
       </c>
-      <c r="R416" s="3" t="str">
+      <c r="R416" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1a|B2c|C1a</v>
       </c>
-      <c r="S416" s="2" t="str">
+      <c r="S416" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="417" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>868</v>
       </c>
@@ -27709,16 +27677,16 @@
       <c r="P417" t="s">
         <v>721</v>
       </c>
-      <c r="R417" s="3" t="str">
+      <c r="R417" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1a|B2c|C1b</v>
       </c>
-      <c r="S417" s="2" t="str">
+      <c r="S417" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="418" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>869</v>
       </c>
@@ -27761,16 +27729,16 @@
       <c r="P418" t="s">
         <v>721</v>
       </c>
-      <c r="R418" s="3" t="str">
+      <c r="R418" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1a|B2c|C1c</v>
       </c>
-      <c r="S418" s="2" t="str">
+      <c r="S418" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="419" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>870</v>
       </c>
@@ -27813,16 +27781,16 @@
       <c r="P419" t="s">
         <v>721</v>
       </c>
-      <c r="R419" s="3" t="str">
+      <c r="R419" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1b|B2c|C1a</v>
       </c>
-      <c r="S419" s="2" t="str">
+      <c r="S419" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="420" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>871</v>
       </c>
@@ -27865,16 +27833,16 @@
       <c r="P420" t="s">
         <v>721</v>
       </c>
-      <c r="R420" s="3" t="str">
+      <c r="R420" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1b|B2c|C1b</v>
       </c>
-      <c r="S420" s="2" t="str">
+      <c r="S420" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="421" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>872</v>
       </c>
@@ -27917,16 +27885,16 @@
       <c r="P421" t="s">
         <v>721</v>
       </c>
-      <c r="R421" s="3" t="str">
+      <c r="R421" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1b|B2c|C1c</v>
       </c>
-      <c r="S421" s="2" t="str">
+      <c r="S421" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="422" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>873</v>
       </c>
@@ -27969,16 +27937,16 @@
       <c r="P422" t="s">
         <v>721</v>
       </c>
-      <c r="R422" s="3" t="str">
+      <c r="R422" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1c|B2a|C1a</v>
       </c>
-      <c r="S422" s="2" t="str">
+      <c r="S422" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="423" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>874</v>
       </c>
@@ -28021,16 +27989,16 @@
       <c r="P423" t="s">
         <v>721</v>
       </c>
-      <c r="R423" s="3" t="str">
+      <c r="R423" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1c|B2a|C1b</v>
       </c>
-      <c r="S423" s="2" t="str">
+      <c r="S423" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="424" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>875</v>
       </c>
@@ -28073,16 +28041,16 @@
       <c r="P424" t="s">
         <v>721</v>
       </c>
-      <c r="R424" s="3" t="str">
+      <c r="R424" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1c|B2a|C1c</v>
       </c>
-      <c r="S424" s="2" t="str">
+      <c r="S424" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="425" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>876</v>
       </c>
@@ -28125,16 +28093,16 @@
       <c r="P425" t="s">
         <v>721</v>
       </c>
-      <c r="R425" s="3" t="str">
+      <c r="R425" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1c|B2b|C1a</v>
       </c>
-      <c r="S425" s="2" t="str">
+      <c r="S425" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="426" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>877</v>
       </c>
@@ -28177,16 +28145,16 @@
       <c r="P426" t="s">
         <v>721</v>
       </c>
-      <c r="R426" s="3" t="str">
+      <c r="R426" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1c|B2b|C1b</v>
       </c>
-      <c r="S426" s="2" t="str">
+      <c r="S426" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="427" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>878</v>
       </c>
@@ -28229,16 +28197,16 @@
       <c r="P427" t="s">
         <v>721</v>
       </c>
-      <c r="R427" s="3" t="str">
+      <c r="R427" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1c|B2b|C1c</v>
       </c>
-      <c r="S427" s="2" t="str">
+      <c r="S427" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="428" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>879</v>
       </c>
@@ -28281,16 +28249,16 @@
       <c r="P428" t="s">
         <v>721</v>
       </c>
-      <c r="R428" s="3" t="str">
+      <c r="R428" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1c|B2c|C1a</v>
       </c>
-      <c r="S428" s="2" t="str">
+      <c r="S428" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="429" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>880</v>
       </c>
@@ -28333,16 +28301,16 @@
       <c r="P429" t="s">
         <v>721</v>
       </c>
-      <c r="R429" s="3" t="str">
+      <c r="R429" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1c|B2c|C1b</v>
       </c>
-      <c r="S429" s="2" t="str">
+      <c r="S429" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="430" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>881</v>
       </c>
@@ -28385,16 +28353,16 @@
       <c r="P430" t="s">
         <v>721</v>
       </c>
-      <c r="R430" s="3" t="str">
+      <c r="R430" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1c|B2c|C1c</v>
       </c>
-      <c r="S430" s="2" t="str">
+      <c r="S430" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="431" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>882</v>
       </c>
@@ -28437,16 +28405,16 @@
       <c r="P431" t="s">
         <v>721</v>
       </c>
-      <c r="R431" s="3" t="str">
+      <c r="R431" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1d|B2c|C1a</v>
       </c>
-      <c r="S431" s="2" t="str">
+      <c r="S431" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="432" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>883</v>
       </c>
@@ -28489,16 +28457,16 @@
       <c r="P432" t="s">
         <v>721</v>
       </c>
-      <c r="R432" s="3" t="str">
+      <c r="R432" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1d|B2c|C1b</v>
       </c>
-      <c r="S432" s="2" t="str">
+      <c r="S432" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
     </row>
-    <row r="433" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>884</v>
       </c>
@@ -28541,11 +28509,11 @@
       <c r="P433" t="s">
         <v>721</v>
       </c>
-      <c r="R433" s="3" t="str">
+      <c r="R433" s="2" t="str">
         <f t="shared" si="13"/>
         <v>java|A3|B1d|B2c|C1c</v>
       </c>
-      <c r="S433" s="2" t="str">
+      <c r="S433" t="str">
         <f t="shared" si="14"/>
         <v>-</v>
       </c>
@@ -30867,44 +30835,44 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:K19">
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
-      <formula>"M"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
-      <formula>"E"</formula>
-    </cfRule>
     <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"-"</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+      <formula>"E"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+      <formula>"M"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:K40">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"E"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C46:K61">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"E"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"M"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/sub-RQ1_result/analysis/result_analysis_excel.xlsx
+++ b/sub-RQ1_result/analysis/result_analysis_excel.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BCDE57-8ED4-4F6D-BBB4-5E43C8C69CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{482212B2-0356-4914-B53B-8802B28615EB}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{482212B2-0356-4914-B53B-8802B28615EB}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="2" r:id="rId1"/>

--- a/sub-RQ1_result/analysis/result_analysis_excel.xlsx
+++ b/sub-RQ1_result/analysis/result_analysis_excel.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Master_Winfo\MA_Supply_chain_security\MS_test_system\sub-RQ1_result\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BCDE57-8ED4-4F6D-BBB4-5E43C8C69CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C96C805-7F3C-4283-82F2-1B45B2478FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{482212B2-0356-4914-B53B-8802B28615EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{482212B2-0356-4914-B53B-8802B28615EB}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="2" r:id="rId1"/>
     <sheet name="FigureC" sheetId="1" r:id="rId2"/>
+    <sheet name="step9" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">step9!$A$1:$I$145</definedName>
     <definedName name="ExterneDaten_1" localSheetId="0" hidden="1">'results'!$A$1:$Q$433</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5788" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6380" uniqueCount="896">
   <si>
     <t>cell_id</t>
   </si>
@@ -2712,13 +2714,40 @@
   </si>
   <si>
     <t>code</t>
+  </si>
+  <si>
+    <t>agreement</t>
+  </si>
+  <si>
+    <t>agree</t>
+  </si>
+  <si>
+    <t>disagree</t>
+  </si>
+  <si>
+    <t>not comparable</t>
+  </si>
+  <si>
+    <t>npm_result_alone</t>
+  </si>
+  <si>
+    <t>invalid cells are also counted, need to be filtered</t>
+  </si>
+  <si>
+    <t>npm alone has different result (in 39 rows)</t>
+  </si>
+  <si>
+    <t>pip alone has different result (in 39 rows)</t>
+  </si>
+  <si>
+    <t>maven alone has different result (in 39 rows)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2738,16 +2767,66 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2755,21 +2834,270 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="57">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2945,40 +3273,29 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7F29230C-F0E4-43EA-8341-3E01AF9D8D83}" name="results" displayName="results" ref="A1:S433" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:S433" xr:uid="{7F29230C-F0E4-43EA-8341-3E01AF9D8D83}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="B1a"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <filters>
-        <filter val="malicious_resolved"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S433" xr:uid="{7F29230C-F0E4-43EA-8341-3E01AF9D8D83}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{A65D53B3-AEE8-4BDA-A007-78AF105B23C7}" uniqueName="1" name="cell_id" queryTableFieldId="1" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{FAE1C5D0-B844-4E04-8570-5E7392EC0CD8}" uniqueName="2" name="timestamp" queryTableFieldId="2" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{BBF46145-6F90-4151-B5A4-CDBB35EFE548}" uniqueName="3" name="ecosystem" queryTableFieldId="3" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{BE192AD0-EA51-423D-8064-F03DFC2283D1}" uniqueName="4" name="A - private registry configuration" queryTableFieldId="4" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{0CC34752-F77F-4389-A551-0DF478F89775}" uniqueName="5" name="B1 - package manager configuration" queryTableFieldId="5" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{860742B4-072C-4C8E-A14D-384D82844D79}" uniqueName="6" name="B2 - version specifier" queryTableFieldId="6" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{55C1A906-487C-4BD6-9FE2-2C83CC981730}" uniqueName="7" name="C - pipeline operation type" queryTableFieldId="7" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{58E9AA63-32ED-49FD-8C66-24784E1318A0}" uniqueName="8" name="classification" queryTableFieldId="8" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{A44E4050-08CE-4488-B898-63D9257CCF92}" uniqueName="9" name="pk1_name" queryTableFieldId="9" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{A65D53B3-AEE8-4BDA-A007-78AF105B23C7}" uniqueName="1" name="cell_id" queryTableFieldId="1" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{FAE1C5D0-B844-4E04-8570-5E7392EC0CD8}" uniqueName="2" name="timestamp" queryTableFieldId="2" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{BBF46145-6F90-4151-B5A4-CDBB35EFE548}" uniqueName="3" name="ecosystem" queryTableFieldId="3" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{BE192AD0-EA51-423D-8064-F03DFC2283D1}" uniqueName="4" name="A - private registry configuration" queryTableFieldId="4" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{0CC34752-F77F-4389-A551-0DF478F89775}" uniqueName="5" name="B1 - package manager configuration" queryTableFieldId="5" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{860742B4-072C-4C8E-A14D-384D82844D79}" uniqueName="6" name="B2 - version specifier" queryTableFieldId="6" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{55C1A906-487C-4BD6-9FE2-2C83CC981730}" uniqueName="7" name="C - pipeline operation type" queryTableFieldId="7" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{58E9AA63-32ED-49FD-8C66-24784E1318A0}" uniqueName="8" name="classification" queryTableFieldId="8" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{A44E4050-08CE-4488-B898-63D9257CCF92}" uniqueName="9" name="pk1_name" queryTableFieldId="9" dataDxfId="48"/>
     <tableColumn id="10" xr3:uid="{71E0CA27-6CEE-4940-B266-B7513F22296A}" uniqueName="10" name="pk1_version" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{F6F3F30F-14D7-481E-A758-BCE99E99F129}" uniqueName="11" name="pk1_url" queryTableFieldId="11" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{921B2E99-895D-4E5E-9510-DEAAD18CD223}" uniqueName="12" name="pk2_name" queryTableFieldId="12" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{F6F3F30F-14D7-481E-A758-BCE99E99F129}" uniqueName="11" name="pk1_url" queryTableFieldId="11" dataDxfId="47"/>
+    <tableColumn id="12" xr3:uid="{921B2E99-895D-4E5E-9510-DEAAD18CD223}" uniqueName="12" name="pk2_name" queryTableFieldId="12" dataDxfId="46"/>
     <tableColumn id="13" xr3:uid="{9084FB30-82DC-4AE6-8FB6-1C31A0551FB8}" uniqueName="13" name="pk2_version" queryTableFieldId="13"/>
-    <tableColumn id="14" xr3:uid="{D5B22B60-C596-4281-B574-FA3B124D4F4F}" uniqueName="14" name="pk2_url" queryTableFieldId="14" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{D94E0725-5A59-42CC-BE75-97D4507A7741}" uniqueName="15" name="artifact_path" queryTableFieldId="15" dataDxfId="15"/>
-    <tableColumn id="16" xr3:uid="{71208F8D-867D-4980-A5B2-3594876264F4}" uniqueName="16" name="git_commit" queryTableFieldId="16" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{D5B22B60-C596-4281-B574-FA3B124D4F4F}" uniqueName="14" name="pk2_url" queryTableFieldId="14" dataDxfId="45"/>
+    <tableColumn id="15" xr3:uid="{D94E0725-5A59-42CC-BE75-97D4507A7741}" uniqueName="15" name="artifact_path" queryTableFieldId="15" dataDxfId="44"/>
+    <tableColumn id="16" xr3:uid="{71208F8D-867D-4980-A5B2-3594876264F4}" uniqueName="16" name="git_commit" queryTableFieldId="16" dataDxfId="43"/>
     <tableColumn id="17" xr3:uid="{27213F26-9F4A-4C3E-AE70-27C7397D8686}" uniqueName="17" name="github_run_id" queryTableFieldId="17"/>
-    <tableColumn id="18" xr3:uid="{91A6E711-13C5-4562-A6EC-0ECEC846B0F3}" uniqueName="18" name="key" queryTableFieldId="18" dataDxfId="13">
+    <tableColumn id="18" xr3:uid="{91A6E711-13C5-4562-A6EC-0ECEC846B0F3}" uniqueName="18" name="key" queryTableFieldId="18" dataDxfId="42">
       <calculatedColumnFormula>C2&amp;"|"&amp;D2&amp;"|"&amp;E2&amp;"|"&amp;F2&amp;"|"&amp;G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{CD516DC1-753B-4C59-ABD3-C987D8E0FB42}" uniqueName="19" name="code" queryTableFieldId="19" dataDxfId="12">
+    <tableColumn id="19" xr3:uid="{CD516DC1-753B-4C59-ABD3-C987D8E0FB42}" uniqueName="19" name="code" queryTableFieldId="19" dataDxfId="41">
       <calculatedColumnFormula>IF(H2="malicious_resolved","M",IF(H2="private_resolved","P",IF(H2="resolution_error","E","-")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3307,7 +3624,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.21875" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" customWidth="1"/>
@@ -3384,7 +3701,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -3445,7 +3762,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -3750,7 +4067,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -3805,7 +4122,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -3860,7 +4177,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -3921,7 +4238,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -3982,7 +4299,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -4043,7 +4360,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -4104,7 +4421,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -4159,7 +4476,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -4214,7 +4531,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -4275,7 +4592,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>72</v>
       </c>
@@ -4336,7 +4653,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -4397,7 +4714,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -4458,7 +4775,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>78</v>
       </c>
@@ -4513,7 +4830,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -4568,7 +4885,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -4629,7 +4946,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -4690,7 +5007,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>87</v>
       </c>
@@ -4751,7 +5068,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>89</v>
       </c>
@@ -4812,7 +5129,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>91</v>
       </c>
@@ -4873,7 +5190,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>96</v>
       </c>
@@ -5178,7 +5495,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>108</v>
       </c>
@@ -5233,7 +5550,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -5288,7 +5605,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>112</v>
       </c>
@@ -5349,7 +5666,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>114</v>
       </c>
@@ -5410,7 +5727,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>116</v>
       </c>
@@ -5471,7 +5788,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -5532,7 +5849,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>120</v>
       </c>
@@ -5587,7 +5904,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -5642,7 +5959,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>124</v>
       </c>
@@ -5703,7 +6020,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -5764,7 +6081,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>128</v>
       </c>
@@ -5825,7 +6142,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>130</v>
       </c>
@@ -5886,7 +6203,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>132</v>
       </c>
@@ -5941,7 +6258,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>134</v>
       </c>
@@ -5996,7 +6313,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>136</v>
       </c>
@@ -6057,7 +6374,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>138</v>
       </c>
@@ -6118,7 +6435,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -6179,7 +6496,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>142</v>
       </c>
@@ -6240,7 +6557,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>144</v>
       </c>
@@ -6295,7 +6612,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>147</v>
       </c>
@@ -6350,7 +6667,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>149</v>
       </c>
@@ -6405,7 +6722,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>151</v>
       </c>
@@ -6460,7 +6777,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>153</v>
       </c>
@@ -6515,7 +6832,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>155</v>
       </c>
@@ -6570,7 +6887,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>157</v>
       </c>
@@ -6625,7 +6942,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>159</v>
       </c>
@@ -6680,7 +6997,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>161</v>
       </c>
@@ -6741,7 +7058,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>163</v>
       </c>
@@ -6802,7 +7119,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>165</v>
       </c>
@@ -6863,7 +7180,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>167</v>
       </c>
@@ -6924,7 +7241,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>169</v>
       </c>
@@ -6979,7 +7296,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>171</v>
       </c>
@@ -7034,7 +7351,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>173</v>
       </c>
@@ -7095,7 +7412,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>175</v>
       </c>
@@ -7156,7 +7473,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>177</v>
       </c>
@@ -7217,7 +7534,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>179</v>
       </c>
@@ -7278,7 +7595,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>181</v>
       </c>
@@ -7333,7 +7650,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>183</v>
       </c>
@@ -7388,7 +7705,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>185</v>
       </c>
@@ -7449,7 +7766,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>187</v>
       </c>
@@ -7510,7 +7827,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>189</v>
       </c>
@@ -7571,7 +7888,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>191</v>
       </c>
@@ -7632,7 +7949,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>193</v>
       </c>
@@ -7687,7 +8004,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>196</v>
       </c>
@@ -7742,7 +8059,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>198</v>
       </c>
@@ -7797,7 +8114,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>200</v>
       </c>
@@ -7852,7 +8169,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>202</v>
       </c>
@@ -7907,7 +8224,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>204</v>
       </c>
@@ -7962,7 +8279,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>206</v>
       </c>
@@ -8017,7 +8334,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>208</v>
       </c>
@@ -8072,7 +8389,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>210</v>
       </c>
@@ -8133,7 +8450,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>212</v>
       </c>
@@ -8194,7 +8511,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>214</v>
       </c>
@@ -8255,7 +8572,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>216</v>
       </c>
@@ -8316,7 +8633,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>218</v>
       </c>
@@ -8371,7 +8688,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>220</v>
       </c>
@@ -8426,7 +8743,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>222</v>
       </c>
@@ -8487,7 +8804,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>224</v>
       </c>
@@ -8548,7 +8865,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>226</v>
       </c>
@@ -8609,7 +8926,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>228</v>
       </c>
@@ -8670,7 +8987,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>230</v>
       </c>
@@ -8731,7 +9048,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>237</v>
       </c>
@@ -8792,7 +9109,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>240</v>
       </c>
@@ -9219,7 +9536,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>256</v>
       </c>
@@ -9280,7 +9597,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>258</v>
       </c>
@@ -9341,7 +9658,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>260</v>
       </c>
@@ -9402,7 +9719,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>262</v>
       </c>
@@ -9463,7 +9780,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>266</v>
       </c>
@@ -9524,7 +9841,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>268</v>
       </c>
@@ -9585,7 +9902,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>270</v>
       </c>
@@ -9646,7 +9963,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>272</v>
       </c>
@@ -9707,7 +10024,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>274</v>
       </c>
@@ -9768,7 +10085,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>276</v>
       </c>
@@ -9829,7 +10146,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>278</v>
       </c>
@@ -9890,7 +10207,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>280</v>
       </c>
@@ -9951,7 +10268,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>282</v>
       </c>
@@ -10012,7 +10329,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>286</v>
       </c>
@@ -10073,7 +10390,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>288</v>
       </c>
@@ -10134,7 +10451,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>290</v>
       </c>
@@ -10195,7 +10512,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>292</v>
       </c>
@@ -10256,7 +10573,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>294</v>
       </c>
@@ -10317,7 +10634,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>296</v>
       </c>
@@ -10372,7 +10689,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>298</v>
       </c>
@@ -10427,7 +10744,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>300</v>
       </c>
@@ -10482,7 +10799,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>302</v>
       </c>
@@ -10543,7 +10860,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>304</v>
       </c>
@@ -10598,7 +10915,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>306</v>
       </c>
@@ -10659,7 +10976,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>308</v>
       </c>
@@ -10720,7 +11037,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>310</v>
       </c>
@@ -10775,7 +11092,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>312</v>
       </c>
@@ -10836,7 +11153,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>314</v>
       </c>
@@ -10897,7 +11214,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>318</v>
       </c>
@@ -10958,7 +11275,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>320</v>
       </c>
@@ -11385,7 +11702,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>336</v>
       </c>
@@ -11446,7 +11763,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>338</v>
       </c>
@@ -11507,7 +11824,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>340</v>
       </c>
@@ -11568,7 +11885,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>342</v>
       </c>
@@ -11629,7 +11946,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>344</v>
       </c>
@@ -11690,7 +12007,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>346</v>
       </c>
@@ -11751,7 +12068,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>348</v>
       </c>
@@ -11812,7 +12129,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>350</v>
       </c>
@@ -11873,7 +12190,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>352</v>
       </c>
@@ -11934,7 +12251,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>354</v>
       </c>
@@ -11995,7 +12312,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>356</v>
       </c>
@@ -12056,7 +12373,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>358</v>
       </c>
@@ -12117,7 +12434,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>360</v>
       </c>
@@ -12178,7 +12495,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>362</v>
       </c>
@@ -12239,7 +12556,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>364</v>
       </c>
@@ -12300,7 +12617,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>366</v>
       </c>
@@ -12361,7 +12678,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>368</v>
       </c>
@@ -12422,7 +12739,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>370</v>
       </c>
@@ -12483,7 +12800,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>372</v>
       </c>
@@ -12538,7 +12855,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>374</v>
       </c>
@@ -12593,7 +12910,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>376</v>
       </c>
@@ -12648,7 +12965,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>378</v>
       </c>
@@ -12709,7 +13026,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>380</v>
       </c>
@@ -12764,7 +13081,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>382</v>
       </c>
@@ -12825,7 +13142,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>384</v>
       </c>
@@ -12886,7 +13203,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>386</v>
       </c>
@@ -12941,7 +13258,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>388</v>
       </c>
@@ -13002,7 +13319,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>390</v>
       </c>
@@ -13057,7 +13374,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>392</v>
       </c>
@@ -13112,7 +13429,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>394</v>
       </c>
@@ -13167,7 +13484,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>396</v>
       </c>
@@ -13222,7 +13539,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>398</v>
       </c>
@@ -13277,7 +13594,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>400</v>
       </c>
@@ -13332,7 +13649,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>402</v>
       </c>
@@ -13387,7 +13704,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>404</v>
       </c>
@@ -13442,7 +13759,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>406</v>
       </c>
@@ -13497,7 +13814,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>408</v>
       </c>
@@ -13558,7 +13875,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>412</v>
       </c>
@@ -13619,7 +13936,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>414</v>
       </c>
@@ -13680,7 +13997,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>416</v>
       </c>
@@ -13741,7 +14058,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>418</v>
       </c>
@@ -13802,7 +14119,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>420</v>
       </c>
@@ -13863,7 +14180,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>422</v>
       </c>
@@ -13924,7 +14241,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>424</v>
       </c>
@@ -13985,7 +14302,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>426</v>
       </c>
@@ -14046,7 +14363,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>428</v>
       </c>
@@ -14107,7 +14424,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>430</v>
       </c>
@@ -14168,7 +14485,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>432</v>
       </c>
@@ -14229,7 +14546,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>434</v>
       </c>
@@ -14290,7 +14607,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>436</v>
       </c>
@@ -14351,7 +14668,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>438</v>
       </c>
@@ -14412,7 +14729,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>440</v>
       </c>
@@ -14473,7 +14790,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>442</v>
       </c>
@@ -14534,7 +14851,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>444</v>
       </c>
@@ -14595,7 +14912,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>446</v>
       </c>
@@ -14650,7 +14967,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>448</v>
       </c>
@@ -14705,7 +15022,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>450</v>
       </c>
@@ -14760,7 +15077,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>452</v>
       </c>
@@ -14821,7 +15138,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>454</v>
       </c>
@@ -14876,7 +15193,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>456</v>
       </c>
@@ -14937,7 +15254,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>458</v>
       </c>
@@ -14998,7 +15315,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>460</v>
       </c>
@@ -15053,7 +15370,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>462</v>
       </c>
@@ -15114,7 +15431,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>464</v>
       </c>
@@ -15169,7 +15486,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>466</v>
       </c>
@@ -15224,7 +15541,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>468</v>
       </c>
@@ -15279,7 +15596,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>470</v>
       </c>
@@ -15334,7 +15651,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>472</v>
       </c>
@@ -15389,7 +15706,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>474</v>
       </c>
@@ -15444,7 +15761,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>476</v>
       </c>
@@ -15499,7 +15816,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>478</v>
       </c>
@@ -15554,7 +15871,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>480</v>
       </c>
@@ -15609,7 +15926,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>482</v>
       </c>
@@ -15670,7 +15987,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>484</v>
       </c>
@@ -15731,7 +16048,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>486</v>
       </c>
@@ -15792,7 +16109,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>488</v>
       </c>
@@ -15853,7 +16170,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>490</v>
       </c>
@@ -15914,7 +16231,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>492</v>
       </c>
@@ -15975,7 +16292,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>494</v>
       </c>
@@ -16036,7 +16353,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>496</v>
       </c>
@@ -16097,7 +16414,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>498</v>
       </c>
@@ -16158,7 +16475,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>500</v>
       </c>
@@ -16213,7 +16530,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>502</v>
       </c>
@@ -16268,7 +16585,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>504</v>
       </c>
@@ -16323,7 +16640,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>506</v>
       </c>
@@ -16384,7 +16701,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>508</v>
       </c>
@@ -16439,7 +16756,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>510</v>
       </c>
@@ -16500,7 +16817,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>512</v>
       </c>
@@ -16561,7 +16878,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>514</v>
       </c>
@@ -16616,7 +16933,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>516</v>
       </c>
@@ -16677,7 +16994,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>518</v>
       </c>
@@ -16738,7 +17055,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>525</v>
       </c>
@@ -16799,7 +17116,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>527</v>
       </c>
@@ -17043,7 +17360,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>537</v>
       </c>
@@ -17104,7 +17421,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>539</v>
       </c>
@@ -17165,7 +17482,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>541</v>
       </c>
@@ -17226,7 +17543,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>543</v>
       </c>
@@ -17287,7 +17604,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>547</v>
       </c>
@@ -17348,7 +17665,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>549</v>
       </c>
@@ -17409,7 +17726,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>551</v>
       </c>
@@ -17470,7 +17787,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>553</v>
       </c>
@@ -17531,7 +17848,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>555</v>
       </c>
@@ -17592,7 +17909,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>557</v>
       </c>
@@ -17653,7 +17970,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>561</v>
       </c>
@@ -17714,7 +18031,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>563</v>
       </c>
@@ -17775,7 +18092,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>565</v>
       </c>
@@ -17830,7 +18147,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>567</v>
       </c>
@@ -17891,7 +18208,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>569</v>
       </c>
@@ -17946,7 +18263,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>571</v>
       </c>
@@ -18007,7 +18324,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>573</v>
       </c>
@@ -18068,7 +18385,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>575</v>
       </c>
@@ -18129,7 +18446,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>577</v>
       </c>
@@ -18190,7 +18507,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>581</v>
       </c>
@@ -18251,7 +18568,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>583</v>
       </c>
@@ -18495,7 +18812,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>593</v>
       </c>
@@ -18556,7 +18873,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>595</v>
       </c>
@@ -18617,7 +18934,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>597</v>
       </c>
@@ -18678,7 +18995,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>599</v>
       </c>
@@ -18739,7 +19056,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>601</v>
       </c>
@@ -18800,7 +19117,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>603</v>
       </c>
@@ -18861,7 +19178,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>605</v>
       </c>
@@ -18922,7 +19239,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>607</v>
       </c>
@@ -18983,7 +19300,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>609</v>
       </c>
@@ -19044,7 +19361,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>611</v>
       </c>
@@ -19105,7 +19422,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>613</v>
       </c>
@@ -19166,7 +19483,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>615</v>
       </c>
@@ -19227,7 +19544,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>617</v>
       </c>
@@ -19282,7 +19599,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>619</v>
       </c>
@@ -19343,7 +19660,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>621</v>
       </c>
@@ -19398,7 +19715,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>623</v>
       </c>
@@ -19459,7 +19776,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>625</v>
       </c>
@@ -19520,7 +19837,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>627</v>
       </c>
@@ -19581,7 +19898,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>629</v>
       </c>
@@ -19636,7 +19953,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>631</v>
       </c>
@@ -19697,7 +20014,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>635</v>
       </c>
@@ -19752,7 +20069,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>637</v>
       </c>
@@ -19807,7 +20124,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>639</v>
       </c>
@@ -19868,7 +20185,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="280" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>643</v>
       </c>
@@ -19923,7 +20240,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>645</v>
       </c>
@@ -19984,7 +20301,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>647</v>
       </c>
@@ -20045,7 +20362,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>649</v>
       </c>
@@ -20106,7 +20423,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>651</v>
       </c>
@@ -20167,7 +20484,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>653</v>
       </c>
@@ -20228,7 +20545,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>655</v>
       </c>
@@ -20289,7 +20606,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>657</v>
       </c>
@@ -20350,7 +20667,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>659</v>
       </c>
@@ -20411,7 +20728,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="289" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>661</v>
       </c>
@@ -20472,7 +20789,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="290" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>663</v>
       </c>
@@ -20533,7 +20850,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="291" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>665</v>
       </c>
@@ -20594,7 +20911,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="292" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>667</v>
       </c>
@@ -20655,7 +20972,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>669</v>
       </c>
@@ -20710,7 +21027,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>671</v>
       </c>
@@ -20771,7 +21088,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>673</v>
       </c>
@@ -20826,7 +21143,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="296" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>675</v>
       </c>
@@ -20887,7 +21204,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>677</v>
       </c>
@@ -20948,7 +21265,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>679</v>
       </c>
@@ -21009,7 +21326,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>681</v>
       </c>
@@ -21070,7 +21387,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>683</v>
       </c>
@@ -21131,7 +21448,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>685</v>
       </c>
@@ -21375,7 +21692,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>693</v>
       </c>
@@ -21436,7 +21753,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>695</v>
       </c>
@@ -21497,7 +21814,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="307" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>697</v>
       </c>
@@ -21558,7 +21875,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="308" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>699</v>
       </c>
@@ -21619,7 +21936,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="309" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>701</v>
       </c>
@@ -21680,7 +21997,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="310" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>703</v>
       </c>
@@ -21741,7 +22058,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>705</v>
       </c>
@@ -21796,7 +22113,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>707</v>
       </c>
@@ -21857,7 +22174,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>709</v>
       </c>
@@ -21912,7 +22229,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>711</v>
       </c>
@@ -21973,7 +22290,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="315" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>713</v>
       </c>
@@ -22034,7 +22351,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="316" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>715</v>
       </c>
@@ -22095,7 +22412,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="317" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>717</v>
       </c>
@@ -22278,7 +22595,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>726</v>
       </c>
@@ -22333,7 +22650,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>728</v>
       </c>
@@ -22394,7 +22711,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="322" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>730</v>
       </c>
@@ -22455,7 +22772,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>732</v>
       </c>
@@ -22510,7 +22827,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>734</v>
       </c>
@@ -22571,7 +22888,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>736</v>
       </c>
@@ -22632,7 +22949,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>738</v>
       </c>
@@ -22687,7 +23004,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>740</v>
       </c>
@@ -22748,7 +23065,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>742</v>
       </c>
@@ -22809,7 +23126,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>744</v>
       </c>
@@ -22992,7 +23309,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>750</v>
       </c>
@@ -23047,7 +23364,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>752</v>
       </c>
@@ -23108,7 +23425,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="334" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>754</v>
       </c>
@@ -23169,7 +23486,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>756</v>
       </c>
@@ -23224,7 +23541,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>758</v>
       </c>
@@ -23285,7 +23602,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="337" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>760</v>
       </c>
@@ -23346,7 +23663,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>762</v>
       </c>
@@ -23401,7 +23718,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>764</v>
       </c>
@@ -23462,7 +23779,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="340" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>766</v>
       </c>
@@ -23523,7 +23840,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>768</v>
       </c>
@@ -23584,7 +23901,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="342" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>770</v>
       </c>
@@ -23645,7 +23962,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>774</v>
       </c>
@@ -23706,7 +24023,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="344" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>776</v>
       </c>
@@ -23761,7 +24078,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>778</v>
       </c>
@@ -23822,7 +24139,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>780</v>
       </c>
@@ -23883,7 +24200,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>782</v>
       </c>
@@ -23938,7 +24255,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>784</v>
       </c>
@@ -23999,7 +24316,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>786</v>
       </c>
@@ -24060,7 +24377,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>788</v>
       </c>
@@ -24115,7 +24432,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>790</v>
       </c>
@@ -24176,7 +24493,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>792</v>
       </c>
@@ -24237,7 +24554,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>794</v>
       </c>
@@ -24298,7 +24615,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>796</v>
       </c>
@@ -24359,7 +24676,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>798</v>
       </c>
@@ -24420,7 +24737,7 @@
         <v>P</v>
       </c>
     </row>
-    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>800</v>
       </c>
@@ -24475,7 +24792,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>802</v>
       </c>
@@ -24536,7 +24853,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>804</v>
       </c>
@@ -24597,7 +24914,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>806</v>
       </c>
@@ -24652,7 +24969,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>808</v>
       </c>
@@ -24713,7 +25030,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>810</v>
       </c>
@@ -24774,7 +25091,7 @@
         <v>M</v>
       </c>
     </row>
-    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>812</v>
       </c>
@@ -24826,7 +25143,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>814</v>
       </c>
@@ -24878,7 +25195,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>815</v>
       </c>
@@ -24930,7 +25247,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>816</v>
       </c>
@@ -24982,7 +25299,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>817</v>
       </c>
@@ -25034,7 +25351,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>818</v>
       </c>
@@ -25086,7 +25403,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>819</v>
       </c>
@@ -25138,7 +25455,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>820</v>
       </c>
@@ -25190,7 +25507,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>821</v>
       </c>
@@ -25242,7 +25559,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>822</v>
       </c>
@@ -25294,7 +25611,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>823</v>
       </c>
@@ -25346,7 +25663,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>824</v>
       </c>
@@ -25398,7 +25715,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>825</v>
       </c>
@@ -25450,7 +25767,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>826</v>
       </c>
@@ -25502,7 +25819,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>827</v>
       </c>
@@ -25554,7 +25871,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>828</v>
       </c>
@@ -25606,7 +25923,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>829</v>
       </c>
@@ -25658,7 +25975,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>830</v>
       </c>
@@ -25710,7 +26027,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>831</v>
       </c>
@@ -25762,7 +26079,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>832</v>
       </c>
@@ -25814,7 +26131,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>833</v>
       </c>
@@ -25866,7 +26183,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>834</v>
       </c>
@@ -25918,7 +26235,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>835</v>
       </c>
@@ -25970,7 +26287,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>836</v>
       </c>
@@ -26022,7 +26339,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>837</v>
       </c>
@@ -26074,7 +26391,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>838</v>
       </c>
@@ -26126,7 +26443,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>839</v>
       </c>
@@ -26178,7 +26495,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>840</v>
       </c>
@@ -26230,7 +26547,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>841</v>
       </c>
@@ -26282,7 +26599,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>842</v>
       </c>
@@ -26334,7 +26651,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>843</v>
       </c>
@@ -26386,7 +26703,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>844</v>
       </c>
@@ -26438,7 +26755,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>845</v>
       </c>
@@ -26490,7 +26807,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>846</v>
       </c>
@@ -26542,7 +26859,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>847</v>
       </c>
@@ -26594,7 +26911,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>848</v>
       </c>
@@ -26646,7 +26963,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>849</v>
       </c>
@@ -26698,7 +27015,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>850</v>
       </c>
@@ -26750,7 +27067,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>851</v>
       </c>
@@ -26802,7 +27119,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>852</v>
       </c>
@@ -26854,7 +27171,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>853</v>
       </c>
@@ -26906,7 +27223,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>854</v>
       </c>
@@ -26958,7 +27275,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>855</v>
       </c>
@@ -27010,7 +27327,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>856</v>
       </c>
@@ -27062,7 +27379,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>857</v>
       </c>
@@ -27114,7 +27431,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>858</v>
       </c>
@@ -27166,7 +27483,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>859</v>
       </c>
@@ -27218,7 +27535,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>860</v>
       </c>
@@ -27270,7 +27587,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>861</v>
       </c>
@@ -27322,7 +27639,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>862</v>
       </c>
@@ -27374,7 +27691,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>863</v>
       </c>
@@ -27426,7 +27743,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>864</v>
       </c>
@@ -27478,7 +27795,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>865</v>
       </c>
@@ -27530,7 +27847,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>866</v>
       </c>
@@ -27582,7 +27899,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>867</v>
       </c>
@@ -27634,7 +27951,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>868</v>
       </c>
@@ -27686,7 +28003,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>869</v>
       </c>
@@ -27738,7 +28055,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>870</v>
       </c>
@@ -27790,7 +28107,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>871</v>
       </c>
@@ -27842,7 +28159,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>872</v>
       </c>
@@ -27894,7 +28211,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>873</v>
       </c>
@@ -27946,7 +28263,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>874</v>
       </c>
@@ -27998,7 +28315,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>875</v>
       </c>
@@ -28050,7 +28367,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>876</v>
       </c>
@@ -28102,7 +28419,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>877</v>
       </c>
@@ -28154,7 +28471,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>878</v>
       </c>
@@ -28206,7 +28523,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>879</v>
       </c>
@@ -28258,7 +28575,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="429" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>880</v>
       </c>
@@ -28310,7 +28627,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>881</v>
       </c>
@@ -28362,7 +28679,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>882</v>
       </c>
@@ -28414,7 +28731,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>883</v>
       </c>
@@ -28466,7 +28783,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="433" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>884</v>
       </c>
@@ -30835,45 +31152,5051 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:K19">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="9" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="10" operator="equal">
       <formula>"E"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="11" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="12" operator="equal">
       <formula>"M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:K40">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="6" operator="equal">
       <formula>"E"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="7" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="8" operator="equal">
       <formula>"M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C46:K61">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"E"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
       <formula>"M"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4249C603-D76A-4D75-8999-A8343558CAF2}">
+  <dimension ref="A1:N145"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="N1" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="str">
+        <f>VLOOKUP("npm_"&amp;A2&amp;"_"&amp;B2&amp;"_"&amp;C2&amp;"_"&amp;D2,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F2" t="str">
+        <f>VLOOKUP("pip_"&amp;A2&amp;"_"&amp;B2&amp;"_"&amp;C2&amp;"_"&amp;D2,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G2" t="str">
+        <f>VLOOKUP("mvn_"&amp;A2&amp;"_"&amp;B2&amp;"_"&amp;C2&amp;"_"&amp;D2,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H2" t="str">
+        <f>IF(COUNTIF(E2:G2,"&lt;&gt;invalid_configuration")&lt;2,"not comparable",IF(MAX(COUNTIF(E2:G2,"malicious_resolved"),COUNTIF(E2:G2,"private_resolved"),COUNTIF(E2:G2,"resolution_error"))=COUNTIF(E2:G2,"&lt;&gt;invalid_configuration"),"agree","disagree"))</f>
+        <v>agree</v>
+      </c>
+      <c r="I2" t="str">
+        <f>IF(H2="disagree",IF(AND(E2&lt;&gt;F2,E2&lt;&gt;G2),"npm alone has different result",IF(AND(F2&lt;&gt;E2,F2&lt;&gt;G2),"pip alone has different result",IF(AND(G2&lt;&gt;E2,G2&lt;&gt;F2),"maven alone has different result","mixed"))),"")</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>COUNTIF(H2:H145,"agree")</f>
+        <v>96</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>888</v>
+      </c>
+      <c r="M2">
+        <f>COUNTIF(I2:I145,"npm alone has different result")</f>
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="str">
+        <f>VLOOKUP("npm_"&amp;A3&amp;"_"&amp;B3&amp;"_"&amp;C3&amp;"_"&amp;D3,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F3" t="str">
+        <f>VLOOKUP("pip_"&amp;A3&amp;"_"&amp;B3&amp;"_"&amp;C3&amp;"_"&amp;D3,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G3" t="str">
+        <f>VLOOKUP("mvn_"&amp;A3&amp;"_"&amp;B3&amp;"_"&amp;C3&amp;"_"&amp;D3,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H66" si="0">IF(COUNTIF(E3:G3,"&lt;&gt;invalid_configuration")&lt;2,"not comparable",IF(MAX(COUNTIF(E3:G3,"malicious_resolved"),COUNTIF(E3:G3,"private_resolved"),COUNTIF(E3:G3,"resolution_error"))=COUNTIF(E3:G3,"&lt;&gt;invalid_configuration"),"agree","disagree"))</f>
+        <v>agree</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I66" si="1">IF(H3="disagree",IF(AND(E3&lt;&gt;F3,E3&lt;&gt;G3),"npm alone has different result",IF(AND(F3&lt;&gt;E3,F3&lt;&gt;G3),"pip alone has different result",IF(AND(G3&lt;&gt;E3,G3&lt;&gt;F3),"maven alone has different result","mixed"))),"")</f>
+        <v/>
+      </c>
+      <c r="J3">
+        <f>COUNTIF(H2:H145,"disagree")</f>
+        <v>39</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>889</v>
+      </c>
+      <c r="M3">
+        <f>COUNTIF(I2:I145,"pip alone has different result")</f>
+        <v>7</v>
+      </c>
+      <c r="N3" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="str">
+        <f>VLOOKUP("npm_"&amp;A4&amp;"_"&amp;B4&amp;"_"&amp;C4&amp;"_"&amp;D4,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F4" t="str">
+        <f>VLOOKUP("pip_"&amp;A4&amp;"_"&amp;B4&amp;"_"&amp;C4&amp;"_"&amp;D4,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G4" t="str">
+        <f>VLOOKUP("mvn_"&amp;A4&amp;"_"&amp;B4&amp;"_"&amp;C4&amp;"_"&amp;D4,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>COUNTIF(H2:H145,"not comparable")</f>
+        <v>9</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="M4">
+        <f>COUNTIF(I2:I145,"maven alone has different result")</f>
+        <v>4</v>
+      </c>
+      <c r="N4" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="str">
+        <f>VLOOKUP("npm_"&amp;A5&amp;"_"&amp;B5&amp;"_"&amp;C5&amp;"_"&amp;D5,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F5" t="str">
+        <f>VLOOKUP("pip_"&amp;A5&amp;"_"&amp;B5&amp;"_"&amp;C5&amp;"_"&amp;D5,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G5" t="str">
+        <f>VLOOKUP("mvn_"&amp;A5&amp;"_"&amp;B5&amp;"_"&amp;C5&amp;"_"&amp;D5,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="str">
+        <f>VLOOKUP("npm_"&amp;A6&amp;"_"&amp;B6&amp;"_"&amp;C6&amp;"_"&amp;D6,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F6" t="str">
+        <f>VLOOKUP("pip_"&amp;A6&amp;"_"&amp;B6&amp;"_"&amp;C6&amp;"_"&amp;D6,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G6" t="str">
+        <f>VLOOKUP("mvn_"&amp;A6&amp;"_"&amp;B6&amp;"_"&amp;C6&amp;"_"&amp;D6,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="str">
+        <f>VLOOKUP("npm_"&amp;A7&amp;"_"&amp;B7&amp;"_"&amp;C7&amp;"_"&amp;D7,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F7" t="str">
+        <f>VLOOKUP("pip_"&amp;A7&amp;"_"&amp;B7&amp;"_"&amp;C7&amp;"_"&amp;D7,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G7" t="str">
+        <f>VLOOKUP("mvn_"&amp;A7&amp;"_"&amp;B7&amp;"_"&amp;C7&amp;"_"&amp;D7,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="str">
+        <f>VLOOKUP("npm_"&amp;A8&amp;"_"&amp;B8&amp;"_"&amp;C8&amp;"_"&amp;D8,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F8" t="str">
+        <f>VLOOKUP("pip_"&amp;A8&amp;"_"&amp;B8&amp;"_"&amp;C8&amp;"_"&amp;D8,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G8" t="str">
+        <f>VLOOKUP("mvn_"&amp;A8&amp;"_"&amp;B8&amp;"_"&amp;C8&amp;"_"&amp;D8,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="str">
+        <f>VLOOKUP("npm_"&amp;A9&amp;"_"&amp;B9&amp;"_"&amp;C9&amp;"_"&amp;D9,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F9" t="str">
+        <f>VLOOKUP("pip_"&amp;A9&amp;"_"&amp;B9&amp;"_"&amp;C9&amp;"_"&amp;D9,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G9" t="str">
+        <f>VLOOKUP("mvn_"&amp;A9&amp;"_"&amp;B9&amp;"_"&amp;C9&amp;"_"&amp;D9,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="str">
+        <f>VLOOKUP("npm_"&amp;A10&amp;"_"&amp;B10&amp;"_"&amp;C10&amp;"_"&amp;D10,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F10" t="str">
+        <f>VLOOKUP("pip_"&amp;A10&amp;"_"&amp;B10&amp;"_"&amp;C10&amp;"_"&amp;D10,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G10" t="str">
+        <f>VLOOKUP("mvn_"&amp;A10&amp;"_"&amp;B10&amp;"_"&amp;C10&amp;"_"&amp;D10,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="str">
+        <f>VLOOKUP("npm_"&amp;A11&amp;"_"&amp;B11&amp;"_"&amp;C11&amp;"_"&amp;D11,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F11" t="str">
+        <f>VLOOKUP("pip_"&amp;A11&amp;"_"&amp;B11&amp;"_"&amp;C11&amp;"_"&amp;D11,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G11" t="str">
+        <f>VLOOKUP("mvn_"&amp;A11&amp;"_"&amp;B11&amp;"_"&amp;C11&amp;"_"&amp;D11,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="str">
+        <f>VLOOKUP("npm_"&amp;A12&amp;"_"&amp;B12&amp;"_"&amp;C12&amp;"_"&amp;D12,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F12" t="str">
+        <f>VLOOKUP("pip_"&amp;A12&amp;"_"&amp;B12&amp;"_"&amp;C12&amp;"_"&amp;D12,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G12" t="str">
+        <f>VLOOKUP("mvn_"&amp;A12&amp;"_"&amp;B12&amp;"_"&amp;C12&amp;"_"&amp;D12,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="str">
+        <f>VLOOKUP("npm_"&amp;A13&amp;"_"&amp;B13&amp;"_"&amp;C13&amp;"_"&amp;D13,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F13" t="str">
+        <f>VLOOKUP("pip_"&amp;A13&amp;"_"&amp;B13&amp;"_"&amp;C13&amp;"_"&amp;D13,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G13" t="str">
+        <f>VLOOKUP("mvn_"&amp;A13&amp;"_"&amp;B13&amp;"_"&amp;C13&amp;"_"&amp;D13,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="str">
+        <f>VLOOKUP("npm_"&amp;A14&amp;"_"&amp;B14&amp;"_"&amp;C14&amp;"_"&amp;D14,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F14" t="str">
+        <f>VLOOKUP("pip_"&amp;A14&amp;"_"&amp;B14&amp;"_"&amp;C14&amp;"_"&amp;D14,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G14" t="str">
+        <f>VLOOKUP("mvn_"&amp;A14&amp;"_"&amp;B14&amp;"_"&amp;C14&amp;"_"&amp;D14,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="str">
+        <f>VLOOKUP("npm_"&amp;A15&amp;"_"&amp;B15&amp;"_"&amp;C15&amp;"_"&amp;D15,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F15" t="str">
+        <f>VLOOKUP("pip_"&amp;A15&amp;"_"&amp;B15&amp;"_"&amp;C15&amp;"_"&amp;D15,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G15" t="str">
+        <f>VLOOKUP("mvn_"&amp;A15&amp;"_"&amp;B15&amp;"_"&amp;C15&amp;"_"&amp;D15,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="str">
+        <f>VLOOKUP("npm_"&amp;A16&amp;"_"&amp;B16&amp;"_"&amp;C16&amp;"_"&amp;D16,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F16" t="str">
+        <f>VLOOKUP("pip_"&amp;A16&amp;"_"&amp;B16&amp;"_"&amp;C16&amp;"_"&amp;D16,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G16" t="str">
+        <f>VLOOKUP("mvn_"&amp;A16&amp;"_"&amp;B16&amp;"_"&amp;C16&amp;"_"&amp;D16,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="str">
+        <f>VLOOKUP("npm_"&amp;A17&amp;"_"&amp;B17&amp;"_"&amp;C17&amp;"_"&amp;D17,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F17" t="str">
+        <f>VLOOKUP("pip_"&amp;A17&amp;"_"&amp;B17&amp;"_"&amp;C17&amp;"_"&amp;D17,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G17" t="str">
+        <f>VLOOKUP("mvn_"&amp;A17&amp;"_"&amp;B17&amp;"_"&amp;C17&amp;"_"&amp;D17,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="str">
+        <f>VLOOKUP("npm_"&amp;A18&amp;"_"&amp;B18&amp;"_"&amp;C18&amp;"_"&amp;D18,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F18" t="str">
+        <f>VLOOKUP("pip_"&amp;A18&amp;"_"&amp;B18&amp;"_"&amp;C18&amp;"_"&amp;D18,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G18" t="str">
+        <f>VLOOKUP("mvn_"&amp;A18&amp;"_"&amp;B18&amp;"_"&amp;C18&amp;"_"&amp;D18,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" t="str">
+        <f>VLOOKUP("npm_"&amp;A19&amp;"_"&amp;B19&amp;"_"&amp;C19&amp;"_"&amp;D19,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F19" t="str">
+        <f>VLOOKUP("pip_"&amp;A19&amp;"_"&amp;B19&amp;"_"&amp;C19&amp;"_"&amp;D19,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G19" t="str">
+        <f>VLOOKUP("mvn_"&amp;A19&amp;"_"&amp;B19&amp;"_"&amp;C19&amp;"_"&amp;D19,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" t="str">
+        <f>VLOOKUP("npm_"&amp;A20&amp;"_"&amp;B20&amp;"_"&amp;C20&amp;"_"&amp;D20,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F20" t="str">
+        <f>VLOOKUP("pip_"&amp;A20&amp;"_"&amp;B20&amp;"_"&amp;C20&amp;"_"&amp;D20,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G20" t="str">
+        <f>VLOOKUP("mvn_"&amp;A20&amp;"_"&amp;B20&amp;"_"&amp;C20&amp;"_"&amp;D20,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="str">
+        <f>VLOOKUP("npm_"&amp;A21&amp;"_"&amp;B21&amp;"_"&amp;C21&amp;"_"&amp;D21,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F21" t="str">
+        <f>VLOOKUP("pip_"&amp;A21&amp;"_"&amp;B21&amp;"_"&amp;C21&amp;"_"&amp;D21,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G21" t="str">
+        <f>VLOOKUP("mvn_"&amp;A21&amp;"_"&amp;B21&amp;"_"&amp;C21&amp;"_"&amp;D21,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" t="str">
+        <f>VLOOKUP("npm_"&amp;A22&amp;"_"&amp;B22&amp;"_"&amp;C22&amp;"_"&amp;D22,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F22" t="str">
+        <f>VLOOKUP("pip_"&amp;A22&amp;"_"&amp;B22&amp;"_"&amp;C22&amp;"_"&amp;D22,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G22" t="str">
+        <f>VLOOKUP("mvn_"&amp;A22&amp;"_"&amp;B22&amp;"_"&amp;C22&amp;"_"&amp;D22,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" t="str">
+        <f>VLOOKUP("npm_"&amp;A23&amp;"_"&amp;B23&amp;"_"&amp;C23&amp;"_"&amp;D23,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F23" t="str">
+        <f>VLOOKUP("pip_"&amp;A23&amp;"_"&amp;B23&amp;"_"&amp;C23&amp;"_"&amp;D23,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G23" t="str">
+        <f>VLOOKUP("mvn_"&amp;A23&amp;"_"&amp;B23&amp;"_"&amp;C23&amp;"_"&amp;D23,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" t="str">
+        <f>VLOOKUP("npm_"&amp;A24&amp;"_"&amp;B24&amp;"_"&amp;C24&amp;"_"&amp;D24,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F24" t="str">
+        <f>VLOOKUP("pip_"&amp;A24&amp;"_"&amp;B24&amp;"_"&amp;C24&amp;"_"&amp;D24,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G24" t="str">
+        <f>VLOOKUP("mvn_"&amp;A24&amp;"_"&amp;B24&amp;"_"&amp;C24&amp;"_"&amp;D24,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" t="str">
+        <f>VLOOKUP("npm_"&amp;A25&amp;"_"&amp;B25&amp;"_"&amp;C25&amp;"_"&amp;D25,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F25" t="str">
+        <f>VLOOKUP("pip_"&amp;A25&amp;"_"&amp;B25&amp;"_"&amp;C25&amp;"_"&amp;D25,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G25" t="str">
+        <f>VLOOKUP("mvn_"&amp;A25&amp;"_"&amp;B25&amp;"_"&amp;C25&amp;"_"&amp;D25,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" t="str">
+        <f>VLOOKUP("npm_"&amp;A26&amp;"_"&amp;B26&amp;"_"&amp;C26&amp;"_"&amp;D26,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F26" t="str">
+        <f>VLOOKUP("pip_"&amp;A26&amp;"_"&amp;B26&amp;"_"&amp;C26&amp;"_"&amp;D26,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G26" t="str">
+        <f>VLOOKUP("mvn_"&amp;A26&amp;"_"&amp;B26&amp;"_"&amp;C26&amp;"_"&amp;D26,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" t="str">
+        <f>VLOOKUP("npm_"&amp;A27&amp;"_"&amp;B27&amp;"_"&amp;C27&amp;"_"&amp;D27,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F27" t="str">
+        <f>VLOOKUP("pip_"&amp;A27&amp;"_"&amp;B27&amp;"_"&amp;C27&amp;"_"&amp;D27,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G27" t="str">
+        <f>VLOOKUP("mvn_"&amp;A27&amp;"_"&amp;B27&amp;"_"&amp;C27&amp;"_"&amp;D27,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" t="str">
+        <f>VLOOKUP("npm_"&amp;A28&amp;"_"&amp;B28&amp;"_"&amp;C28&amp;"_"&amp;D28,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F28" t="str">
+        <f>VLOOKUP("pip_"&amp;A28&amp;"_"&amp;B28&amp;"_"&amp;C28&amp;"_"&amp;D28,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G28" t="str">
+        <f>VLOOKUP("mvn_"&amp;A28&amp;"_"&amp;B28&amp;"_"&amp;C28&amp;"_"&amp;D28,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" t="str">
+        <f>VLOOKUP("npm_"&amp;A29&amp;"_"&amp;B29&amp;"_"&amp;C29&amp;"_"&amp;D29,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F29" t="str">
+        <f>VLOOKUP("pip_"&amp;A29&amp;"_"&amp;B29&amp;"_"&amp;C29&amp;"_"&amp;D29,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G29" t="str">
+        <f>VLOOKUP("mvn_"&amp;A29&amp;"_"&amp;B29&amp;"_"&amp;C29&amp;"_"&amp;D29,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" t="str">
+        <f>VLOOKUP("npm_"&amp;A30&amp;"_"&amp;B30&amp;"_"&amp;C30&amp;"_"&amp;D30,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F30" t="str">
+        <f>VLOOKUP("pip_"&amp;A30&amp;"_"&amp;B30&amp;"_"&amp;C30&amp;"_"&amp;D30,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G30" t="str">
+        <f>VLOOKUP("mvn_"&amp;A30&amp;"_"&amp;B30&amp;"_"&amp;C30&amp;"_"&amp;D30,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" t="str">
+        <f>VLOOKUP("npm_"&amp;A31&amp;"_"&amp;B31&amp;"_"&amp;C31&amp;"_"&amp;D31,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F31" t="str">
+        <f>VLOOKUP("pip_"&amp;A31&amp;"_"&amp;B31&amp;"_"&amp;C31&amp;"_"&amp;D31,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G31" t="str">
+        <f>VLOOKUP("mvn_"&amp;A31&amp;"_"&amp;B31&amp;"_"&amp;C31&amp;"_"&amp;D31,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" t="str">
+        <f>VLOOKUP("npm_"&amp;A32&amp;"_"&amp;B32&amp;"_"&amp;C32&amp;"_"&amp;D32,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F32" t="str">
+        <f>VLOOKUP("pip_"&amp;A32&amp;"_"&amp;B32&amp;"_"&amp;C32&amp;"_"&amp;D32,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G32" t="str">
+        <f>VLOOKUP("mvn_"&amp;A32&amp;"_"&amp;B32&amp;"_"&amp;C32&amp;"_"&amp;D32,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="str">
+        <f>VLOOKUP("npm_"&amp;A33&amp;"_"&amp;B33&amp;"_"&amp;C33&amp;"_"&amp;D33,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F33" t="str">
+        <f>VLOOKUP("pip_"&amp;A33&amp;"_"&amp;B33&amp;"_"&amp;C33&amp;"_"&amp;D33,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G33" t="str">
+        <f>VLOOKUP("mvn_"&amp;A33&amp;"_"&amp;B33&amp;"_"&amp;C33&amp;"_"&amp;D33,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" t="str">
+        <f>VLOOKUP("npm_"&amp;A34&amp;"_"&amp;B34&amp;"_"&amp;C34&amp;"_"&amp;D34,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F34" t="str">
+        <f>VLOOKUP("pip_"&amp;A34&amp;"_"&amp;B34&amp;"_"&amp;C34&amp;"_"&amp;D34,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G34" t="str">
+        <f>VLOOKUP("mvn_"&amp;A34&amp;"_"&amp;B34&amp;"_"&amp;C34&amp;"_"&amp;D34,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" t="str">
+        <f>VLOOKUP("npm_"&amp;A35&amp;"_"&amp;B35&amp;"_"&amp;C35&amp;"_"&amp;D35,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F35" t="str">
+        <f>VLOOKUP("pip_"&amp;A35&amp;"_"&amp;B35&amp;"_"&amp;C35&amp;"_"&amp;D35,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G35" t="str">
+        <f>VLOOKUP("mvn_"&amp;A35&amp;"_"&amp;B35&amp;"_"&amp;C35&amp;"_"&amp;D35,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" t="str">
+        <f>VLOOKUP("npm_"&amp;A36&amp;"_"&amp;B36&amp;"_"&amp;C36&amp;"_"&amp;D36,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F36" t="str">
+        <f>VLOOKUP("pip_"&amp;A36&amp;"_"&amp;B36&amp;"_"&amp;C36&amp;"_"&amp;D36,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G36" t="str">
+        <f>VLOOKUP("mvn_"&amp;A36&amp;"_"&amp;B36&amp;"_"&amp;C36&amp;"_"&amp;D36,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" t="str">
+        <f>VLOOKUP("npm_"&amp;A37&amp;"_"&amp;B37&amp;"_"&amp;C37&amp;"_"&amp;D37,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F37" t="str">
+        <f>VLOOKUP("pip_"&amp;A37&amp;"_"&amp;B37&amp;"_"&amp;C37&amp;"_"&amp;D37,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G37" t="str">
+        <f>VLOOKUP("mvn_"&amp;A37&amp;"_"&amp;B37&amp;"_"&amp;C37&amp;"_"&amp;D37,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" t="str">
+        <f>VLOOKUP("npm_"&amp;A38&amp;"_"&amp;B38&amp;"_"&amp;C38&amp;"_"&amp;D38,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F38" t="str">
+        <f>VLOOKUP("pip_"&amp;A38&amp;"_"&amp;B38&amp;"_"&amp;C38&amp;"_"&amp;D38,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G38" t="str">
+        <f>VLOOKUP("mvn_"&amp;A38&amp;"_"&amp;B38&amp;"_"&amp;C38&amp;"_"&amp;D38,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" t="str">
+        <f>VLOOKUP("npm_"&amp;A39&amp;"_"&amp;B39&amp;"_"&amp;C39&amp;"_"&amp;D39,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F39" t="str">
+        <f>VLOOKUP("pip_"&amp;A39&amp;"_"&amp;B39&amp;"_"&amp;C39&amp;"_"&amp;D39,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G39" t="str">
+        <f>VLOOKUP("mvn_"&amp;A39&amp;"_"&amp;B39&amp;"_"&amp;C39&amp;"_"&amp;D39,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" t="str">
+        <f>VLOOKUP("npm_"&amp;A40&amp;"_"&amp;B40&amp;"_"&amp;C40&amp;"_"&amp;D40,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F40" t="str">
+        <f>VLOOKUP("pip_"&amp;A40&amp;"_"&amp;B40&amp;"_"&amp;C40&amp;"_"&amp;D40,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G40" t="str">
+        <f>VLOOKUP("mvn_"&amp;A40&amp;"_"&amp;B40&amp;"_"&amp;C40&amp;"_"&amp;D40,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" t="str">
+        <f>VLOOKUP("npm_"&amp;A41&amp;"_"&amp;B41&amp;"_"&amp;C41&amp;"_"&amp;D41,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F41" t="str">
+        <f>VLOOKUP("pip_"&amp;A41&amp;"_"&amp;B41&amp;"_"&amp;C41&amp;"_"&amp;D41,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G41" t="str">
+        <f>VLOOKUP("mvn_"&amp;A41&amp;"_"&amp;B41&amp;"_"&amp;C41&amp;"_"&amp;D41,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" t="str">
+        <f>VLOOKUP("npm_"&amp;A42&amp;"_"&amp;B42&amp;"_"&amp;C42&amp;"_"&amp;D42,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F42" t="str">
+        <f>VLOOKUP("pip_"&amp;A42&amp;"_"&amp;B42&amp;"_"&amp;C42&amp;"_"&amp;D42,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G42" t="str">
+        <f>VLOOKUP("mvn_"&amp;A42&amp;"_"&amp;B42&amp;"_"&amp;C42&amp;"_"&amp;D42,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" t="str">
+        <f>VLOOKUP("npm_"&amp;A43&amp;"_"&amp;B43&amp;"_"&amp;C43&amp;"_"&amp;D43,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F43" t="str">
+        <f>VLOOKUP("pip_"&amp;A43&amp;"_"&amp;B43&amp;"_"&amp;C43&amp;"_"&amp;D43,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G43" t="str">
+        <f>VLOOKUP("mvn_"&amp;A43&amp;"_"&amp;B43&amp;"_"&amp;C43&amp;"_"&amp;D43,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" t="str">
+        <f>VLOOKUP("npm_"&amp;A44&amp;"_"&amp;B44&amp;"_"&amp;C44&amp;"_"&amp;D44,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F44" t="str">
+        <f>VLOOKUP("pip_"&amp;A44&amp;"_"&amp;B44&amp;"_"&amp;C44&amp;"_"&amp;D44,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G44" t="str">
+        <f>VLOOKUP("mvn_"&amp;A44&amp;"_"&amp;B44&amp;"_"&amp;C44&amp;"_"&amp;D44,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" t="str">
+        <f>VLOOKUP("npm_"&amp;A45&amp;"_"&amp;B45&amp;"_"&amp;C45&amp;"_"&amp;D45,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F45" t="str">
+        <f>VLOOKUP("pip_"&amp;A45&amp;"_"&amp;B45&amp;"_"&amp;C45&amp;"_"&amp;D45,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G45" t="str">
+        <f>VLOOKUP("mvn_"&amp;A45&amp;"_"&amp;B45&amp;"_"&amp;C45&amp;"_"&amp;D45,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" t="str">
+        <f>VLOOKUP("npm_"&amp;A46&amp;"_"&amp;B46&amp;"_"&amp;C46&amp;"_"&amp;D46,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F46" t="str">
+        <f>VLOOKUP("pip_"&amp;A46&amp;"_"&amp;B46&amp;"_"&amp;C46&amp;"_"&amp;D46,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G46" t="str">
+        <f>VLOOKUP("mvn_"&amp;A46&amp;"_"&amp;B46&amp;"_"&amp;C46&amp;"_"&amp;D46,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" t="str">
+        <f>VLOOKUP("npm_"&amp;A47&amp;"_"&amp;B47&amp;"_"&amp;C47&amp;"_"&amp;D47,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F47" t="str">
+        <f>VLOOKUP("pip_"&amp;A47&amp;"_"&amp;B47&amp;"_"&amp;C47&amp;"_"&amp;D47,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G47" t="str">
+        <f>VLOOKUP("mvn_"&amp;A47&amp;"_"&amp;B47&amp;"_"&amp;C47&amp;"_"&amp;D47,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" t="str">
+        <f>VLOOKUP("npm_"&amp;A48&amp;"_"&amp;B48&amp;"_"&amp;C48&amp;"_"&amp;D48,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F48" t="str">
+        <f>VLOOKUP("pip_"&amp;A48&amp;"_"&amp;B48&amp;"_"&amp;C48&amp;"_"&amp;D48,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G48" t="str">
+        <f>VLOOKUP("mvn_"&amp;A48&amp;"_"&amp;B48&amp;"_"&amp;C48&amp;"_"&amp;D48,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" t="str">
+        <f>VLOOKUP("npm_"&amp;A49&amp;"_"&amp;B49&amp;"_"&amp;C49&amp;"_"&amp;D49,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F49" t="str">
+        <f>VLOOKUP("pip_"&amp;A49&amp;"_"&amp;B49&amp;"_"&amp;C49&amp;"_"&amp;D49,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G49" t="str">
+        <f>VLOOKUP("mvn_"&amp;A49&amp;"_"&amp;B49&amp;"_"&amp;C49&amp;"_"&amp;D49,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" t="str">
+        <f>VLOOKUP("npm_"&amp;A50&amp;"_"&amp;B50&amp;"_"&amp;C50&amp;"_"&amp;D50,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F50" t="str">
+        <f>VLOOKUP("pip_"&amp;A50&amp;"_"&amp;B50&amp;"_"&amp;C50&amp;"_"&amp;D50,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G50" t="str">
+        <f>VLOOKUP("mvn_"&amp;A50&amp;"_"&amp;B50&amp;"_"&amp;C50&amp;"_"&amp;D50,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" t="str">
+        <f>VLOOKUP("npm_"&amp;A51&amp;"_"&amp;B51&amp;"_"&amp;C51&amp;"_"&amp;D51,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F51" t="str">
+        <f>VLOOKUP("pip_"&amp;A51&amp;"_"&amp;B51&amp;"_"&amp;C51&amp;"_"&amp;D51,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G51" t="str">
+        <f>VLOOKUP("mvn_"&amp;A51&amp;"_"&amp;B51&amp;"_"&amp;C51&amp;"_"&amp;D51,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" t="str">
+        <f>VLOOKUP("npm_"&amp;A52&amp;"_"&amp;B52&amp;"_"&amp;C52&amp;"_"&amp;D52,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F52" t="str">
+        <f>VLOOKUP("pip_"&amp;A52&amp;"_"&amp;B52&amp;"_"&amp;C52&amp;"_"&amp;D52,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G52" t="str">
+        <f>VLOOKUP("mvn_"&amp;A52&amp;"_"&amp;B52&amp;"_"&amp;C52&amp;"_"&amp;D52,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H52" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" t="str">
+        <f>VLOOKUP("npm_"&amp;A53&amp;"_"&amp;B53&amp;"_"&amp;C53&amp;"_"&amp;D53,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F53" t="str">
+        <f>VLOOKUP("pip_"&amp;A53&amp;"_"&amp;B53&amp;"_"&amp;C53&amp;"_"&amp;D53,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G53" t="str">
+        <f>VLOOKUP("mvn_"&amp;A53&amp;"_"&amp;B53&amp;"_"&amp;C53&amp;"_"&amp;D53,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" t="str">
+        <f>VLOOKUP("npm_"&amp;A54&amp;"_"&amp;B54&amp;"_"&amp;C54&amp;"_"&amp;D54,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F54" t="str">
+        <f>VLOOKUP("pip_"&amp;A54&amp;"_"&amp;B54&amp;"_"&amp;C54&amp;"_"&amp;D54,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G54" t="str">
+        <f>VLOOKUP("mvn_"&amp;A54&amp;"_"&amp;B54&amp;"_"&amp;C54&amp;"_"&amp;D54,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" t="str">
+        <f>VLOOKUP("npm_"&amp;A55&amp;"_"&amp;B55&amp;"_"&amp;C55&amp;"_"&amp;D55,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F55" t="str">
+        <f>VLOOKUP("pip_"&amp;A55&amp;"_"&amp;B55&amp;"_"&amp;C55&amp;"_"&amp;D55,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G55" t="str">
+        <f>VLOOKUP("mvn_"&amp;A55&amp;"_"&amp;B55&amp;"_"&amp;C55&amp;"_"&amp;D55,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" t="str">
+        <f>VLOOKUP("npm_"&amp;A56&amp;"_"&amp;B56&amp;"_"&amp;C56&amp;"_"&amp;D56,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F56" t="str">
+        <f>VLOOKUP("pip_"&amp;A56&amp;"_"&amp;B56&amp;"_"&amp;C56&amp;"_"&amp;D56,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G56" t="str">
+        <f>VLOOKUP("mvn_"&amp;A56&amp;"_"&amp;B56&amp;"_"&amp;C56&amp;"_"&amp;D56,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" t="str">
+        <f>VLOOKUP("npm_"&amp;A57&amp;"_"&amp;B57&amp;"_"&amp;C57&amp;"_"&amp;D57,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F57" t="str">
+        <f>VLOOKUP("pip_"&amp;A57&amp;"_"&amp;B57&amp;"_"&amp;C57&amp;"_"&amp;D57,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G57" t="str">
+        <f>VLOOKUP("mvn_"&amp;A57&amp;"_"&amp;B57&amp;"_"&amp;C57&amp;"_"&amp;D57,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" t="str">
+        <f>VLOOKUP("npm_"&amp;A58&amp;"_"&amp;B58&amp;"_"&amp;C58&amp;"_"&amp;D58,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F58" t="str">
+        <f>VLOOKUP("pip_"&amp;A58&amp;"_"&amp;B58&amp;"_"&amp;C58&amp;"_"&amp;D58,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G58" t="str">
+        <f>VLOOKUP("mvn_"&amp;A58&amp;"_"&amp;B58&amp;"_"&amp;C58&amp;"_"&amp;D58,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" t="str">
+        <f>VLOOKUP("npm_"&amp;A59&amp;"_"&amp;B59&amp;"_"&amp;C59&amp;"_"&amp;D59,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F59" t="str">
+        <f>VLOOKUP("pip_"&amp;A59&amp;"_"&amp;B59&amp;"_"&amp;C59&amp;"_"&amp;D59,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G59" t="str">
+        <f>VLOOKUP("mvn_"&amp;A59&amp;"_"&amp;B59&amp;"_"&amp;C59&amp;"_"&amp;D59,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" t="str">
+        <f>VLOOKUP("npm_"&amp;A60&amp;"_"&amp;B60&amp;"_"&amp;C60&amp;"_"&amp;D60,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F60" t="str">
+        <f>VLOOKUP("pip_"&amp;A60&amp;"_"&amp;B60&amp;"_"&amp;C60&amp;"_"&amp;D60,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G60" t="str">
+        <f>VLOOKUP("mvn_"&amp;A60&amp;"_"&amp;B60&amp;"_"&amp;C60&amp;"_"&amp;D60,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" t="str">
+        <f>VLOOKUP("npm_"&amp;A61&amp;"_"&amp;B61&amp;"_"&amp;C61&amp;"_"&amp;D61,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F61" t="str">
+        <f>VLOOKUP("pip_"&amp;A61&amp;"_"&amp;B61&amp;"_"&amp;C61&amp;"_"&amp;D61,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G61" t="str">
+        <f>VLOOKUP("mvn_"&amp;A61&amp;"_"&amp;B61&amp;"_"&amp;C61&amp;"_"&amp;D61,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I61" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62" t="str">
+        <f>VLOOKUP("npm_"&amp;A62&amp;"_"&amp;B62&amp;"_"&amp;C62&amp;"_"&amp;D62,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F62" t="str">
+        <f>VLOOKUP("pip_"&amp;A62&amp;"_"&amp;B62&amp;"_"&amp;C62&amp;"_"&amp;D62,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G62" t="str">
+        <f>VLOOKUP("mvn_"&amp;A62&amp;"_"&amp;B62&amp;"_"&amp;C62&amp;"_"&amp;D62,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H62" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I62" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" t="str">
+        <f>VLOOKUP("npm_"&amp;A63&amp;"_"&amp;B63&amp;"_"&amp;C63&amp;"_"&amp;D63,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F63" t="str">
+        <f>VLOOKUP("pip_"&amp;A63&amp;"_"&amp;B63&amp;"_"&amp;C63&amp;"_"&amp;D63,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G63" t="str">
+        <f>VLOOKUP("mvn_"&amp;A63&amp;"_"&amp;B63&amp;"_"&amp;C63&amp;"_"&amp;D63,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H63" t="str">
+        <f t="shared" si="0"/>
+        <v>disagree</v>
+      </c>
+      <c r="I63" t="str">
+        <f t="shared" si="1"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" t="str">
+        <f>VLOOKUP("npm_"&amp;A64&amp;"_"&amp;B64&amp;"_"&amp;C64&amp;"_"&amp;D64,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F64" t="str">
+        <f>VLOOKUP("pip_"&amp;A64&amp;"_"&amp;B64&amp;"_"&amp;C64&amp;"_"&amp;D64,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G64" t="str">
+        <f>VLOOKUP("mvn_"&amp;A64&amp;"_"&amp;B64&amp;"_"&amp;C64&amp;"_"&amp;D64,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H64" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I64" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" t="str">
+        <f>VLOOKUP("npm_"&amp;A65&amp;"_"&amp;B65&amp;"_"&amp;C65&amp;"_"&amp;D65,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F65" t="str">
+        <f>VLOOKUP("pip_"&amp;A65&amp;"_"&amp;B65&amp;"_"&amp;C65&amp;"_"&amp;D65,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G65" t="str">
+        <f>VLOOKUP("mvn_"&amp;A65&amp;"_"&amp;B65&amp;"_"&amp;C65&amp;"_"&amp;D65,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H65" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I65" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" t="str">
+        <f>VLOOKUP("npm_"&amp;A66&amp;"_"&amp;B66&amp;"_"&amp;C66&amp;"_"&amp;D66,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F66" t="str">
+        <f>VLOOKUP("pip_"&amp;A66&amp;"_"&amp;B66&amp;"_"&amp;C66&amp;"_"&amp;D66,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G66" t="str">
+        <f>VLOOKUP("mvn_"&amp;A66&amp;"_"&amp;B66&amp;"_"&amp;C66&amp;"_"&amp;D66,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" si="0"/>
+        <v>agree</v>
+      </c>
+      <c r="I66" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" t="str">
+        <f>VLOOKUP("npm_"&amp;A67&amp;"_"&amp;B67&amp;"_"&amp;C67&amp;"_"&amp;D67,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F67" t="str">
+        <f>VLOOKUP("pip_"&amp;A67&amp;"_"&amp;B67&amp;"_"&amp;C67&amp;"_"&amp;D67,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G67" t="str">
+        <f>VLOOKUP("mvn_"&amp;A67&amp;"_"&amp;B67&amp;"_"&amp;C67&amp;"_"&amp;D67,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" ref="H67:H130" si="2">IF(COUNTIF(E67:G67,"&lt;&gt;invalid_configuration")&lt;2,"not comparable",IF(MAX(COUNTIF(E67:G67,"malicious_resolved"),COUNTIF(E67:G67,"private_resolved"),COUNTIF(E67:G67,"resolution_error"))=COUNTIF(E67:G67,"&lt;&gt;invalid_configuration"),"agree","disagree"))</f>
+        <v>agree</v>
+      </c>
+      <c r="I67" t="str">
+        <f t="shared" ref="I67:I130" si="3">IF(H67="disagree",IF(AND(E67&lt;&gt;F67,E67&lt;&gt;G67),"npm alone has different result",IF(AND(F67&lt;&gt;E67,F67&lt;&gt;G67),"pip alone has different result",IF(AND(G67&lt;&gt;E67,G67&lt;&gt;F67),"maven alone has different result","mixed"))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68" t="str">
+        <f>VLOOKUP("npm_"&amp;A68&amp;"_"&amp;B68&amp;"_"&amp;C68&amp;"_"&amp;D68,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F68" t="str">
+        <f>VLOOKUP("pip_"&amp;A68&amp;"_"&amp;B68&amp;"_"&amp;C68&amp;"_"&amp;D68,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G68" t="str">
+        <f>VLOOKUP("mvn_"&amp;A68&amp;"_"&amp;B68&amp;"_"&amp;C68&amp;"_"&amp;D68,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I68" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E69" t="str">
+        <f>VLOOKUP("npm_"&amp;A69&amp;"_"&amp;B69&amp;"_"&amp;C69&amp;"_"&amp;D69,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F69" t="str">
+        <f>VLOOKUP("pip_"&amp;A69&amp;"_"&amp;B69&amp;"_"&amp;C69&amp;"_"&amp;D69,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G69" t="str">
+        <f>VLOOKUP("mvn_"&amp;A69&amp;"_"&amp;B69&amp;"_"&amp;C69&amp;"_"&amp;D69,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I69" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70" t="str">
+        <f>VLOOKUP("npm_"&amp;A70&amp;"_"&amp;B70&amp;"_"&amp;C70&amp;"_"&amp;D70,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F70" t="str">
+        <f>VLOOKUP("pip_"&amp;A70&amp;"_"&amp;B70&amp;"_"&amp;C70&amp;"_"&amp;D70,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G70" t="str">
+        <f>VLOOKUP("mvn_"&amp;A70&amp;"_"&amp;B70&amp;"_"&amp;C70&amp;"_"&amp;D70,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H70" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I70" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" t="str">
+        <f>VLOOKUP("npm_"&amp;A71&amp;"_"&amp;B71&amp;"_"&amp;C71&amp;"_"&amp;D71,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F71" t="str">
+        <f>VLOOKUP("pip_"&amp;A71&amp;"_"&amp;B71&amp;"_"&amp;C71&amp;"_"&amp;D71,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G71" t="str">
+        <f>VLOOKUP("mvn_"&amp;A71&amp;"_"&amp;B71&amp;"_"&amp;C71&amp;"_"&amp;D71,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H71" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I71" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72" t="str">
+        <f>VLOOKUP("npm_"&amp;A72&amp;"_"&amp;B72&amp;"_"&amp;C72&amp;"_"&amp;D72,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F72" t="str">
+        <f>VLOOKUP("pip_"&amp;A72&amp;"_"&amp;B72&amp;"_"&amp;C72&amp;"_"&amp;D72,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G72" t="str">
+        <f>VLOOKUP("mvn_"&amp;A72&amp;"_"&amp;B72&amp;"_"&amp;C72&amp;"_"&amp;D72,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H72" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I72" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" t="str">
+        <f>VLOOKUP("npm_"&amp;A73&amp;"_"&amp;B73&amp;"_"&amp;C73&amp;"_"&amp;D73,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F73" t="str">
+        <f>VLOOKUP("pip_"&amp;A73&amp;"_"&amp;B73&amp;"_"&amp;C73&amp;"_"&amp;D73,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G73" t="str">
+        <f>VLOOKUP("mvn_"&amp;A73&amp;"_"&amp;B73&amp;"_"&amp;C73&amp;"_"&amp;D73,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H73" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I73" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" t="str">
+        <f>VLOOKUP("npm_"&amp;A74&amp;"_"&amp;B74&amp;"_"&amp;C74&amp;"_"&amp;D74,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F74" t="str">
+        <f>VLOOKUP("pip_"&amp;A74&amp;"_"&amp;B74&amp;"_"&amp;C74&amp;"_"&amp;D74,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G74" t="str">
+        <f>VLOOKUP("mvn_"&amp;A74&amp;"_"&amp;B74&amp;"_"&amp;C74&amp;"_"&amp;D74,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H74" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I74" t="str">
+        <f t="shared" si="3"/>
+        <v>maven alone has different result</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" t="str">
+        <f>VLOOKUP("npm_"&amp;A75&amp;"_"&amp;B75&amp;"_"&amp;C75&amp;"_"&amp;D75,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F75" t="str">
+        <f>VLOOKUP("pip_"&amp;A75&amp;"_"&amp;B75&amp;"_"&amp;C75&amp;"_"&amp;D75,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G75" t="str">
+        <f>VLOOKUP("mvn_"&amp;A75&amp;"_"&amp;B75&amp;"_"&amp;C75&amp;"_"&amp;D75,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H75" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I75" t="str">
+        <f t="shared" si="3"/>
+        <v>maven alone has different result</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E76" t="str">
+        <f>VLOOKUP("npm_"&amp;A76&amp;"_"&amp;B76&amp;"_"&amp;C76&amp;"_"&amp;D76,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F76" t="str">
+        <f>VLOOKUP("pip_"&amp;A76&amp;"_"&amp;B76&amp;"_"&amp;C76&amp;"_"&amp;D76,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G76" t="str">
+        <f>VLOOKUP("mvn_"&amp;A76&amp;"_"&amp;B76&amp;"_"&amp;C76&amp;"_"&amp;D76,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H76" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I76" t="str">
+        <f t="shared" si="3"/>
+        <v>maven alone has different result</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E77" t="str">
+        <f>VLOOKUP("npm_"&amp;A77&amp;"_"&amp;B77&amp;"_"&amp;C77&amp;"_"&amp;D77,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F77" t="str">
+        <f>VLOOKUP("pip_"&amp;A77&amp;"_"&amp;B77&amp;"_"&amp;C77&amp;"_"&amp;D77,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G77" t="str">
+        <f>VLOOKUP("mvn_"&amp;A77&amp;"_"&amp;B77&amp;"_"&amp;C77&amp;"_"&amp;D77,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H77" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I77" t="str">
+        <f t="shared" si="3"/>
+        <v>maven alone has different result</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E78" t="str">
+        <f>VLOOKUP("npm_"&amp;A78&amp;"_"&amp;B78&amp;"_"&amp;C78&amp;"_"&amp;D78,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F78" t="str">
+        <f>VLOOKUP("pip_"&amp;A78&amp;"_"&amp;B78&amp;"_"&amp;C78&amp;"_"&amp;D78,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G78" t="str">
+        <f>VLOOKUP("mvn_"&amp;A78&amp;"_"&amp;B78&amp;"_"&amp;C78&amp;"_"&amp;D78,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H78" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I78" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E79" t="str">
+        <f>VLOOKUP("npm_"&amp;A79&amp;"_"&amp;B79&amp;"_"&amp;C79&amp;"_"&amp;D79,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F79" t="str">
+        <f>VLOOKUP("pip_"&amp;A79&amp;"_"&amp;B79&amp;"_"&amp;C79&amp;"_"&amp;D79,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G79" t="str">
+        <f>VLOOKUP("mvn_"&amp;A79&amp;"_"&amp;B79&amp;"_"&amp;C79&amp;"_"&amp;D79,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H79" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I79" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E80" t="str">
+        <f>VLOOKUP("npm_"&amp;A80&amp;"_"&amp;B80&amp;"_"&amp;C80&amp;"_"&amp;D80,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F80" t="str">
+        <f>VLOOKUP("pip_"&amp;A80&amp;"_"&amp;B80&amp;"_"&amp;C80&amp;"_"&amp;D80,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G80" t="str">
+        <f>VLOOKUP("mvn_"&amp;A80&amp;"_"&amp;B80&amp;"_"&amp;C80&amp;"_"&amp;D80,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H80" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I80" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81" t="str">
+        <f>VLOOKUP("npm_"&amp;A81&amp;"_"&amp;B81&amp;"_"&amp;C81&amp;"_"&amp;D81,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F81" t="str">
+        <f>VLOOKUP("pip_"&amp;A81&amp;"_"&amp;B81&amp;"_"&amp;C81&amp;"_"&amp;D81,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G81" t="str">
+        <f>VLOOKUP("mvn_"&amp;A81&amp;"_"&amp;B81&amp;"_"&amp;C81&amp;"_"&amp;D81,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H81" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I81" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" t="str">
+        <f>VLOOKUP("npm_"&amp;A82&amp;"_"&amp;B82&amp;"_"&amp;C82&amp;"_"&amp;D82,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F82" t="str">
+        <f>VLOOKUP("pip_"&amp;A82&amp;"_"&amp;B82&amp;"_"&amp;C82&amp;"_"&amp;D82,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G82" t="str">
+        <f>VLOOKUP("mvn_"&amp;A82&amp;"_"&amp;B82&amp;"_"&amp;C82&amp;"_"&amp;D82,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H82" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I82" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E83" t="str">
+        <f>VLOOKUP("npm_"&amp;A83&amp;"_"&amp;B83&amp;"_"&amp;C83&amp;"_"&amp;D83,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F83" t="str">
+        <f>VLOOKUP("pip_"&amp;A83&amp;"_"&amp;B83&amp;"_"&amp;C83&amp;"_"&amp;D83,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G83" t="str">
+        <f>VLOOKUP("mvn_"&amp;A83&amp;"_"&amp;B83&amp;"_"&amp;C83&amp;"_"&amp;D83,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H83" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I83" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E84" t="str">
+        <f>VLOOKUP("npm_"&amp;A84&amp;"_"&amp;B84&amp;"_"&amp;C84&amp;"_"&amp;D84,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F84" t="str">
+        <f>VLOOKUP("pip_"&amp;A84&amp;"_"&amp;B84&amp;"_"&amp;C84&amp;"_"&amp;D84,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G84" t="str">
+        <f>VLOOKUP("mvn_"&amp;A84&amp;"_"&amp;B84&amp;"_"&amp;C84&amp;"_"&amp;D84,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H84" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I84" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E85" t="str">
+        <f>VLOOKUP("npm_"&amp;A85&amp;"_"&amp;B85&amp;"_"&amp;C85&amp;"_"&amp;D85,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F85" t="str">
+        <f>VLOOKUP("pip_"&amp;A85&amp;"_"&amp;B85&amp;"_"&amp;C85&amp;"_"&amp;D85,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G85" t="str">
+        <f>VLOOKUP("mvn_"&amp;A85&amp;"_"&amp;B85&amp;"_"&amp;C85&amp;"_"&amp;D85,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H85" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I85" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E86" t="str">
+        <f>VLOOKUP("npm_"&amp;A86&amp;"_"&amp;B86&amp;"_"&amp;C86&amp;"_"&amp;D86,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F86" t="str">
+        <f>VLOOKUP("pip_"&amp;A86&amp;"_"&amp;B86&amp;"_"&amp;C86&amp;"_"&amp;D86,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G86" t="str">
+        <f>VLOOKUP("mvn_"&amp;A86&amp;"_"&amp;B86&amp;"_"&amp;C86&amp;"_"&amp;D86,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H86" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I86" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E87" t="str">
+        <f>VLOOKUP("npm_"&amp;A87&amp;"_"&amp;B87&amp;"_"&amp;C87&amp;"_"&amp;D87,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F87" t="str">
+        <f>VLOOKUP("pip_"&amp;A87&amp;"_"&amp;B87&amp;"_"&amp;C87&amp;"_"&amp;D87,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G87" t="str">
+        <f>VLOOKUP("mvn_"&amp;A87&amp;"_"&amp;B87&amp;"_"&amp;C87&amp;"_"&amp;D87,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H87" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I87" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" t="str">
+        <f>VLOOKUP("npm_"&amp;A88&amp;"_"&amp;B88&amp;"_"&amp;C88&amp;"_"&amp;D88,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F88" t="str">
+        <f>VLOOKUP("pip_"&amp;A88&amp;"_"&amp;B88&amp;"_"&amp;C88&amp;"_"&amp;D88,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G88" t="str">
+        <f>VLOOKUP("mvn_"&amp;A88&amp;"_"&amp;B88&amp;"_"&amp;C88&amp;"_"&amp;D88,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H88" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I88" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E89" t="str">
+        <f>VLOOKUP("npm_"&amp;A89&amp;"_"&amp;B89&amp;"_"&amp;C89&amp;"_"&amp;D89,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F89" t="str">
+        <f>VLOOKUP("pip_"&amp;A89&amp;"_"&amp;B89&amp;"_"&amp;C89&amp;"_"&amp;D89,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G89" t="str">
+        <f>VLOOKUP("mvn_"&amp;A89&amp;"_"&amp;B89&amp;"_"&amp;C89&amp;"_"&amp;D89,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H89" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I89" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E90" t="str">
+        <f>VLOOKUP("npm_"&amp;A90&amp;"_"&amp;B90&amp;"_"&amp;C90&amp;"_"&amp;D90,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F90" t="str">
+        <f>VLOOKUP("pip_"&amp;A90&amp;"_"&amp;B90&amp;"_"&amp;C90&amp;"_"&amp;D90,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G90" t="str">
+        <f>VLOOKUP("mvn_"&amp;A90&amp;"_"&amp;B90&amp;"_"&amp;C90&amp;"_"&amp;D90,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H90" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I90" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E91" t="str">
+        <f>VLOOKUP("npm_"&amp;A91&amp;"_"&amp;B91&amp;"_"&amp;C91&amp;"_"&amp;D91,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F91" t="str">
+        <f>VLOOKUP("pip_"&amp;A91&amp;"_"&amp;B91&amp;"_"&amp;C91&amp;"_"&amp;D91,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G91" t="str">
+        <f>VLOOKUP("mvn_"&amp;A91&amp;"_"&amp;B91&amp;"_"&amp;C91&amp;"_"&amp;D91,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H91" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I91" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E92" t="str">
+        <f>VLOOKUP("npm_"&amp;A92&amp;"_"&amp;B92&amp;"_"&amp;C92&amp;"_"&amp;D92,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F92" t="str">
+        <f>VLOOKUP("pip_"&amp;A92&amp;"_"&amp;B92&amp;"_"&amp;C92&amp;"_"&amp;D92,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G92" t="str">
+        <f>VLOOKUP("mvn_"&amp;A92&amp;"_"&amp;B92&amp;"_"&amp;C92&amp;"_"&amp;D92,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H92" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I92" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E93" t="str">
+        <f>VLOOKUP("npm_"&amp;A93&amp;"_"&amp;B93&amp;"_"&amp;C93&amp;"_"&amp;D93,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F93" t="str">
+        <f>VLOOKUP("pip_"&amp;A93&amp;"_"&amp;B93&amp;"_"&amp;C93&amp;"_"&amp;D93,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G93" t="str">
+        <f>VLOOKUP("mvn_"&amp;A93&amp;"_"&amp;B93&amp;"_"&amp;C93&amp;"_"&amp;D93,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H93" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I93" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E94" t="str">
+        <f>VLOOKUP("npm_"&amp;A94&amp;"_"&amp;B94&amp;"_"&amp;C94&amp;"_"&amp;D94,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F94" t="str">
+        <f>VLOOKUP("pip_"&amp;A94&amp;"_"&amp;B94&amp;"_"&amp;C94&amp;"_"&amp;D94,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G94" t="str">
+        <f>VLOOKUP("mvn_"&amp;A94&amp;"_"&amp;B94&amp;"_"&amp;C94&amp;"_"&amp;D94,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H94" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I94" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E95" t="str">
+        <f>VLOOKUP("npm_"&amp;A95&amp;"_"&amp;B95&amp;"_"&amp;C95&amp;"_"&amp;D95,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F95" t="str">
+        <f>VLOOKUP("pip_"&amp;A95&amp;"_"&amp;B95&amp;"_"&amp;C95&amp;"_"&amp;D95,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G95" t="str">
+        <f>VLOOKUP("mvn_"&amp;A95&amp;"_"&amp;B95&amp;"_"&amp;C95&amp;"_"&amp;D95,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H95" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I95" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E96" t="str">
+        <f>VLOOKUP("npm_"&amp;A96&amp;"_"&amp;B96&amp;"_"&amp;C96&amp;"_"&amp;D96,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F96" t="str">
+        <f>VLOOKUP("pip_"&amp;A96&amp;"_"&amp;B96&amp;"_"&amp;C96&amp;"_"&amp;D96,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G96" t="str">
+        <f>VLOOKUP("mvn_"&amp;A96&amp;"_"&amp;B96&amp;"_"&amp;C96&amp;"_"&amp;D96,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H96" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I96" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E97" t="str">
+        <f>VLOOKUP("npm_"&amp;A97&amp;"_"&amp;B97&amp;"_"&amp;C97&amp;"_"&amp;D97,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F97" t="str">
+        <f>VLOOKUP("pip_"&amp;A97&amp;"_"&amp;B97&amp;"_"&amp;C97&amp;"_"&amp;D97,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G97" t="str">
+        <f>VLOOKUP("mvn_"&amp;A97&amp;"_"&amp;B97&amp;"_"&amp;C97&amp;"_"&amp;D97,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H97" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I97" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E98" t="str">
+        <f>VLOOKUP("npm_"&amp;A98&amp;"_"&amp;B98&amp;"_"&amp;C98&amp;"_"&amp;D98,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F98" t="str">
+        <f>VLOOKUP("pip_"&amp;A98&amp;"_"&amp;B98&amp;"_"&amp;C98&amp;"_"&amp;D98,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G98" t="str">
+        <f>VLOOKUP("mvn_"&amp;A98&amp;"_"&amp;B98&amp;"_"&amp;C98&amp;"_"&amp;D98,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H98" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I98" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E99" t="str">
+        <f>VLOOKUP("npm_"&amp;A99&amp;"_"&amp;B99&amp;"_"&amp;C99&amp;"_"&amp;D99,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F99" t="str">
+        <f>VLOOKUP("pip_"&amp;A99&amp;"_"&amp;B99&amp;"_"&amp;C99&amp;"_"&amp;D99,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G99" t="str">
+        <f>VLOOKUP("mvn_"&amp;A99&amp;"_"&amp;B99&amp;"_"&amp;C99&amp;"_"&amp;D99,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H99" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I99" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E100" t="str">
+        <f>VLOOKUP("npm_"&amp;A100&amp;"_"&amp;B100&amp;"_"&amp;C100&amp;"_"&amp;D100,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F100" t="str">
+        <f>VLOOKUP("pip_"&amp;A100&amp;"_"&amp;B100&amp;"_"&amp;C100&amp;"_"&amp;D100,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G100" t="str">
+        <f>VLOOKUP("mvn_"&amp;A100&amp;"_"&amp;B100&amp;"_"&amp;C100&amp;"_"&amp;D100,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H100" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I100" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E101" t="str">
+        <f>VLOOKUP("npm_"&amp;A101&amp;"_"&amp;B101&amp;"_"&amp;C101&amp;"_"&amp;D101,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F101" t="str">
+        <f>VLOOKUP("pip_"&amp;A101&amp;"_"&amp;B101&amp;"_"&amp;C101&amp;"_"&amp;D101,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G101" t="str">
+        <f>VLOOKUP("mvn_"&amp;A101&amp;"_"&amp;B101&amp;"_"&amp;C101&amp;"_"&amp;D101,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H101" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I101" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E102" t="str">
+        <f>VLOOKUP("npm_"&amp;A102&amp;"_"&amp;B102&amp;"_"&amp;C102&amp;"_"&amp;D102,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F102" t="str">
+        <f>VLOOKUP("pip_"&amp;A102&amp;"_"&amp;B102&amp;"_"&amp;C102&amp;"_"&amp;D102,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G102" t="str">
+        <f>VLOOKUP("mvn_"&amp;A102&amp;"_"&amp;B102&amp;"_"&amp;C102&amp;"_"&amp;D102,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H102" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I102" t="str">
+        <f t="shared" si="3"/>
+        <v>pip alone has different result</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E103" t="str">
+        <f>VLOOKUP("npm_"&amp;A103&amp;"_"&amp;B103&amp;"_"&amp;C103&amp;"_"&amp;D103,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F103" t="str">
+        <f>VLOOKUP("pip_"&amp;A103&amp;"_"&amp;B103&amp;"_"&amp;C103&amp;"_"&amp;D103,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G103" t="str">
+        <f>VLOOKUP("mvn_"&amp;A103&amp;"_"&amp;B103&amp;"_"&amp;C103&amp;"_"&amp;D103,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H103" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I103" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E104" t="str">
+        <f>VLOOKUP("npm_"&amp;A104&amp;"_"&amp;B104&amp;"_"&amp;C104&amp;"_"&amp;D104,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F104" t="str">
+        <f>VLOOKUP("pip_"&amp;A104&amp;"_"&amp;B104&amp;"_"&amp;C104&amp;"_"&amp;D104,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G104" t="str">
+        <f>VLOOKUP("mvn_"&amp;A104&amp;"_"&amp;B104&amp;"_"&amp;C104&amp;"_"&amp;D104,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H104" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I104" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E105" t="str">
+        <f>VLOOKUP("npm_"&amp;A105&amp;"_"&amp;B105&amp;"_"&amp;C105&amp;"_"&amp;D105,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F105" t="str">
+        <f>VLOOKUP("pip_"&amp;A105&amp;"_"&amp;B105&amp;"_"&amp;C105&amp;"_"&amp;D105,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G105" t="str">
+        <f>VLOOKUP("mvn_"&amp;A105&amp;"_"&amp;B105&amp;"_"&amp;C105&amp;"_"&amp;D105,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H105" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I105" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E106" t="str">
+        <f>VLOOKUP("npm_"&amp;A106&amp;"_"&amp;B106&amp;"_"&amp;C106&amp;"_"&amp;D106,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F106" t="str">
+        <f>VLOOKUP("pip_"&amp;A106&amp;"_"&amp;B106&amp;"_"&amp;C106&amp;"_"&amp;D106,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G106" t="str">
+        <f>VLOOKUP("mvn_"&amp;A106&amp;"_"&amp;B106&amp;"_"&amp;C106&amp;"_"&amp;D106,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H106" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I106" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E107" t="str">
+        <f>VLOOKUP("npm_"&amp;A107&amp;"_"&amp;B107&amp;"_"&amp;C107&amp;"_"&amp;D107,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F107" t="str">
+        <f>VLOOKUP("pip_"&amp;A107&amp;"_"&amp;B107&amp;"_"&amp;C107&amp;"_"&amp;D107,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G107" t="str">
+        <f>VLOOKUP("mvn_"&amp;A107&amp;"_"&amp;B107&amp;"_"&amp;C107&amp;"_"&amp;D107,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H107" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I107" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E108" t="str">
+        <f>VLOOKUP("npm_"&amp;A108&amp;"_"&amp;B108&amp;"_"&amp;C108&amp;"_"&amp;D108,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F108" t="str">
+        <f>VLOOKUP("pip_"&amp;A108&amp;"_"&amp;B108&amp;"_"&amp;C108&amp;"_"&amp;D108,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G108" t="str">
+        <f>VLOOKUP("mvn_"&amp;A108&amp;"_"&amp;B108&amp;"_"&amp;C108&amp;"_"&amp;D108,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H108" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I108" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E109" t="str">
+        <f>VLOOKUP("npm_"&amp;A109&amp;"_"&amp;B109&amp;"_"&amp;C109&amp;"_"&amp;D109,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F109" t="str">
+        <f>VLOOKUP("pip_"&amp;A109&amp;"_"&amp;B109&amp;"_"&amp;C109&amp;"_"&amp;D109,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G109" t="str">
+        <f>VLOOKUP("mvn_"&amp;A109&amp;"_"&amp;B109&amp;"_"&amp;C109&amp;"_"&amp;D109,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H109" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I109" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E110" t="str">
+        <f>VLOOKUP("npm_"&amp;A110&amp;"_"&amp;B110&amp;"_"&amp;C110&amp;"_"&amp;D110,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F110" t="str">
+        <f>VLOOKUP("pip_"&amp;A110&amp;"_"&amp;B110&amp;"_"&amp;C110&amp;"_"&amp;D110,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G110" t="str">
+        <f>VLOOKUP("mvn_"&amp;A110&amp;"_"&amp;B110&amp;"_"&amp;C110&amp;"_"&amp;D110,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H110" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I110" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E111" t="str">
+        <f>VLOOKUP("npm_"&amp;A111&amp;"_"&amp;B111&amp;"_"&amp;C111&amp;"_"&amp;D111,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F111" t="str">
+        <f>VLOOKUP("pip_"&amp;A111&amp;"_"&amp;B111&amp;"_"&amp;C111&amp;"_"&amp;D111,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G111" t="str">
+        <f>VLOOKUP("mvn_"&amp;A111&amp;"_"&amp;B111&amp;"_"&amp;C111&amp;"_"&amp;D111,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H111" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I111" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E112" t="str">
+        <f>VLOOKUP("npm_"&amp;A112&amp;"_"&amp;B112&amp;"_"&amp;C112&amp;"_"&amp;D112,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F112" t="str">
+        <f>VLOOKUP("pip_"&amp;A112&amp;"_"&amp;B112&amp;"_"&amp;C112&amp;"_"&amp;D112,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G112" t="str">
+        <f>VLOOKUP("mvn_"&amp;A112&amp;"_"&amp;B112&amp;"_"&amp;C112&amp;"_"&amp;D112,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H112" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I112" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A113" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E113" t="str">
+        <f>VLOOKUP("npm_"&amp;A113&amp;"_"&amp;B113&amp;"_"&amp;C113&amp;"_"&amp;D113,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F113" t="str">
+        <f>VLOOKUP("pip_"&amp;A113&amp;"_"&amp;B113&amp;"_"&amp;C113&amp;"_"&amp;D113,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G113" t="str">
+        <f>VLOOKUP("mvn_"&amp;A113&amp;"_"&amp;B113&amp;"_"&amp;C113&amp;"_"&amp;D113,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H113" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I113" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E114" t="str">
+        <f>VLOOKUP("npm_"&amp;A114&amp;"_"&amp;B114&amp;"_"&amp;C114&amp;"_"&amp;D114,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F114" t="str">
+        <f>VLOOKUP("pip_"&amp;A114&amp;"_"&amp;B114&amp;"_"&amp;C114&amp;"_"&amp;D114,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G114" t="str">
+        <f>VLOOKUP("mvn_"&amp;A114&amp;"_"&amp;B114&amp;"_"&amp;C114&amp;"_"&amp;D114,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H114" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I114" t="str">
+        <f t="shared" si="3"/>
+        <v>pip alone has different result</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E115" t="str">
+        <f>VLOOKUP("npm_"&amp;A115&amp;"_"&amp;B115&amp;"_"&amp;C115&amp;"_"&amp;D115,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F115" t="str">
+        <f>VLOOKUP("pip_"&amp;A115&amp;"_"&amp;B115&amp;"_"&amp;C115&amp;"_"&amp;D115,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G115" t="str">
+        <f>VLOOKUP("mvn_"&amp;A115&amp;"_"&amp;B115&amp;"_"&amp;C115&amp;"_"&amp;D115,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H115" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I115" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E116" t="str">
+        <f>VLOOKUP("npm_"&amp;A116&amp;"_"&amp;B116&amp;"_"&amp;C116&amp;"_"&amp;D116,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F116" t="str">
+        <f>VLOOKUP("pip_"&amp;A116&amp;"_"&amp;B116&amp;"_"&amp;C116&amp;"_"&amp;D116,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G116" t="str">
+        <f>VLOOKUP("mvn_"&amp;A116&amp;"_"&amp;B116&amp;"_"&amp;C116&amp;"_"&amp;D116,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H116" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I116" t="str">
+        <f t="shared" si="3"/>
+        <v>pip alone has different result</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A117" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E117" t="str">
+        <f>VLOOKUP("npm_"&amp;A117&amp;"_"&amp;B117&amp;"_"&amp;C117&amp;"_"&amp;D117,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F117" t="str">
+        <f>VLOOKUP("pip_"&amp;A117&amp;"_"&amp;B117&amp;"_"&amp;C117&amp;"_"&amp;D117,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G117" t="str">
+        <f>VLOOKUP("mvn_"&amp;A117&amp;"_"&amp;B117&amp;"_"&amp;C117&amp;"_"&amp;D117,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H117" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I117" t="str">
+        <f t="shared" si="3"/>
+        <v>pip alone has different result</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E118" t="str">
+        <f>VLOOKUP("npm_"&amp;A118&amp;"_"&amp;B118&amp;"_"&amp;C118&amp;"_"&amp;D118,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F118" t="str">
+        <f>VLOOKUP("pip_"&amp;A118&amp;"_"&amp;B118&amp;"_"&amp;C118&amp;"_"&amp;D118,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G118" t="str">
+        <f>VLOOKUP("mvn_"&amp;A118&amp;"_"&amp;B118&amp;"_"&amp;C118&amp;"_"&amp;D118,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H118" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I118" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E119" t="str">
+        <f>VLOOKUP("npm_"&amp;A119&amp;"_"&amp;B119&amp;"_"&amp;C119&amp;"_"&amp;D119,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F119" t="str">
+        <f>VLOOKUP("pip_"&amp;A119&amp;"_"&amp;B119&amp;"_"&amp;C119&amp;"_"&amp;D119,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G119" t="str">
+        <f>VLOOKUP("mvn_"&amp;A119&amp;"_"&amp;B119&amp;"_"&amp;C119&amp;"_"&amp;D119,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H119" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I119" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E120" t="str">
+        <f>VLOOKUP("npm_"&amp;A120&amp;"_"&amp;B120&amp;"_"&amp;C120&amp;"_"&amp;D120,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F120" t="str">
+        <f>VLOOKUP("pip_"&amp;A120&amp;"_"&amp;B120&amp;"_"&amp;C120&amp;"_"&amp;D120,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G120" t="str">
+        <f>VLOOKUP("mvn_"&amp;A120&amp;"_"&amp;B120&amp;"_"&amp;C120&amp;"_"&amp;D120,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H120" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I120" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E121" t="str">
+        <f>VLOOKUP("npm_"&amp;A121&amp;"_"&amp;B121&amp;"_"&amp;C121&amp;"_"&amp;D121,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F121" t="str">
+        <f>VLOOKUP("pip_"&amp;A121&amp;"_"&amp;B121&amp;"_"&amp;C121&amp;"_"&amp;D121,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G121" t="str">
+        <f>VLOOKUP("mvn_"&amp;A121&amp;"_"&amp;B121&amp;"_"&amp;C121&amp;"_"&amp;D121,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H121" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I121" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E122" t="str">
+        <f>VLOOKUP("npm_"&amp;A122&amp;"_"&amp;B122&amp;"_"&amp;C122&amp;"_"&amp;D122,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F122" t="str">
+        <f>VLOOKUP("pip_"&amp;A122&amp;"_"&amp;B122&amp;"_"&amp;C122&amp;"_"&amp;D122,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G122" t="str">
+        <f>VLOOKUP("mvn_"&amp;A122&amp;"_"&amp;B122&amp;"_"&amp;C122&amp;"_"&amp;D122,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H122" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I122" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E123" t="str">
+        <f>VLOOKUP("npm_"&amp;A123&amp;"_"&amp;B123&amp;"_"&amp;C123&amp;"_"&amp;D123,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F123" t="str">
+        <f>VLOOKUP("pip_"&amp;A123&amp;"_"&amp;B123&amp;"_"&amp;C123&amp;"_"&amp;D123,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G123" t="str">
+        <f>VLOOKUP("mvn_"&amp;A123&amp;"_"&amp;B123&amp;"_"&amp;C123&amp;"_"&amp;D123,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H123" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I123" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E124" t="str">
+        <f>VLOOKUP("npm_"&amp;A124&amp;"_"&amp;B124&amp;"_"&amp;C124&amp;"_"&amp;D124,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F124" t="str">
+        <f>VLOOKUP("pip_"&amp;A124&amp;"_"&amp;B124&amp;"_"&amp;C124&amp;"_"&amp;D124,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G124" t="str">
+        <f>VLOOKUP("mvn_"&amp;A124&amp;"_"&amp;B124&amp;"_"&amp;C124&amp;"_"&amp;D124,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H124" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I124" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E125" t="str">
+        <f>VLOOKUP("npm_"&amp;A125&amp;"_"&amp;B125&amp;"_"&amp;C125&amp;"_"&amp;D125,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F125" t="str">
+        <f>VLOOKUP("pip_"&amp;A125&amp;"_"&amp;B125&amp;"_"&amp;C125&amp;"_"&amp;D125,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G125" t="str">
+        <f>VLOOKUP("mvn_"&amp;A125&amp;"_"&amp;B125&amp;"_"&amp;C125&amp;"_"&amp;D125,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H125" t="str">
+        <f t="shared" si="2"/>
+        <v>agree</v>
+      </c>
+      <c r="I125" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E126" t="str">
+        <f>VLOOKUP("npm_"&amp;A126&amp;"_"&amp;B126&amp;"_"&amp;C126&amp;"_"&amp;D126,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F126" t="str">
+        <f>VLOOKUP("pip_"&amp;A126&amp;"_"&amp;B126&amp;"_"&amp;C126&amp;"_"&amp;D126,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G126" t="str">
+        <f>VLOOKUP("mvn_"&amp;A126&amp;"_"&amp;B126&amp;"_"&amp;C126&amp;"_"&amp;D126,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H126" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I126" t="str">
+        <f t="shared" si="3"/>
+        <v>pip alone has different result</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E127" t="str">
+        <f>VLOOKUP("npm_"&amp;A127&amp;"_"&amp;B127&amp;"_"&amp;C127&amp;"_"&amp;D127,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F127" t="str">
+        <f>VLOOKUP("pip_"&amp;A127&amp;"_"&amp;B127&amp;"_"&amp;C127&amp;"_"&amp;D127,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G127" t="str">
+        <f>VLOOKUP("mvn_"&amp;A127&amp;"_"&amp;B127&amp;"_"&amp;C127&amp;"_"&amp;D127,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H127" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I127" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E128" t="str">
+        <f>VLOOKUP("npm_"&amp;A128&amp;"_"&amp;B128&amp;"_"&amp;C128&amp;"_"&amp;D128,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F128" t="str">
+        <f>VLOOKUP("pip_"&amp;A128&amp;"_"&amp;B128&amp;"_"&amp;C128&amp;"_"&amp;D128,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G128" t="str">
+        <f>VLOOKUP("mvn_"&amp;A128&amp;"_"&amp;B128&amp;"_"&amp;C128&amp;"_"&amp;D128,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H128" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I128" t="str">
+        <f t="shared" si="3"/>
+        <v>pip alone has different result</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D129" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="E129" t="str">
+        <f>VLOOKUP("npm_"&amp;A129&amp;"_"&amp;B129&amp;"_"&amp;C129&amp;"_"&amp;D129,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F129" t="str">
+        <f>VLOOKUP("pip_"&amp;A129&amp;"_"&amp;B129&amp;"_"&amp;C129&amp;"_"&amp;D129,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G129" t="str">
+        <f>VLOOKUP("mvn_"&amp;A129&amp;"_"&amp;B129&amp;"_"&amp;C129&amp;"_"&amp;D129,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H129" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I129" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E130" t="str">
+        <f>VLOOKUP("npm_"&amp;A130&amp;"_"&amp;B130&amp;"_"&amp;C130&amp;"_"&amp;D130,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="F130" t="str">
+        <f>VLOOKUP("pip_"&amp;A130&amp;"_"&amp;B130&amp;"_"&amp;C130&amp;"_"&amp;D130,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G130" t="str">
+        <f>VLOOKUP("mvn_"&amp;A130&amp;"_"&amp;B130&amp;"_"&amp;C130&amp;"_"&amp;D130,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H130" t="str">
+        <f t="shared" si="2"/>
+        <v>disagree</v>
+      </c>
+      <c r="I130" t="str">
+        <f t="shared" si="3"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A131" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E131" t="str">
+        <f>VLOOKUP("npm_"&amp;A131&amp;"_"&amp;B131&amp;"_"&amp;C131&amp;"_"&amp;D131,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F131" t="str">
+        <f>VLOOKUP("pip_"&amp;A131&amp;"_"&amp;B131&amp;"_"&amp;C131&amp;"_"&amp;D131,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="G131" t="str">
+        <f>VLOOKUP("mvn_"&amp;A131&amp;"_"&amp;B131&amp;"_"&amp;C131&amp;"_"&amp;D131,'results'!$A:$H,8,FALSE)</f>
+        <v>private_resolved</v>
+      </c>
+      <c r="H131" t="str">
+        <f t="shared" ref="H131:H145" si="4">IF(COUNTIF(E131:G131,"&lt;&gt;invalid_configuration")&lt;2,"not comparable",IF(MAX(COUNTIF(E131:G131,"malicious_resolved"),COUNTIF(E131:G131,"private_resolved"),COUNTIF(E131:G131,"resolution_error"))=COUNTIF(E131:G131,"&lt;&gt;invalid_configuration"),"agree","disagree"))</f>
+        <v>disagree</v>
+      </c>
+      <c r="I131" t="str">
+        <f t="shared" ref="I131:I145" si="5">IF(H131="disagree",IF(AND(E131&lt;&gt;F131,E131&lt;&gt;G131),"npm alone has different result",IF(AND(F131&lt;&gt;E131,F131&lt;&gt;G131),"pip alone has different result",IF(AND(G131&lt;&gt;E131,G131&lt;&gt;F131),"maven alone has different result","mixed"))),"")</f>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E132" t="str">
+        <f>VLOOKUP("npm_"&amp;A132&amp;"_"&amp;B132&amp;"_"&amp;C132&amp;"_"&amp;D132,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F132" t="str">
+        <f>VLOOKUP("pip_"&amp;A132&amp;"_"&amp;B132&amp;"_"&amp;C132&amp;"_"&amp;D132,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G132" t="str">
+        <f>VLOOKUP("mvn_"&amp;A132&amp;"_"&amp;B132&amp;"_"&amp;C132&amp;"_"&amp;D132,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H132" t="str">
+        <f t="shared" si="4"/>
+        <v>agree</v>
+      </c>
+      <c r="I132" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A133" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E133" t="str">
+        <f>VLOOKUP("npm_"&amp;A133&amp;"_"&amp;B133&amp;"_"&amp;C133&amp;"_"&amp;D133,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F133" t="str">
+        <f>VLOOKUP("pip_"&amp;A133&amp;"_"&amp;B133&amp;"_"&amp;C133&amp;"_"&amp;D133,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="G133" t="str">
+        <f>VLOOKUP("mvn_"&amp;A133&amp;"_"&amp;B133&amp;"_"&amp;C133&amp;"_"&amp;D133,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H133" t="str">
+        <f t="shared" si="4"/>
+        <v>agree</v>
+      </c>
+      <c r="I133" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E134" t="str">
+        <f>VLOOKUP("npm_"&amp;A134&amp;"_"&amp;B134&amp;"_"&amp;C134&amp;"_"&amp;D134,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="F134" t="str">
+        <f>VLOOKUP("pip_"&amp;A134&amp;"_"&amp;B134&amp;"_"&amp;C134&amp;"_"&amp;D134,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G134" t="str">
+        <f>VLOOKUP("mvn_"&amp;A134&amp;"_"&amp;B134&amp;"_"&amp;C134&amp;"_"&amp;D134,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="H134" t="str">
+        <f t="shared" si="4"/>
+        <v>agree</v>
+      </c>
+      <c r="I134" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A135" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E135" t="str">
+        <f>VLOOKUP("npm_"&amp;A135&amp;"_"&amp;B135&amp;"_"&amp;C135&amp;"_"&amp;D135,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F135" t="str">
+        <f>VLOOKUP("pip_"&amp;A135&amp;"_"&amp;B135&amp;"_"&amp;C135&amp;"_"&amp;D135,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G135" t="str">
+        <f>VLOOKUP("mvn_"&amp;A135&amp;"_"&amp;B135&amp;"_"&amp;C135&amp;"_"&amp;D135,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="H135" t="str">
+        <f t="shared" si="4"/>
+        <v>disagree</v>
+      </c>
+      <c r="I135" t="str">
+        <f t="shared" si="5"/>
+        <v>pip alone has different result</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E136" t="str">
+        <f>VLOOKUP("npm_"&amp;A136&amp;"_"&amp;B136&amp;"_"&amp;C136&amp;"_"&amp;D136,'results'!$A:$H,8,FALSE)</f>
+        <v>malicious_resolved</v>
+      </c>
+      <c r="F136" t="str">
+        <f>VLOOKUP("pip_"&amp;A136&amp;"_"&amp;B136&amp;"_"&amp;C136&amp;"_"&amp;D136,'results'!$A:$H,8,FALSE)</f>
+        <v>resolution_error</v>
+      </c>
+      <c r="G136" t="str">
+        <f>VLOOKUP("mvn_"&amp;A136&amp;"_"&amp;B136&amp;"_"&amp;C136&amp;"_"&amp;D136,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H136" t="str">
+        <f t="shared" si="4"/>
+        <v>disagree</v>
+      </c>
+      <c r="I136" t="str">
+        <f t="shared" si="5"/>
+        <v>npm alone has different result</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A137" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E137" t="str">
+        <f>VLOOKUP("npm_"&amp;A137&amp;"_"&amp;B137&amp;"_"&amp;C137&amp;"_"&amp;D137,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="F137" t="str">
+        <f>VLOOKUP("pip_"&amp;A137&amp;"_"&amp;B137&amp;"_"&amp;C137&amp;"_"&amp;D137,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="G137" t="str">
+        <f>VLOOKUP("mvn_"&amp;A137&amp;"_"&amp;B137&amp;"_"&amp;C137&amp;"_"&amp;D137,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H137" t="str">
+        <f t="shared" si="4"/>
+        <v>not comparable</v>
+      </c>
+      <c r="I137" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E138" t="str">
+        <f>VLOOKUP("npm_"&amp;A138&amp;"_"&amp;B138&amp;"_"&amp;C138&amp;"_"&amp;D138,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="F138" t="str">
+        <f>VLOOKUP("pip_"&amp;A138&amp;"_"&amp;B138&amp;"_"&amp;C138&amp;"_"&amp;D138,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="G138" t="str">
+        <f>VLOOKUP("mvn_"&amp;A138&amp;"_"&amp;B138&amp;"_"&amp;C138&amp;"_"&amp;D138,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H138" t="str">
+        <f t="shared" si="4"/>
+        <v>not comparable</v>
+      </c>
+      <c r="I138" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A139" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E139" t="str">
+        <f>VLOOKUP("npm_"&amp;A139&amp;"_"&amp;B139&amp;"_"&amp;C139&amp;"_"&amp;D139,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="F139" t="str">
+        <f>VLOOKUP("pip_"&amp;A139&amp;"_"&amp;B139&amp;"_"&amp;C139&amp;"_"&amp;D139,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="G139" t="str">
+        <f>VLOOKUP("mvn_"&amp;A139&amp;"_"&amp;B139&amp;"_"&amp;C139&amp;"_"&amp;D139,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H139" t="str">
+        <f t="shared" si="4"/>
+        <v>not comparable</v>
+      </c>
+      <c r="I139" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E140" t="str">
+        <f>VLOOKUP("npm_"&amp;A140&amp;"_"&amp;B140&amp;"_"&amp;C140&amp;"_"&amp;D140,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="F140" t="str">
+        <f>VLOOKUP("pip_"&amp;A140&amp;"_"&amp;B140&amp;"_"&amp;C140&amp;"_"&amp;D140,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="G140" t="str">
+        <f>VLOOKUP("mvn_"&amp;A140&amp;"_"&amp;B140&amp;"_"&amp;C140&amp;"_"&amp;D140,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H140" t="str">
+        <f t="shared" si="4"/>
+        <v>not comparable</v>
+      </c>
+      <c r="I140" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A141" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E141" t="str">
+        <f>VLOOKUP("npm_"&amp;A141&amp;"_"&amp;B141&amp;"_"&amp;C141&amp;"_"&amp;D141,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="F141" t="str">
+        <f>VLOOKUP("pip_"&amp;A141&amp;"_"&amp;B141&amp;"_"&amp;C141&amp;"_"&amp;D141,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="G141" t="str">
+        <f>VLOOKUP("mvn_"&amp;A141&amp;"_"&amp;B141&amp;"_"&amp;C141&amp;"_"&amp;D141,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H141" t="str">
+        <f t="shared" si="4"/>
+        <v>not comparable</v>
+      </c>
+      <c r="I141" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A142" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E142" t="str">
+        <f>VLOOKUP("npm_"&amp;A142&amp;"_"&amp;B142&amp;"_"&amp;C142&amp;"_"&amp;D142,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="F142" t="str">
+        <f>VLOOKUP("pip_"&amp;A142&amp;"_"&amp;B142&amp;"_"&amp;C142&amp;"_"&amp;D142,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="G142" t="str">
+        <f>VLOOKUP("mvn_"&amp;A142&amp;"_"&amp;B142&amp;"_"&amp;C142&amp;"_"&amp;D142,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H142" t="str">
+        <f t="shared" si="4"/>
+        <v>not comparable</v>
+      </c>
+      <c r="I142" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A143" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E143" t="str">
+        <f>VLOOKUP("npm_"&amp;A143&amp;"_"&amp;B143&amp;"_"&amp;C143&amp;"_"&amp;D143,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="F143" t="str">
+        <f>VLOOKUP("pip_"&amp;A143&amp;"_"&amp;B143&amp;"_"&amp;C143&amp;"_"&amp;D143,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="G143" t="str">
+        <f>VLOOKUP("mvn_"&amp;A143&amp;"_"&amp;B143&amp;"_"&amp;C143&amp;"_"&amp;D143,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H143" t="str">
+        <f t="shared" si="4"/>
+        <v>not comparable</v>
+      </c>
+      <c r="I143" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A144" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E144" t="str">
+        <f>VLOOKUP("npm_"&amp;A144&amp;"_"&amp;B144&amp;"_"&amp;C144&amp;"_"&amp;D144,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="F144" t="str">
+        <f>VLOOKUP("pip_"&amp;A144&amp;"_"&amp;B144&amp;"_"&amp;C144&amp;"_"&amp;D144,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="G144" t="str">
+        <f>VLOOKUP("mvn_"&amp;A144&amp;"_"&amp;B144&amp;"_"&amp;C144&amp;"_"&amp;D144,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H144" t="str">
+        <f t="shared" si="4"/>
+        <v>not comparable</v>
+      </c>
+      <c r="I144" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A145" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E145" t="str">
+        <f>VLOOKUP("npm_"&amp;A145&amp;"_"&amp;B145&amp;"_"&amp;C145&amp;"_"&amp;D145,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="F145" t="str">
+        <f>VLOOKUP("pip_"&amp;A145&amp;"_"&amp;B145&amp;"_"&amp;C145&amp;"_"&amp;D145,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="G145" t="str">
+        <f>VLOOKUP("mvn_"&amp;A145&amp;"_"&amp;B145&amp;"_"&amp;C145&amp;"_"&amp;D145,'results'!$A:$H,8,FALSE)</f>
+        <v>invalid_configuration</v>
+      </c>
+      <c r="H145" t="str">
+        <f t="shared" si="4"/>
+        <v>not comparable</v>
+      </c>
+      <c r="I145" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I145" xr:uid="{4249C603-D76A-4D75-8999-A8343558CAF2}"/>
+  <conditionalFormatting sqref="H1:H1048576 I1">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
+      <formula>"agree"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+      <formula>"disagree"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+      <formula>"not comparable"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:G145">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="private_resolve">
+      <formula>NOT(ISERROR(SEARCH("private_resolve",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="resolution_error">
+      <formula>NOT(ISERROR(SEARCH("resolution_error",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="malicious_resolved">
+      <formula>NOT(ISERROR(SEARCH("malicious_resolved",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="invalid">
+      <formula>NOT(ISERROR(SEARCH("invalid",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/sub-RQ1_result/analysis/result_analysis_excel.xlsx
+++ b/sub-RQ1_result/analysis/result_analysis_excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Master_Winfo\MA_Supply_chain_security\MS_test_system\sub-RQ1_result\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352EBEDA-C432-4507-BD2F-8EE2C97921FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD5B371-4D52-4476-BF86-4EC3A6F00134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{482212B2-0356-4914-B53B-8802B28615EB}"/>
   </bookViews>

--- a/sub-RQ1_result/analysis/result_analysis_excel.xlsx
+++ b/sub-RQ1_result/analysis/result_analysis_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Master_Winfo\MA_Supply_chain_security\MS_test_system\sub-RQ1_result\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD5B371-4D52-4476-BF86-4EC3A6F00134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D079F33D-E640-4BD6-94A8-5E059DD0321C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{482212B2-0356-4914-B53B-8802B28615EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{482212B2-0356-4914-B53B-8802B28615EB}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="2" r:id="rId1"/>
@@ -2950,7 +2950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2966,6 +2966,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -3257,7 +3258,34 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7F29230C-F0E4-43EA-8341-3E01AF9D8D83}" name="results" displayName="results" ref="A1:W433" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:W433" xr:uid="{7F29230C-F0E4-43EA-8341-3E01AF9D8D83}"/>
+  <autoFilter ref="A1:W433" xr:uid="{7F29230C-F0E4-43EA-8341-3E01AF9D8D83}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="java"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="B1d"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="B2a"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="C1b"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <filter val="malicious_resolved"/>
+        <filter val="resolution_error"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{A65D53B3-AEE8-4BDA-A007-78AF105B23C7}" uniqueName="1" name="cell_id" queryTableFieldId="1" dataDxfId="42"/>
     <tableColumn id="2" xr3:uid="{FAE1C5D0-B844-4E04-8570-5E7392EC0CD8}" uniqueName="2" name="timestamp" queryTableFieldId="2" dataDxfId="41"/>
@@ -3709,7 +3737,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -3786,7 +3814,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -3863,7 +3891,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -3940,7 +3968,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -4021,7 +4049,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -4102,7 +4130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -4179,7 +4207,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -4250,7 +4278,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -4321,7 +4349,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -4398,7 +4426,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -4475,7 +4503,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -4552,7 +4580,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -4629,7 +4657,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -4700,7 +4728,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -4771,7 +4799,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -4848,7 +4876,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>72</v>
       </c>
@@ -4925,7 +4953,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -5002,7 +5030,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -5079,7 +5107,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>78</v>
       </c>
@@ -5150,7 +5178,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -5221,7 +5249,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -5298,7 +5326,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -5375,7 +5403,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>87</v>
       </c>
@@ -5452,7 +5480,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>89</v>
       </c>
@@ -5529,7 +5557,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>91</v>
       </c>
@@ -5606,7 +5634,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>96</v>
       </c>
@@ -5683,7 +5711,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -5760,7 +5788,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>102</v>
       </c>
@@ -5837,7 +5865,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>104</v>
       </c>
@@ -5914,7 +5942,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>106</v>
       </c>
@@ -5991,7 +6019,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>108</v>
       </c>
@@ -6062,7 +6090,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -6133,7 +6161,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>112</v>
       </c>
@@ -6210,7 +6238,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>114</v>
       </c>
@@ -6287,7 +6315,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>116</v>
       </c>
@@ -6364,7 +6392,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -6441,7 +6469,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>120</v>
       </c>
@@ -6512,7 +6540,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -6583,7 +6611,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>124</v>
       </c>
@@ -6660,7 +6688,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -6737,7 +6765,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>128</v>
       </c>
@@ -6814,7 +6842,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>130</v>
       </c>
@@ -6891,7 +6919,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>132</v>
       </c>
@@ -6962,7 +6990,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>134</v>
       </c>
@@ -7033,7 +7061,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>136</v>
       </c>
@@ -7110,7 +7138,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>138</v>
       </c>
@@ -7187,7 +7215,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -7264,7 +7292,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>142</v>
       </c>
@@ -7341,7 +7369,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>144</v>
       </c>
@@ -7412,7 +7440,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>147</v>
       </c>
@@ -7483,7 +7511,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>149</v>
       </c>
@@ -7554,7 +7582,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>151</v>
       </c>
@@ -7625,7 +7653,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>153</v>
       </c>
@@ -7696,7 +7724,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>155</v>
       </c>
@@ -7767,7 +7795,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>157</v>
       </c>
@@ -7838,7 +7866,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>159</v>
       </c>
@@ -7909,7 +7937,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>161</v>
       </c>
@@ -7986,7 +8014,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>163</v>
       </c>
@@ -8063,7 +8091,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>165</v>
       </c>
@@ -8140,7 +8168,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>167</v>
       </c>
@@ -8217,7 +8245,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>169</v>
       </c>
@@ -8288,7 +8316,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>171</v>
       </c>
@@ -8359,7 +8387,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>173</v>
       </c>
@@ -8436,7 +8464,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>175</v>
       </c>
@@ -8513,7 +8541,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>177</v>
       </c>
@@ -8590,7 +8618,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>179</v>
       </c>
@@ -8667,7 +8695,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>181</v>
       </c>
@@ -8738,7 +8766,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>183</v>
       </c>
@@ -8809,7 +8837,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>185</v>
       </c>
@@ -8886,7 +8914,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>187</v>
       </c>
@@ -8963,7 +8991,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>189</v>
       </c>
@@ -9040,7 +9068,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>191</v>
       </c>
@@ -9117,7 +9145,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>193</v>
       </c>
@@ -9188,7 +9216,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>196</v>
       </c>
@@ -9259,7 +9287,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>198</v>
       </c>
@@ -9330,7 +9358,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>200</v>
       </c>
@@ -9401,7 +9429,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>202</v>
       </c>
@@ -9472,7 +9500,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>204</v>
       </c>
@@ -9543,7 +9571,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>206</v>
       </c>
@@ -9614,7 +9642,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>208</v>
       </c>
@@ -9685,7 +9713,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>210</v>
       </c>
@@ -9762,7 +9790,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>212</v>
       </c>
@@ -9839,7 +9867,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>214</v>
       </c>
@@ -9916,7 +9944,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>216</v>
       </c>
@@ -9993,7 +10021,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>218</v>
       </c>
@@ -10064,7 +10092,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>220</v>
       </c>
@@ -10135,7 +10163,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>222</v>
       </c>
@@ -10212,7 +10240,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>224</v>
       </c>
@@ -10289,7 +10317,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>226</v>
       </c>
@@ -10366,7 +10394,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>228</v>
       </c>
@@ -10443,7 +10471,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>230</v>
       </c>
@@ -10520,7 +10548,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>237</v>
       </c>
@@ -10597,7 +10625,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>240</v>
       </c>
@@ -10674,7 +10702,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>242</v>
       </c>
@@ -10751,7 +10779,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>246</v>
       </c>
@@ -10828,7 +10856,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>248</v>
       </c>
@@ -10905,7 +10933,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>250</v>
       </c>
@@ -10982,7 +11010,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>252</v>
       </c>
@@ -11059,7 +11087,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>254</v>
       </c>
@@ -11136,7 +11164,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>256</v>
       </c>
@@ -11213,7 +11241,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>258</v>
       </c>
@@ -11290,7 +11318,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>260</v>
       </c>
@@ -11367,7 +11395,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>262</v>
       </c>
@@ -11444,7 +11472,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>266</v>
       </c>
@@ -11521,7 +11549,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>268</v>
       </c>
@@ -11598,7 +11626,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>270</v>
       </c>
@@ -11675,7 +11703,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>272</v>
       </c>
@@ -11752,7 +11780,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>274</v>
       </c>
@@ -11829,7 +11857,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>276</v>
       </c>
@@ -11906,7 +11934,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>278</v>
       </c>
@@ -11983,7 +12011,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>280</v>
       </c>
@@ -12060,7 +12088,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>282</v>
       </c>
@@ -12137,7 +12165,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>286</v>
       </c>
@@ -12214,7 +12242,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>288</v>
       </c>
@@ -12291,7 +12319,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>290</v>
       </c>
@@ -12368,7 +12396,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>292</v>
       </c>
@@ -12445,7 +12473,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>294</v>
       </c>
@@ -12522,7 +12550,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>296</v>
       </c>
@@ -12593,7 +12621,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>298</v>
       </c>
@@ -12664,7 +12692,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>300</v>
       </c>
@@ -12735,7 +12763,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>302</v>
       </c>
@@ -12812,7 +12840,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>304</v>
       </c>
@@ -12883,7 +12911,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>306</v>
       </c>
@@ -12960,7 +12988,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>308</v>
       </c>
@@ -13037,7 +13065,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>310</v>
       </c>
@@ -13108,7 +13136,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>312</v>
       </c>
@@ -13185,7 +13213,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>314</v>
       </c>
@@ -13262,7 +13290,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>318</v>
       </c>
@@ -13339,7 +13367,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>320</v>
       </c>
@@ -13416,7 +13444,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>322</v>
       </c>
@@ -13493,7 +13521,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>326</v>
       </c>
@@ -13570,7 +13598,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>328</v>
       </c>
@@ -13647,7 +13675,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>330</v>
       </c>
@@ -13724,7 +13752,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>332</v>
       </c>
@@ -13801,7 +13829,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>334</v>
       </c>
@@ -13878,7 +13906,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>336</v>
       </c>
@@ -13955,7 +13983,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>338</v>
       </c>
@@ -14032,7 +14060,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>340</v>
       </c>
@@ -14109,7 +14137,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>342</v>
       </c>
@@ -14186,7 +14214,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>344</v>
       </c>
@@ -14263,7 +14291,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>346</v>
       </c>
@@ -14340,7 +14368,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>348</v>
       </c>
@@ -14417,7 +14445,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>350</v>
       </c>
@@ -14494,7 +14522,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>352</v>
       </c>
@@ -14571,7 +14599,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>354</v>
       </c>
@@ -14648,7 +14676,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>356</v>
       </c>
@@ -14725,7 +14753,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>358</v>
       </c>
@@ -14802,7 +14830,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>360</v>
       </c>
@@ -14879,7 +14907,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>362</v>
       </c>
@@ -14956,7 +14984,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>364</v>
       </c>
@@ -15033,7 +15061,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>366</v>
       </c>
@@ -15110,7 +15138,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>368</v>
       </c>
@@ -15187,7 +15215,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>370</v>
       </c>
@@ -15264,7 +15292,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>372</v>
       </c>
@@ -15335,7 +15363,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>374</v>
       </c>
@@ -15406,7 +15434,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>376</v>
       </c>
@@ -15477,7 +15505,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>378</v>
       </c>
@@ -15554,7 +15582,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>380</v>
       </c>
@@ -15625,7 +15653,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>382</v>
       </c>
@@ -15702,7 +15730,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>384</v>
       </c>
@@ -15779,7 +15807,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>386</v>
       </c>
@@ -15850,7 +15878,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>388</v>
       </c>
@@ -15927,7 +15955,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>390</v>
       </c>
@@ -15998,7 +16026,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>392</v>
       </c>
@@ -16069,7 +16097,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>394</v>
       </c>
@@ -16140,7 +16168,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>396</v>
       </c>
@@ -16211,7 +16239,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>398</v>
       </c>
@@ -16282,7 +16310,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>400</v>
       </c>
@@ -16353,7 +16381,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>402</v>
       </c>
@@ -16424,7 +16452,7 @@
         <v/>
       </c>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>404</v>
       </c>
@@ -16495,7 +16523,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>406</v>
       </c>
@@ -16566,7 +16594,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>408</v>
       </c>
@@ -16643,7 +16671,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>412</v>
       </c>
@@ -16720,7 +16748,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>414</v>
       </c>
@@ -16797,7 +16825,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>416</v>
       </c>
@@ -16874,7 +16902,7 @@
         <v/>
       </c>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>418</v>
       </c>
@@ -16951,7 +16979,7 @@
         <v/>
       </c>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>420</v>
       </c>
@@ -17028,7 +17056,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>422</v>
       </c>
@@ -17105,7 +17133,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>424</v>
       </c>
@@ -17182,7 +17210,7 @@
         <v/>
       </c>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>426</v>
       </c>
@@ -17259,7 +17287,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>428</v>
       </c>
@@ -17336,7 +17364,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>430</v>
       </c>
@@ -17413,7 +17441,7 @@
         <v/>
       </c>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>432</v>
       </c>
@@ -17490,7 +17518,7 @@
         <v/>
       </c>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>434</v>
       </c>
@@ -17567,7 +17595,7 @@
         <v/>
       </c>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>436</v>
       </c>
@@ -17644,7 +17672,7 @@
         <v/>
       </c>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>438</v>
       </c>
@@ -17721,7 +17749,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>440</v>
       </c>
@@ -17798,7 +17826,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>442</v>
       </c>
@@ -17875,7 +17903,7 @@
         <v/>
       </c>
     </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>444</v>
       </c>
@@ -17952,7 +17980,7 @@
         <v/>
       </c>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>446</v>
       </c>
@@ -18023,7 +18051,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>448</v>
       </c>
@@ -18094,7 +18122,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>450</v>
       </c>
@@ -18165,7 +18193,7 @@
         <v/>
       </c>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>452</v>
       </c>
@@ -18242,7 +18270,7 @@
         <v/>
       </c>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>454</v>
       </c>
@@ -18313,7 +18341,7 @@
         <v/>
       </c>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>456</v>
       </c>
@@ -18390,7 +18418,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>458</v>
       </c>
@@ -18467,7 +18495,7 @@
         <v/>
       </c>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>460</v>
       </c>
@@ -18538,7 +18566,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>462</v>
       </c>
@@ -18615,7 +18643,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>464</v>
       </c>
@@ -18686,7 +18714,7 @@
         <v/>
       </c>
     </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>466</v>
       </c>
@@ -18757,7 +18785,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>468</v>
       </c>
@@ -18828,7 +18856,7 @@
         <v/>
       </c>
     </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>470</v>
       </c>
@@ -18899,7 +18927,7 @@
         <v/>
       </c>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>472</v>
       </c>
@@ -18970,7 +18998,7 @@
         <v/>
       </c>
     </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>474</v>
       </c>
@@ -19041,7 +19069,7 @@
         <v/>
       </c>
     </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>476</v>
       </c>
@@ -19112,7 +19140,7 @@
         <v/>
       </c>
     </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>478</v>
       </c>
@@ -19183,7 +19211,7 @@
         <v/>
       </c>
     </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>480</v>
       </c>
@@ -19254,7 +19282,7 @@
         <v/>
       </c>
     </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>482</v>
       </c>
@@ -19331,7 +19359,7 @@
         <v/>
       </c>
     </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>484</v>
       </c>
@@ -19408,7 +19436,7 @@
         <v/>
       </c>
     </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>486</v>
       </c>
@@ -19485,7 +19513,7 @@
         <v/>
       </c>
     </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>488</v>
       </c>
@@ -19562,7 +19590,7 @@
         <v/>
       </c>
     </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>490</v>
       </c>
@@ -19639,7 +19667,7 @@
         <v/>
       </c>
     </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>492</v>
       </c>
@@ -19716,7 +19744,7 @@
         <v/>
       </c>
     </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>494</v>
       </c>
@@ -19793,7 +19821,7 @@
         <v/>
       </c>
     </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>496</v>
       </c>
@@ -19870,7 +19898,7 @@
         <v/>
       </c>
     </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>498</v>
       </c>
@@ -19947,7 +19975,7 @@
         <v/>
       </c>
     </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>500</v>
       </c>
@@ -20018,7 +20046,7 @@
         <v/>
       </c>
     </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>502</v>
       </c>
@@ -20089,7 +20117,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>504</v>
       </c>
@@ -20160,7 +20188,7 @@
         <v/>
       </c>
     </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>506</v>
       </c>
@@ -20237,7 +20265,7 @@
         <v/>
       </c>
     </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>508</v>
       </c>
@@ -20308,7 +20336,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>510</v>
       </c>
@@ -20385,7 +20413,7 @@
         <v/>
       </c>
     </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>512</v>
       </c>
@@ -20462,7 +20490,7 @@
         <v/>
       </c>
     </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>514</v>
       </c>
@@ -20533,7 +20561,7 @@
         <v/>
       </c>
     </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>516</v>
       </c>
@@ -20610,7 +20638,7 @@
         <v/>
       </c>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>518</v>
       </c>
@@ -20687,7 +20715,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>525</v>
       </c>
@@ -20764,7 +20792,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>527</v>
       </c>
@@ -20841,7 +20869,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>529</v>
       </c>
@@ -20918,7 +20946,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>533</v>
       </c>
@@ -20995,7 +21023,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>535</v>
       </c>
@@ -21072,7 +21100,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>537</v>
       </c>
@@ -21149,7 +21177,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>539</v>
       </c>
@@ -21226,7 +21254,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>541</v>
       </c>
@@ -21303,7 +21331,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>543</v>
       </c>
@@ -21380,7 +21408,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>547</v>
       </c>
@@ -21457,7 +21485,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>549</v>
       </c>
@@ -21534,7 +21562,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>551</v>
       </c>
@@ -21611,7 +21639,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>553</v>
       </c>
@@ -21688,7 +21716,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>555</v>
       </c>
@@ -21765,7 +21793,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>557</v>
       </c>
@@ -21842,7 +21870,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>561</v>
       </c>
@@ -21919,7 +21947,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>563</v>
       </c>
@@ -21996,7 +22024,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>565</v>
       </c>
@@ -22089,7 +22117,7 @@
       <c r="G246" t="s">
         <v>238</v>
       </c>
-      <c r="H246" t="s">
+      <c r="H246" s="13" t="s">
         <v>48</v>
       </c>
       <c r="I246" t="s">
@@ -22144,7 +22172,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>569</v>
       </c>
@@ -22215,7 +22243,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>571</v>
       </c>
@@ -22292,7 +22320,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>573</v>
       </c>
@@ -22369,7 +22397,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>575</v>
       </c>
@@ -22446,7 +22474,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>577</v>
       </c>
@@ -22523,7 +22551,7 @@
         <v/>
       </c>
     </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>581</v>
       </c>
@@ -22600,7 +22628,7 @@
         <v/>
       </c>
     </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>583</v>
       </c>
@@ -22677,7 +22705,7 @@
         <v/>
       </c>
     </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>585</v>
       </c>
@@ -22754,7 +22782,7 @@
         <v/>
       </c>
     </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>589</v>
       </c>
@@ -22831,7 +22859,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>591</v>
       </c>
@@ -22908,7 +22936,7 @@
         <v/>
       </c>
     </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>593</v>
       </c>
@@ -22985,7 +23013,7 @@
         <v/>
       </c>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>595</v>
       </c>
@@ -23062,7 +23090,7 @@
         <v/>
       </c>
     </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>597</v>
       </c>
@@ -23139,7 +23167,7 @@
         <v/>
       </c>
     </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>599</v>
       </c>
@@ -23216,7 +23244,7 @@
         <v/>
       </c>
     </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>601</v>
       </c>
@@ -23293,7 +23321,7 @@
         <v/>
       </c>
     </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>603</v>
       </c>
@@ -23370,7 +23398,7 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>605</v>
       </c>
@@ -23447,7 +23475,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>607</v>
       </c>
@@ -23524,7 +23552,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>609</v>
       </c>
@@ -23601,7 +23629,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>611</v>
       </c>
@@ -23678,7 +23706,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>613</v>
       </c>
@@ -23755,7 +23783,7 @@
         <v/>
       </c>
     </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>615</v>
       </c>
@@ -23832,7 +23860,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>617</v>
       </c>
@@ -23925,7 +23953,7 @@
       <c r="G270" t="s">
         <v>238</v>
       </c>
-      <c r="H270" t="s">
+      <c r="H270" s="13" t="s">
         <v>48</v>
       </c>
       <c r="I270" t="s">
@@ -23980,7 +24008,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>621</v>
       </c>
@@ -24051,7 +24079,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>623</v>
       </c>
@@ -24128,7 +24156,7 @@
         <v/>
       </c>
     </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>625</v>
       </c>
@@ -24205,7 +24233,7 @@
         <v/>
       </c>
     </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>627</v>
       </c>
@@ -24282,7 +24310,7 @@
         <v/>
       </c>
     </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>629</v>
       </c>
@@ -24353,7 +24381,7 @@
         <v/>
       </c>
     </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>631</v>
       </c>
@@ -24430,7 +24458,7 @@
         <v/>
       </c>
     </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>635</v>
       </c>
@@ -24501,7 +24529,7 @@
         <v/>
       </c>
     </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>637</v>
       </c>
@@ -24572,7 +24600,7 @@
         <v/>
       </c>
     </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>639</v>
       </c>
@@ -24649,7 +24677,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>643</v>
       </c>
@@ -24720,7 +24748,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>645</v>
       </c>
@@ -24797,7 +24825,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>647</v>
       </c>
@@ -24874,7 +24902,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>649</v>
       </c>
@@ -24951,7 +24979,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>651</v>
       </c>
@@ -25028,7 +25056,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>653</v>
       </c>
@@ -25105,7 +25133,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>655</v>
       </c>
@@ -25182,7 +25210,7 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>657</v>
       </c>
@@ -25259,7 +25287,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>659</v>
       </c>
@@ -25336,7 +25364,7 @@
         <v/>
       </c>
     </row>
-    <row r="289" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>661</v>
       </c>
@@ -25413,7 +25441,7 @@
         <v/>
       </c>
     </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>663</v>
       </c>
@@ -25490,7 +25518,7 @@
         <v/>
       </c>
     </row>
-    <row r="291" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>665</v>
       </c>
@@ -25567,7 +25595,7 @@
         <v/>
       </c>
     </row>
-    <row r="292" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>667</v>
       </c>
@@ -25644,7 +25672,7 @@
         <v/>
       </c>
     </row>
-    <row r="293" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>669</v>
       </c>
@@ -25737,7 +25765,7 @@
       <c r="G294" t="s">
         <v>238</v>
       </c>
-      <c r="H294" t="s">
+      <c r="H294" s="13" t="s">
         <v>48</v>
       </c>
       <c r="I294" t="s">
@@ -25792,7 +25820,7 @@
         <v/>
       </c>
     </row>
-    <row r="295" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>673</v>
       </c>
@@ -25863,7 +25891,7 @@
         <v/>
       </c>
     </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>675</v>
       </c>
@@ -25940,7 +25968,7 @@
         <v/>
       </c>
     </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>677</v>
       </c>
@@ -26017,7 +26045,7 @@
         <v/>
       </c>
     </row>
-    <row r="298" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>679</v>
       </c>
@@ -26094,7 +26122,7 @@
         <v/>
       </c>
     </row>
-    <row r="299" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>681</v>
       </c>
@@ -26171,7 +26199,7 @@
         <v/>
       </c>
     </row>
-    <row r="300" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>683</v>
       </c>
@@ -26248,7 +26276,7 @@
         <v/>
       </c>
     </row>
-    <row r="301" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>685</v>
       </c>
@@ -26325,7 +26353,7 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>687</v>
       </c>
@@ -26402,7 +26430,7 @@
         <v/>
       </c>
     </row>
-    <row r="303" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>689</v>
       </c>
@@ -26479,7 +26507,7 @@
         <v/>
       </c>
     </row>
-    <row r="304" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>691</v>
       </c>
@@ -26556,7 +26584,7 @@
         <v/>
       </c>
     </row>
-    <row r="305" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>693</v>
       </c>
@@ -26633,7 +26661,7 @@
         <v/>
       </c>
     </row>
-    <row r="306" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>695</v>
       </c>
@@ -26710,7 +26738,7 @@
         <v/>
       </c>
     </row>
-    <row r="307" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>697</v>
       </c>
@@ -26787,7 +26815,7 @@
         <v/>
       </c>
     </row>
-    <row r="308" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>699</v>
       </c>
@@ -26864,7 +26892,7 @@
         <v/>
       </c>
     </row>
-    <row r="309" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>701</v>
       </c>
@@ -26941,7 +26969,7 @@
         <v/>
       </c>
     </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>703</v>
       </c>
@@ -27018,7 +27046,7 @@
         <v/>
       </c>
     </row>
-    <row r="311" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>705</v>
       </c>
@@ -27111,7 +27139,7 @@
       <c r="G312" t="s">
         <v>238</v>
       </c>
-      <c r="H312" t="s">
+      <c r="H312" s="13" t="s">
         <v>48</v>
       </c>
       <c r="I312" t="s">
@@ -27166,7 +27194,7 @@
         <v/>
       </c>
     </row>
-    <row r="313" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>709</v>
       </c>
@@ -27237,7 +27265,7 @@
         <v/>
       </c>
     </row>
-    <row r="314" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>711</v>
       </c>
@@ -27314,7 +27342,7 @@
         <v/>
       </c>
     </row>
-    <row r="315" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>713</v>
       </c>
@@ -27391,7 +27419,7 @@
         <v/>
       </c>
     </row>
-    <row r="316" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>715</v>
       </c>
@@ -27468,7 +27496,7 @@
         <v/>
       </c>
     </row>
-    <row r="317" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>717</v>
       </c>
@@ -27545,7 +27573,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="318" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>722</v>
       </c>
@@ -27622,7 +27650,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="319" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>724</v>
       </c>
@@ -27699,7 +27727,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="320" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>726</v>
       </c>
@@ -27770,7 +27798,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>728</v>
       </c>
@@ -27847,7 +27875,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>730</v>
       </c>
@@ -27924,7 +27952,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>732</v>
       </c>
@@ -27995,7 +28023,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="324" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>734</v>
       </c>
@@ -28072,7 +28100,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="325" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>736</v>
       </c>
@@ -28149,7 +28177,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>738</v>
       </c>
@@ -28220,7 +28248,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>740</v>
       </c>
@@ -28297,7 +28325,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>742</v>
       </c>
@@ -28374,7 +28402,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>744</v>
       </c>
@@ -28451,7 +28479,7 @@
         <v/>
       </c>
     </row>
-    <row r="330" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>746</v>
       </c>
@@ -28528,7 +28556,7 @@
         <v/>
       </c>
     </row>
-    <row r="331" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>748</v>
       </c>
@@ -28605,7 +28633,7 @@
         <v/>
       </c>
     </row>
-    <row r="332" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>750</v>
       </c>
@@ -28676,7 +28704,7 @@
         <v/>
       </c>
     </row>
-    <row r="333" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>752</v>
       </c>
@@ -28753,7 +28781,7 @@
         <v/>
       </c>
     </row>
-    <row r="334" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>754</v>
       </c>
@@ -28830,7 +28858,7 @@
         <v/>
       </c>
     </row>
-    <row r="335" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>756</v>
       </c>
@@ -28901,7 +28929,7 @@
         <v/>
       </c>
     </row>
-    <row r="336" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>758</v>
       </c>
@@ -28978,7 +29006,7 @@
         <v/>
       </c>
     </row>
-    <row r="337" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>760</v>
       </c>
@@ -29055,7 +29083,7 @@
         <v/>
       </c>
     </row>
-    <row r="338" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>762</v>
       </c>
@@ -29126,7 +29154,7 @@
         <v/>
       </c>
     </row>
-    <row r="339" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>764</v>
       </c>
@@ -29203,7 +29231,7 @@
         <v/>
       </c>
     </row>
-    <row r="340" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>766</v>
       </c>
@@ -29280,7 +29308,7 @@
         <v/>
       </c>
     </row>
-    <row r="341" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>768</v>
       </c>
@@ -29357,7 +29385,7 @@
         <v/>
       </c>
     </row>
-    <row r="342" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>770</v>
       </c>
@@ -29434,7 +29462,7 @@
         <v/>
       </c>
     </row>
-    <row r="343" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>774</v>
       </c>
@@ -29511,7 +29539,7 @@
         <v/>
       </c>
     </row>
-    <row r="344" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>776</v>
       </c>
@@ -29582,7 +29610,7 @@
         <v/>
       </c>
     </row>
-    <row r="345" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>778</v>
       </c>
@@ -29659,7 +29687,7 @@
         <v/>
       </c>
     </row>
-    <row r="346" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>780</v>
       </c>
@@ -29736,7 +29764,7 @@
         <v/>
       </c>
     </row>
-    <row r="347" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>782</v>
       </c>
@@ -29807,7 +29835,7 @@
         <v/>
       </c>
     </row>
-    <row r="348" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>784</v>
       </c>
@@ -29884,7 +29912,7 @@
         <v/>
       </c>
     </row>
-    <row r="349" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>786</v>
       </c>
@@ -29961,7 +29989,7 @@
         <v/>
       </c>
     </row>
-    <row r="350" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>788</v>
       </c>
@@ -30032,7 +30060,7 @@
         <v/>
       </c>
     </row>
-    <row r="351" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>790</v>
       </c>
@@ -30109,7 +30137,7 @@
         <v/>
       </c>
     </row>
-    <row r="352" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>792</v>
       </c>
@@ -30186,7 +30214,7 @@
         <v/>
       </c>
     </row>
-    <row r="353" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>794</v>
       </c>
@@ -30263,7 +30291,7 @@
         <v/>
       </c>
     </row>
-    <row r="354" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>796</v>
       </c>
@@ -30340,7 +30368,7 @@
         <v/>
       </c>
     </row>
-    <row r="355" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>798</v>
       </c>
@@ -30417,7 +30445,7 @@
         <v/>
       </c>
     </row>
-    <row r="356" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>800</v>
       </c>
@@ -30488,7 +30516,7 @@
         <v/>
       </c>
     </row>
-    <row r="357" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>802</v>
       </c>
@@ -30565,7 +30593,7 @@
         <v/>
       </c>
     </row>
-    <row r="358" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>804</v>
       </c>
@@ -30642,7 +30670,7 @@
         <v/>
       </c>
     </row>
-    <row r="359" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>806</v>
       </c>
@@ -30713,7 +30741,7 @@
         <v/>
       </c>
     </row>
-    <row r="360" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>808</v>
       </c>
@@ -30790,7 +30818,7 @@
         <v/>
       </c>
     </row>
-    <row r="361" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>810</v>
       </c>
@@ -30867,7 +30895,7 @@
         <v/>
       </c>
     </row>
-    <row r="362" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>812</v>
       </c>
@@ -30935,7 +30963,7 @@
         <v/>
       </c>
     </row>
-    <row r="363" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>814</v>
       </c>
@@ -31003,7 +31031,7 @@
         <v/>
       </c>
     </row>
-    <row r="364" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>815</v>
       </c>
@@ -31071,7 +31099,7 @@
         <v/>
       </c>
     </row>
-    <row r="365" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>816</v>
       </c>
@@ -31139,7 +31167,7 @@
         <v/>
       </c>
     </row>
-    <row r="366" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>817</v>
       </c>
@@ -31207,7 +31235,7 @@
         <v/>
       </c>
     </row>
-    <row r="367" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>818</v>
       </c>
@@ -31275,7 +31303,7 @@
         <v/>
       </c>
     </row>
-    <row r="368" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>819</v>
       </c>
@@ -31343,7 +31371,7 @@
         <v/>
       </c>
     </row>
-    <row r="369" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>820</v>
       </c>
@@ -31411,7 +31439,7 @@
         <v/>
       </c>
     </row>
-    <row r="370" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>821</v>
       </c>
@@ -31479,7 +31507,7 @@
         <v/>
       </c>
     </row>
-    <row r="371" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>822</v>
       </c>
@@ -31547,7 +31575,7 @@
         <v/>
       </c>
     </row>
-    <row r="372" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>823</v>
       </c>
@@ -31615,7 +31643,7 @@
         <v/>
       </c>
     </row>
-    <row r="373" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>824</v>
       </c>
@@ -31683,7 +31711,7 @@
         <v/>
       </c>
     </row>
-    <row r="374" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>825</v>
       </c>
@@ -31751,7 +31779,7 @@
         <v/>
       </c>
     </row>
-    <row r="375" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>826</v>
       </c>
@@ -31819,7 +31847,7 @@
         <v/>
       </c>
     </row>
-    <row r="376" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>827</v>
       </c>
@@ -31887,7 +31915,7 @@
         <v/>
       </c>
     </row>
-    <row r="377" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>828</v>
       </c>
@@ -31955,7 +31983,7 @@
         <v/>
       </c>
     </row>
-    <row r="378" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>829</v>
       </c>
@@ -32023,7 +32051,7 @@
         <v/>
       </c>
     </row>
-    <row r="379" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>830</v>
       </c>
@@ -32091,7 +32119,7 @@
         <v/>
       </c>
     </row>
-    <row r="380" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>831</v>
       </c>
@@ -32159,7 +32187,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="381" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>832</v>
       </c>
@@ -32227,7 +32255,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="382" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>833</v>
       </c>
@@ -32295,7 +32323,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="383" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>834</v>
       </c>
@@ -32363,7 +32391,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="384" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>835</v>
       </c>
@@ -32431,7 +32459,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="385" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>836</v>
       </c>
@@ -32499,7 +32527,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="386" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>837</v>
       </c>
@@ -32567,7 +32595,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="387" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>838</v>
       </c>
@@ -32635,7 +32663,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="388" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>839</v>
       </c>
@@ -32703,7 +32731,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="389" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>840</v>
       </c>
@@ -32771,7 +32799,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="390" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>841</v>
       </c>
@@ -32839,7 +32867,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="391" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>842</v>
       </c>
@@ -32907,7 +32935,7 @@
         <v>same</v>
       </c>
     </row>
-    <row r="392" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>843</v>
       </c>
@@ -32975,7 +33003,7 @@
         <v/>
       </c>
     </row>
-    <row r="393" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>844</v>
       </c>
@@ -33043,7 +33071,7 @@
         <v/>
       </c>
     </row>
-    <row r="394" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>845</v>
       </c>
@@ -33111,7 +33139,7 @@
         <v/>
       </c>
     </row>
-    <row r="395" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>846</v>
       </c>
@@ -33179,7 +33207,7 @@
         <v/>
       </c>
     </row>
-    <row r="396" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>847</v>
       </c>
@@ -33247,7 +33275,7 @@
         <v/>
       </c>
     </row>
-    <row r="397" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>848</v>
       </c>
@@ -33315,7 +33343,7 @@
         <v/>
       </c>
     </row>
-    <row r="398" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>849</v>
       </c>
@@ -33383,7 +33411,7 @@
         <v/>
       </c>
     </row>
-    <row r="399" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>850</v>
       </c>
@@ -33451,7 +33479,7 @@
         <v/>
       </c>
     </row>
-    <row r="400" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>851</v>
       </c>
@@ -33519,7 +33547,7 @@
         <v/>
       </c>
     </row>
-    <row r="401" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>852</v>
       </c>
@@ -33587,7 +33615,7 @@
         <v/>
       </c>
     </row>
-    <row r="402" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>853</v>
       </c>
@@ -33655,7 +33683,7 @@
         <v/>
       </c>
     </row>
-    <row r="403" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>854</v>
       </c>
@@ -33723,7 +33751,7 @@
         <v/>
       </c>
     </row>
-    <row r="404" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>855</v>
       </c>
@@ -33791,7 +33819,7 @@
         <v/>
       </c>
     </row>
-    <row r="405" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>856</v>
       </c>
@@ -33859,7 +33887,7 @@
         <v/>
       </c>
     </row>
-    <row r="406" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>857</v>
       </c>
@@ -33927,7 +33955,7 @@
         <v/>
       </c>
     </row>
-    <row r="407" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>858</v>
       </c>
@@ -33995,7 +34023,7 @@
         <v/>
       </c>
     </row>
-    <row r="408" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>859</v>
       </c>
@@ -34063,7 +34091,7 @@
         <v/>
       </c>
     </row>
-    <row r="409" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>860</v>
       </c>
@@ -34131,7 +34159,7 @@
         <v/>
       </c>
     </row>
-    <row r="410" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>861</v>
       </c>
@@ -34199,7 +34227,7 @@
         <v/>
       </c>
     </row>
-    <row r="411" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>862</v>
       </c>
@@ -34267,7 +34295,7 @@
         <v/>
       </c>
     </row>
-    <row r="412" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>863</v>
       </c>
@@ -34335,7 +34363,7 @@
         <v/>
       </c>
     </row>
-    <row r="413" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>864</v>
       </c>
@@ -34403,7 +34431,7 @@
         <v/>
       </c>
     </row>
-    <row r="414" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>865</v>
       </c>
@@ -34471,7 +34499,7 @@
         <v/>
       </c>
     </row>
-    <row r="415" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>866</v>
       </c>
@@ -34539,7 +34567,7 @@
         <v/>
       </c>
     </row>
-    <row r="416" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>867</v>
       </c>
@@ -34607,7 +34635,7 @@
         <v/>
       </c>
     </row>
-    <row r="417" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>868</v>
       </c>
@@ -34675,7 +34703,7 @@
         <v/>
       </c>
     </row>
-    <row r="418" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>869</v>
       </c>
@@ -34743,7 +34771,7 @@
         <v/>
       </c>
     </row>
-    <row r="419" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>870</v>
       </c>
@@ -34811,7 +34839,7 @@
         <v/>
       </c>
     </row>
-    <row r="420" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>871</v>
       </c>
@@ -34879,7 +34907,7 @@
         <v/>
       </c>
     </row>
-    <row r="421" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>872</v>
       </c>
@@ -34947,7 +34975,7 @@
         <v/>
       </c>
     </row>
-    <row r="422" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>873</v>
       </c>
@@ -35015,7 +35043,7 @@
         <v/>
       </c>
     </row>
-    <row r="423" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>874</v>
       </c>
@@ -35083,7 +35111,7 @@
         <v/>
       </c>
     </row>
-    <row r="424" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>875</v>
       </c>
@@ -35151,7 +35179,7 @@
         <v/>
       </c>
     </row>
-    <row r="425" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>876</v>
       </c>
@@ -35219,7 +35247,7 @@
         <v/>
       </c>
     </row>
-    <row r="426" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>877</v>
       </c>
@@ -35287,7 +35315,7 @@
         <v/>
       </c>
     </row>
-    <row r="427" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>878</v>
       </c>
@@ -35355,7 +35383,7 @@
         <v/>
       </c>
     </row>
-    <row r="428" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>879</v>
       </c>
@@ -35423,7 +35451,7 @@
         <v/>
       </c>
     </row>
-    <row r="429" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>880</v>
       </c>
@@ -35491,7 +35519,7 @@
         <v/>
       </c>
     </row>
-    <row r="430" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>881</v>
       </c>
@@ -35559,7 +35587,7 @@
         <v/>
       </c>
     </row>
-    <row r="431" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>882</v>
       </c>
@@ -35627,7 +35655,7 @@
         <v/>
       </c>
     </row>
-    <row r="432" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>883</v>
       </c>
@@ -35695,7 +35723,7 @@
         <v/>
       </c>
     </row>
-    <row r="433" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>884</v>
       </c>
